--- a/context/card_data.xlsx
+++ b/context/card_data.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1447">
   <si>
     <t>Table 1</t>
   </si>
@@ -106,13 +106,13 @@
     <t>Test 1</t>
   </si>
   <si>
-    <t>Booster Pack - Blightsilver / 133</t>
-  </si>
-  <si>
-    <t>Booster Pack - Unseen Presence / 0</t>
-  </si>
-  <si>
-    <t>Booster Pack - Wind of Dominance / 47</t>
+    <t>Booster Pack - Blightsilver / 47</t>
+  </si>
+  <si>
+    <t>Booster Pack - Unseen Presence / 48</t>
+  </si>
+  <si>
+    <t>Booster Pack - Wind of Dominance / 50</t>
   </si>
   <si>
     <t>Pyromancer</t>
@@ -466,7 +466,7 @@
     <t>Once, if survived Reckoning: +ATK&amp;DEF equal to half of that foe’s card</t>
   </si>
   <si>
-    <t>Wide smile lady</t>
+    <t>Wide Smile Lady</t>
   </si>
   <si>
     <t>Nuki the Tanuki</t>
@@ -556,7 +556,7 @@
     <t>Once, after attacked a non-unit cell, this card can attack 1 more time.</t>
   </si>
   <si>
-    <t>Cruel Angel</t>
+    <t>Mean Angel</t>
   </si>
   <si>
     <t>Once, destroy Anima card during battle calculation</t>
@@ -616,7 +616,7 @@
     <t>Fujin</t>
   </si>
   <si>
-    <t>Hachiman the Battlemaster</t>
+    <t>Jiro the Battlemaster</t>
   </si>
   <si>
     <t>-10 ATK permanently at the end of that turn if this card has not performed attack.</t>
@@ -1222,7 +1222,7 @@
     <t>Death Cobra</t>
   </si>
   <si>
-    <t>At the end of this turn, select 1 exposed foe’s card. Put 1 venom flag on it.</t>
+    <t>Owner’s turn end: select 1 exposed card. Put 1 venom flag on it. In Reckoning, foe with Venom Flag get -50 DEF</t>
   </si>
   <si>
     <t>Blood Hound</t>
@@ -1663,7 +1663,7 @@
     <t>Plant-29</t>
   </si>
   <si>
-    <t>Start of owner's turn: Flip a coin. Head: put Venom Flag on 1 exposed card. Tail: put Mutagen Flag on any of your unit.</t>
+    <t>Start of owner's turn: Flip a coin. Head: put Venom Flag on 1 exposed ally or foe card. Tail: put Mutagen Flag on any of your unit.</t>
   </si>
   <si>
     <t>Nanomites Beast</t>
@@ -1985,6 +1985,18 @@
   </si>
   <si>
     <t>Alchemist</t>
+  </si>
+  <si>
+    <t>Venom Queen</t>
+  </si>
+  <si>
+    <t>While this card remains exposed, -15 ATK&amp;DEF to all cards with Venom Flag</t>
+  </si>
+  <si>
+    <t>Vicious Lizard</t>
+  </si>
+  <si>
+    <t>+60 ATK&amp;DEF vs foe with Venom Flag. +40 ATK if itself has Venom Flag</t>
   </si>
   <si>
     <t>Evolving Cell</t>
@@ -2210,10 +2222,10 @@
     <t>Diamond Unicorn</t>
   </si>
   <si>
-    <t>Once Union, ??? until this turn’s end</t>
-  </si>
-  <si>
-    <t>Once Union, +15 ATK until this turn’s end</t>
+    <t>Summoned: ??? until this turn’s end</t>
+  </si>
+  <si>
+    <t>Summoned: +15 ATK until this turn’s end</t>
   </si>
   <si>
     <t>1 ??? + 1 ??? + 500 cost</t>
@@ -2394,10 +2406,10 @@
     <t>Scarlet Shroom</t>
   </si>
   <si>
-    <t xml:space="preserve">If ???, put venom flag on all ???. </t>
-  </si>
-  <si>
-    <t>Once Union, put venom flag on all foe’s exposed card</t>
+    <t xml:space="preserve">Summoned: put venom flag on all ???. </t>
+  </si>
+  <si>
+    <t>Summoned: put venom flag on all foe’s exposed card</t>
   </si>
   <si>
     <t>2 ??? + 500 cost</t>
@@ -3493,10 +3505,13 @@
     <t>Cannot select unit with ?? DEF as attack target. Destroy this card in Reckoning with ???</t>
   </si>
   <si>
-    <t>Booster Pack - Blightsilver / 23</t>
-  </si>
-  <si>
-    <t>Booster Pack - Wind of Dominance / 9</t>
+    <t>Booster Pack - Blightsilver / 9</t>
+  </si>
+  <si>
+    <t>Booster Pack - Unseen Presence / 9</t>
+  </si>
+  <si>
+    <t>Booster Pack - Wind of Dominance / 5</t>
   </si>
   <si>
     <t>Trap Hole</t>
@@ -3605,943 +3620,949 @@
     <t>-20 ATK to all the attacking player’s units until the end of this turn</t>
   </si>
   <si>
+    <t>Radiation</t>
+  </si>
+  <si>
+    <t>Attacking unit permanently lose 10 ATK&amp;DEF. it loses more 10 ATK&amp;DEF for each trap cards in trapper’s void</t>
+  </si>
+  <si>
+    <t>Acid Trap Hole</t>
+  </si>
+  <si>
+    <t>Flip 2 coin, attacking player loses 50 Crystals per each head(s).</t>
+  </si>
+  <si>
+    <t>Lava Trap Hole</t>
+  </si>
+  <si>
+    <t>Flip 3 coin, attacking player loses 100 Crystals per each head(s).</t>
+  </si>
+  <si>
+    <t>Fissure</t>
+  </si>
+  <si>
+    <t>Attacking player loses 200 Crystals</t>
+  </si>
+  <si>
+    <t>Soul Blast</t>
+  </si>
+  <si>
+    <t>Attacking player lose 150 Crystals for each unit cards in trapper’s void</t>
+  </si>
+  <si>
+    <t>Grudge</t>
+  </si>
+  <si>
+    <t>-10 ATK to the attacking monster permanently for each unit cards in trapper’s void</t>
+  </si>
+  <si>
+    <t>Anti-virus</t>
+  </si>
+  <si>
+    <t>If attacker is Bio, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
+  </si>
+  <si>
+    <t>Witch Hunt</t>
+  </si>
+  <si>
+    <t>If attacker is Arcane, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
+  </si>
+  <si>
+    <t>Standoff</t>
+  </si>
+  <si>
+    <t>If attacker is Anima, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
+  </si>
+  <si>
+    <t>Apple of Adam</t>
+  </si>
+  <si>
+    <t>If attacker is Divine, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
+  </si>
+  <si>
+    <t>Purify</t>
+  </si>
+  <si>
+    <t>If attacker is Chaos, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
+  </si>
+  <si>
+    <t>Solar Flare</t>
+  </si>
+  <si>
+    <t>If attacker is Cosmic, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
+  </si>
+  <si>
+    <t>Hunting Season</t>
+  </si>
+  <si>
+    <t>If attacker is Nature, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
+  </si>
+  <si>
+    <t>Dart Trap</t>
+  </si>
+  <si>
+    <t>If the attacking monster is the first one in that turn, destroy it.</t>
+  </si>
+  <si>
+    <t>Science Cage</t>
+  </si>
+  <si>
+    <t>If attacking unit Is Bio affinity, end owner's turn immediately. Remove all flags from it.</t>
+  </si>
+  <si>
+    <t>Loop Hole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If attacker is Arcane, end the owner's turn immediately. </t>
+  </si>
+  <si>
+    <t>Talisman of Light</t>
+  </si>
+  <si>
+    <t>If attacker is Chaos, -50 ATK to that monster permanently</t>
+  </si>
+  <si>
+    <t>Forbidden Grail</t>
+  </si>
+  <si>
+    <t>If attacker is Divine, -50 DEF to that monster permanently</t>
+  </si>
+  <si>
+    <t>Electric Fence</t>
+  </si>
+  <si>
+    <t>If attacker is Nature, it cannot attack until attacker’s next turn ends</t>
+  </si>
+  <si>
+    <t>Discourage</t>
+  </si>
+  <si>
+    <t>If attacker Is Anima -15 ATK to all exposed cards on their side until attacker’s next turn ends</t>
+  </si>
+  <si>
+    <t>Galaxy Toll</t>
+  </si>
+  <si>
+    <t>If attacker is Cosmic, foe loses 1000 Crystals</t>
+  </si>
+  <si>
+    <t>Union Cage</t>
+  </si>
+  <si>
+    <t>If attacking unit Is Union card, that unit cannot attack until the attacker’s next turn ends.</t>
+  </si>
+  <si>
+    <t>Plunder</t>
+  </si>
+  <si>
+    <t>The attacker chooses to let trapper receive 2000 Crystals, or destroy the attacking monster.</t>
+  </si>
+  <si>
+    <t>Decoy Puppet</t>
+  </si>
+  <si>
+    <t>This turn, attacker cannot perform any more attack using unit with 400 or less cost.</t>
+  </si>
+  <si>
+    <t>Hard Scale</t>
+  </si>
+  <si>
+    <t>All of trapper’s unit gain +5 DEF in Reckoning until attacker’s next turn ends</t>
+  </si>
+  <si>
+    <t>Steel Scale</t>
+  </si>
+  <si>
+    <t>All of trapper’s units gain +15 DEF in Reckoning until attacker’s next turn ends</t>
+  </si>
+  <si>
+    <t>Trick Door</t>
+  </si>
+  <si>
+    <t>Trapper select 1 unit and swap or relocate to any cell. Repeat Reckoning if it’s this cell.</t>
+  </si>
+  <si>
+    <t>Boiling Oil</t>
+  </si>
+  <si>
+    <t>All of attacker’s unit get -10 ATK in Reckoning until this turn’s end</t>
+  </si>
+  <si>
+    <t>Lightning Rod</t>
+  </si>
+  <si>
+    <t>Foe loses 1000 Crystals if they target this card with any tech card</t>
+  </si>
+  <si>
+    <t>Dreamcatcher</t>
+  </si>
+  <si>
+    <t>When foe use a tech card, this card can be triggered. That tech card effect is cancelled.</t>
+  </si>
+  <si>
+    <t>Stumble</t>
+  </si>
+  <si>
+    <t>Attacker ends owner's turn immediately. If attacker has any remaining attack, they are transferred to their next turn.</t>
+  </si>
+  <si>
+    <t>Ruckus</t>
+  </si>
+  <si>
+    <t>Until the end of trapper’s turn, All exposed Bio monster gain +5 ATK</t>
+  </si>
+  <si>
+    <t>Red Card</t>
+  </si>
+  <si>
+    <t>Flip 2 coin, if both are head, that unit cannot until attacker’s next turn ends</t>
+  </si>
+  <si>
+    <t>Counter Punch</t>
+  </si>
+  <si>
+    <t>Attacking unit get -5 DEF until the end of trapper’s turn</t>
+  </si>
+  <si>
+    <t>Counter Tackle</t>
+  </si>
+  <si>
+    <t>Attacking unit get -15 DEF until the end of trapper’s turn</t>
+  </si>
+  <si>
+    <t>Street Joke</t>
+  </si>
+  <si>
+    <t>Trapper reveal 1 of their cell, they receive 100 Crystal</t>
+  </si>
+  <si>
+    <t>Alarm</t>
+  </si>
+  <si>
+    <t>Until this turn ends, All trapper’s Anima monster gain +10 DEF in Reckoning</t>
+  </si>
+  <si>
+    <t>Protective Instinct</t>
+  </si>
+  <si>
+    <t>Trapper select 1 Nature unit. Until the end of trapper’s turn, that card gain +10 ATK</t>
+  </si>
+  <si>
+    <t>Self-destruct</t>
+  </si>
+  <si>
+    <t>Trapper select 1 of their unit. +10 ATK until trapper’s turn ends, but also destroy it. Trapper pay no cost.</t>
+  </si>
+  <si>
+    <t>Bounty</t>
+  </si>
+  <si>
+    <t>Until the end of trapper’s turn, if trapper destroy that unit, they receive Crystal equal to half of the unit’s cost</t>
+  </si>
+  <si>
+    <t>Pepper Spray</t>
+  </si>
+  <si>
+    <t>Flip 2 coin, if head, the attacker lose -5 ATK for each head(s) until attacker’s next turn ends.</t>
+  </si>
+  <si>
+    <t>Share the Pain</t>
+  </si>
+  <si>
+    <t>If trapper has 1000 or less Crystal, drain Crystal from attacker until both players have same amount of Crystals</t>
+  </si>
+  <si>
+    <t>Tripwire</t>
+  </si>
+  <si>
+    <t>Destroy the attacker with 20 or less ATK. Attacker side pay no cost.</t>
+  </si>
+  <si>
+    <t>Illustration</t>
+  </si>
+  <si>
+    <t>Booster Pack - Blightsilver / 4</t>
+  </si>
+  <si>
+    <t>Booster Pack - Unseen Presence / 3</t>
+  </si>
+  <si>
+    <t>Welcoming Door</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>Choose any square on their side and reveal it</t>
+  </si>
+  <si>
+    <t>Spy</t>
+  </si>
+  <si>
+    <t>Reveal 1 of foe’s cell</t>
+  </si>
+  <si>
+    <t>Ceasefire</t>
+  </si>
+  <si>
+    <t>Both players skip 1 turn (tax is forced to apply)</t>
+  </si>
+  <si>
+    <t>Make Friend</t>
+  </si>
+  <si>
+    <t>Both players select 1 monster from their side. That monster cannot attack until this player’s next turn ends</t>
+  </si>
+  <si>
+    <t>Double Spy</t>
+  </si>
+  <si>
+    <t>Only trigger if this player have Spy card in the void. Reveal 2 square on foe's side of the field.</t>
+  </si>
+  <si>
+    <t>Invisible Spy</t>
+  </si>
+  <si>
+    <t>Only trigger if this player have Double Spy card in the void. Reveal 2 square on foe's side of the field.</t>
+  </si>
+  <si>
+    <t>Corrupted Spy</t>
+  </si>
+  <si>
+    <t>Reveal 3 square on foe's side of the field. If any trap or unit is found, this player pays 700 Crystal for each card found.</t>
+  </si>
+  <si>
+    <t>Tease</t>
+  </si>
+  <si>
+    <t>Foe chooses and reveal 1 of their cell</t>
+  </si>
+  <si>
+    <t>Bribe</t>
+  </si>
+  <si>
+    <t>Foe can choose to reveal a unit card and receive 700 Crystals or do nothing</t>
+  </si>
+  <si>
+    <t>Release Mutagen</t>
+  </si>
+  <si>
+    <t>Add Mutagen Flag to 1 of this player’s unit</t>
+  </si>
+  <si>
+    <t>Prayer</t>
+  </si>
+  <si>
+    <t>Once, until foe’s turn ends: prevent Divine card from being destroyed</t>
+  </si>
+  <si>
+    <t>Arcane Nova</t>
+  </si>
+  <si>
+    <t>Destroy up to 3 exposed foe units (no cost is paid). This player discard all of their tech cards afterward.</t>
+  </si>
+  <si>
+    <t>Rift Strike</t>
+  </si>
+  <si>
+    <t>Select 1 exposed foe’s card. Destroy other exposed units on that same rows. Foe don’t pay cost.</t>
+  </si>
+  <si>
+    <t>Great Diplomacy</t>
+  </si>
+  <si>
+    <t>This player selects up to 5 of their units and reveal them.</t>
+  </si>
+  <si>
+    <t>War Supply</t>
+  </si>
+  <si>
+    <t>This player’s units get +10 ATK&amp;DEF in Reckoning until turn’s end</t>
+  </si>
+  <si>
+    <t>Harsh Training</t>
+  </si>
+  <si>
+    <t>+10 ATK permanently to one of this player's unit.</t>
+  </si>
+  <si>
+    <t>Illegal Steroid</t>
+  </si>
+  <si>
+    <t>+30 ATK for 1 unit until the end of this turn.</t>
+  </si>
+  <si>
+    <t>Secret Dagger</t>
+  </si>
+  <si>
+    <t>Can only be used on face-down card. Turn that card exposed and +15 ATK until the end of this turn.</t>
+  </si>
+  <si>
+    <t>Garrison</t>
+  </si>
+  <si>
+    <t>Until foe's turn ends: +20 DEF to all this player's cards in Reckoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulletproof Vest </t>
+  </si>
+  <si>
+    <t>+15 DEF permanently for 1 exposed unit. If use on face-down card, flip it up.</t>
+  </si>
+  <si>
+    <t>Siege Cannon</t>
+  </si>
+  <si>
+    <t>Until the end of this turn, once, foe’s defending unit is destroyed.</t>
+  </si>
+  <si>
+    <t>Silence Agent</t>
+  </si>
+  <si>
+    <t>Destroy 1 of foe’s exposed card</t>
+  </si>
+  <si>
+    <t>Accident</t>
+  </si>
+  <si>
+    <t>Destroy 1 of foe’s exposed card. If there is no exposed card, foe must choose the target. foe pays no cost.</t>
+  </si>
+  <si>
+    <t>Berserk</t>
+  </si>
+  <si>
+    <t>Select 1 of this player's exposed unit. They get 1 additional attack, but can only perform attack with that unit. Can’t use this card if already performed any attack.</t>
+  </si>
+  <si>
+    <t>Radar</t>
+  </si>
+  <si>
+    <t>Reveal 3 of foe’s cell</t>
+  </si>
+  <si>
+    <t>Palace Party</t>
+  </si>
+  <si>
+    <t>This player reveal 1 face-down unit. Foe must reveal 1 of their face-down unit (if any)</t>
+  </si>
+  <si>
+    <t>Essence Transfer</t>
+  </si>
+  <si>
+    <t>This player chooses 1 unit. Move all its ATK&amp;DEF bonuses or debuffs to another ally unit.</t>
+  </si>
+  <si>
+    <t>Blood Ritual</t>
+  </si>
+  <si>
+    <t>Destroy 1 card on this player’s side (No paid cost). Choose 1 of foe's exposed unit. Its ATK&amp;DEF becomes 0 permanently</t>
+  </si>
+  <si>
+    <t>Arcane Duplication</t>
+  </si>
+  <si>
+    <t>This player. Choose 1 unit. Create a token copy of it on an empty cell. Destroy it at the end of this player’s next turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Travel </t>
+  </si>
+  <si>
+    <t>Once only, revive 1 unit to any unoccupied or empty cell in exposed position. Double its Crystal cost.</t>
+  </si>
+  <si>
+    <t>Resurrection</t>
+  </si>
+  <si>
+    <t>Once, revive 1 unit. It has no ATK,DEF, or ability.</t>
+  </si>
+  <si>
+    <t>Tech Copy</t>
+  </si>
+  <si>
+    <t>Foe show 1 tech card in their hand. Add a copy of that card into this player's Tech Stack.</t>
+  </si>
+  <si>
+    <t>Force Shield</t>
+  </si>
+  <si>
+    <t>This player selects 1 card. It is not destroyed until the end of foe's turn</t>
+  </si>
+  <si>
+    <t>Wisp Light</t>
+  </si>
+  <si>
+    <t>Destroy as many ally ‘wisp’ units. Reveal that much cells on foe's side.</t>
+  </si>
+  <si>
+    <t>Lucky Day</t>
+  </si>
+  <si>
+    <t>Flip a coin. If head, receive 600 Crystals. Always head, if trapper’s Crystal is 1000 or less.</t>
+  </si>
+  <si>
+    <t>Immortal Blood</t>
+  </si>
+  <si>
+    <t>Revive 1 immortal vampire or vampire servant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yin Yang Swap </t>
+  </si>
+  <si>
+    <t>Swap ATK&amp;DEF on 1 exposed unit until the end of this turn</t>
+  </si>
+  <si>
+    <t>Coin on the Street</t>
+  </si>
+  <si>
+    <t>Receive 20 Crystals</t>
+  </si>
+  <si>
+    <t>Bank Note on the Street</t>
+  </si>
+  <si>
+    <t>Receive 50 Crystals</t>
+  </si>
+  <si>
+    <t>Casual Gambling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flip a coin. If head, receive 100 Crystals. </t>
+  </si>
+  <si>
+    <t>Degen Gambling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flip a coin. If head, receive 200 Crystals. If tail, lose 400 Crystals </t>
+  </si>
+  <si>
+    <t>Gift</t>
+  </si>
+  <si>
+    <t>Foe receive 50 Crystals</t>
+  </si>
+  <si>
+    <t>Hired Spanker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until the end of foe's turn, if foe attack the bluffed cell, foe receive 1000 Crystals. </t>
+  </si>
+  <si>
+    <t>Tax Avoidance</t>
+  </si>
+  <si>
+    <t>End this player’s turn without paying tax (the tax penalty still doubles)</t>
+  </si>
+  <si>
+    <t>Compensation</t>
+  </si>
+  <si>
+    <t>This turn, whenever this player attack a Dead End, they receive 20 Crystals</t>
+  </si>
+  <si>
+    <t>Phony Fight</t>
+  </si>
+  <si>
+    <t>-10 DEF to 1 exposed unit on the field until the end of this turn. Foe receive 500 Crystals</t>
+  </si>
+  <si>
+    <t>Facetious</t>
+  </si>
+  <si>
+    <t>Send an emoticon bubble to another player once</t>
+  </si>
+  <si>
+    <t>Telepathy</t>
+  </si>
+  <si>
+    <t>Send a very short message to foe once.</t>
+  </si>
+  <si>
+    <t>Borrow</t>
+  </si>
+  <si>
+    <t>Receive 200 Crystals. At the end of this player’s turn, they lose 300 Crystals</t>
+  </si>
+  <si>
+    <t>Flimsy Axe</t>
+  </si>
+  <si>
+    <t>Flip a coin. If head, +5 ATK to 1 ally unit until this turn ends.</t>
+  </si>
+  <si>
+    <t>Flimsy Shield</t>
+  </si>
+  <si>
+    <t>Flip a coin. If head, +5 DEF to 1 ally unit until this turn ends.</t>
+  </si>
+  <si>
+    <t>All-out Tactics</t>
+  </si>
+  <si>
+    <t>+10 ATK to one ally unit permanently. But its DEF becomes 0 permanently.</t>
+  </si>
+  <si>
+    <t>Fair Fight</t>
+  </si>
+  <si>
+    <t>Both players select 1 of their unit. They gain +10 ATK&amp;DEF permanently</t>
+  </si>
+  <si>
+    <t>Greater Telepathy</t>
+  </si>
+  <si>
+    <t>Send a medium length message to foe once.</t>
+  </si>
+  <si>
+    <t>Loan</t>
+  </si>
+  <si>
+    <t>Receive 600 Crystals. At this player’s next turn’s end: lose 800 Crystals</t>
+  </si>
+  <si>
+    <t>Old Spear</t>
+  </si>
+  <si>
+    <t>+5 ATK to 1 ally unit until this turn ends.</t>
+  </si>
+  <si>
+    <t>Old Shield</t>
+  </si>
+  <si>
+    <t>+5 DEF to 1 ally unit until this turn ends.</t>
+  </si>
+  <si>
+    <t>Provoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the end of foe’s turn, foe must attack the selected cell first. </t>
+  </si>
+  <si>
+    <t>Supreme Telepathy</t>
+  </si>
+  <si>
+    <t>Send a long message to foe once.</t>
+  </si>
+  <si>
+    <t>Mortgage</t>
+  </si>
+  <si>
+    <t>Receive 1200 Crystals. At the end of this player’s turn, lose 1500 Crystals</t>
+  </si>
+  <si>
+    <t>Big Finger</t>
+  </si>
+  <si>
+    <t>Send a very big improper emoticon bubble to foe</t>
+  </si>
+  <si>
+    <t>Big Love</t>
+  </si>
+  <si>
+    <t>Send a very big lovely emoticon bubble to foe</t>
+  </si>
+  <si>
+    <t>Pretify</t>
+  </si>
+  <si>
+    <t>+20 DEF permanently to ally unit or foe’s exposed unit. But its ATK becomes 0 permanently.</t>
+  </si>
+  <si>
+    <t>Stone Skin</t>
+  </si>
+  <si>
+    <t>+20 DEF permanently to ally unit. But its ATK becomes 0 permanently.</t>
+  </si>
+  <si>
+    <t>Battle Royale</t>
+  </si>
+  <si>
+    <t>Both players select 1 of their unit. They gain +30 ATK&amp;DEF</t>
+  </si>
+  <si>
+    <t>Guerrilla Tactics</t>
+  </si>
+  <si>
+    <t>Until the end of foe's turn, If they attack a non-unit card, flip a coin. Head: destroy the attacking unit.</t>
+  </si>
+  <si>
+    <t>Toll</t>
+  </si>
+  <si>
+    <t>Until the end of foe's turn, they have to pay 500 Crystal tax to perform an attack.</t>
+  </si>
+  <si>
+    <t>Skull Amulet</t>
+  </si>
+  <si>
+    <t>+5 ATK permanently to 1 Chaos card.</t>
+  </si>
+  <si>
+    <t>Might</t>
+  </si>
+  <si>
+    <t>+10 ATK to 1 ally Anima card until this turn ends</t>
+  </si>
+  <si>
+    <t>Arcane Knowledge</t>
+  </si>
+  <si>
+    <t>+5 ATK&amp;DEF to 1 ally Arcane unit until the end of foe’s turn.</t>
+  </si>
+  <si>
+    <t>Forest Fire</t>
+  </si>
+  <si>
+    <t>Destroy all Nature cards on foe's side. Discard all of this player’s Tech cards.</t>
+  </si>
+  <si>
+    <t>Black Hole</t>
+  </si>
+  <si>
+    <t>Destroy all Cosmo cards on foe's side. Discard all of this player’s Tech cards.</t>
+  </si>
+  <si>
+    <t>Holy Arrival</t>
+  </si>
+  <si>
+    <t>Destroy all Chaos cards on foe's side. Discard all of this player’s Tech cards.</t>
+  </si>
+  <si>
+    <t>Corrupted Heaven</t>
+  </si>
+  <si>
+    <t>Destroy all Divine cards on foe's side. Discard all of this player’s Tech cards.</t>
+  </si>
+  <si>
+    <t>Earthquake</t>
+  </si>
+  <si>
+    <t>Destroy all Anima cards on foe's side. Discard all of this player’s Tech cards.</t>
+  </si>
+  <si>
+    <t>Lab Destruction</t>
+  </si>
+  <si>
+    <t>Destroy all Bio cards on foe's side. Discard all of this player’s Tech cards.</t>
+  </si>
+  <si>
+    <t>Anti-magic Field</t>
+  </si>
+  <si>
+    <t>Destroy all Arcane cards on foe's side. Discard all of this player’s Tech cards.</t>
+  </si>
+  <si>
+    <t>Air Shower</t>
+  </si>
+  <si>
+    <t>Clear all flags on the field</t>
+  </si>
+  <si>
+    <t>Mining Tax</t>
+  </si>
+  <si>
+    <t>Until the end of foe’s turn, if any player attacks a Dead End, that player loses 200 Crystals</t>
+  </si>
+  <si>
+    <t>Ouija</t>
+  </si>
+  <si>
+    <t>Reveal foe’s cells up to number of this player’s unit in the void.</t>
+  </si>
+  <si>
+    <t>Deep Mine</t>
+  </si>
+  <si>
+    <t>Flip a coin. If head, reveal 2 square on foe's side of the field</t>
+  </si>
+  <si>
+    <t>Gold Panning</t>
+  </si>
+  <si>
+    <t>Flip a coin. If head, reveal 1 square on foe's side of the field</t>
+  </si>
+  <si>
+    <t>Flashlight</t>
+  </si>
+  <si>
+    <t>Reveal 1 column on foe’s side. Cannot perform attack this turn. Cannot use this card if already attacked this turn.</t>
+  </si>
+  <si>
+    <t>Lantern</t>
+  </si>
+  <si>
+    <t>Reveal 2 adjacent cells on foe's side of the field.</t>
+  </si>
+  <si>
+    <t>GPS Tracker</t>
+  </si>
+  <si>
+    <t>Reveal 2 adjacent cells next to exposed unit on foe's side of the field.</t>
+  </si>
+  <si>
+    <t>Blessing</t>
+  </si>
+  <si>
+    <t>Clear all flags from 1 ally unit</t>
+  </si>
+  <si>
+    <t>Bright Sun</t>
+  </si>
+  <si>
+    <t>Clear all flags from all cards on the field</t>
+  </si>
+  <si>
+    <t>Rugpull</t>
+  </si>
+  <si>
+    <t>Both players lose 2000 Crystals. Discard all tech in this player’s hands.</t>
+  </si>
+  <si>
+    <t>Crack the Whip</t>
+  </si>
+  <si>
+    <t>Once, this player’s attacking unit can attack twice. But it cannot attack again until the end of this player’s next turn.</t>
+  </si>
+  <si>
+    <t>Need Revise</t>
+  </si>
+  <si>
+    <t>Full open fire</t>
+  </si>
+  <si>
+    <t>Both players gain 2 additional attack for one of owner's turn.</t>
+  </si>
+  <si>
+    <t>Service Charge</t>
+  </si>
+  <si>
+    <t>Until the end of foe's turn. Foe have to pay 50 Crystal tax to perform an attack.</t>
+  </si>
+  <si>
+    <t>Lazy Scout</t>
+  </si>
+  <si>
+    <t>Reveal 1 foe’s cell. This player cannot perform any attack. Cannot use this card if already attacked.</t>
+  </si>
+  <si>
+    <t>Last Gambit</t>
+  </si>
+  <si>
+    <t>If this player has 5 or less cards on the field, destroy 1 foe’s card.</t>
+  </si>
+  <si>
+    <t>Trash Penalty</t>
+  </si>
+  <si>
+    <t>Foe chooses either clearing all of their bluffs or take 500 damage</t>
+  </si>
+  <si>
+    <t>Silence Zone</t>
+  </si>
+  <si>
+    <t>Clear all bluffs from both players. No one can use bluff ever again during this duel.</t>
+  </si>
+  <si>
+    <t>Big Mouth</t>
+  </si>
+  <si>
+    <t>Select 1 cell. Bluff on that cell becomes large permanently</t>
+  </si>
+  <si>
+    <t>Bare Fist Fight</t>
+  </si>
+  <si>
+    <t>Both players select and discard 1 tech card from their hand.</t>
+  </si>
+  <si>
+    <t>Mine Detector</t>
+  </si>
+  <si>
+    <t>Reveal 1 card on foe's side. If it’s a trap, destroy it and gain 200 Crystals</t>
+  </si>
+  <si>
+    <t>Natural Healing</t>
+  </si>
+  <si>
+    <t>If all exposed ally units are Nature card, gain 40 Crystals for each of them</t>
+  </si>
+  <si>
+    <t>Third Eye</t>
+  </si>
+  <si>
+    <t>If this is the last tech card on this player’s hand, reveal 3 cards on foe's side</t>
+  </si>
+  <si>
+    <t>Punching Bag</t>
+  </si>
+  <si>
+    <t>1 ally unit’s ATK&amp;DEF becomes 0 permanently. It cannot be destroyed until the end of foe’s turn.</t>
+  </si>
+  <si>
+    <t>Scattered Shot</t>
+  </si>
+  <si>
+    <t>Flip 3 coins. Destroy foe’s exposed unit equal to number of heads. foe pays no cost.</t>
+  </si>
+  <si>
+    <t>Spotlight</t>
+  </si>
+  <si>
+    <t>Flip 5 coins. Reveal foe’s cell equal to number of heads</t>
+  </si>
+  <si>
+    <t>Tight Door</t>
+  </si>
+  <si>
+    <t>Next turn, foe can attack only once</t>
+  </si>
+  <si>
+    <t>Katana Strike</t>
+  </si>
+  <si>
+    <t>Select 1 exposed foe’s card. Destroy other exposed cards on that same columns as the selected cell. Foe don’t pay Crystal cost.</t>
+  </si>
+  <si>
+    <t>Mining Season</t>
+  </si>
+  <si>
+    <t>Until foe’s turn ends, both players can only target face-down card</t>
+  </si>
+  <si>
+    <t>Throne Duel</t>
+  </si>
+  <si>
+    <t>Until foe’s turn ends, both players can only attack with unit with 800 or more cost. Cannot use if already attacked.</t>
+  </si>
+  <si>
+    <t>Joint Maneuver</t>
+  </si>
+  <si>
+    <t>Until foe’s turn ends, both players can only attack with unit with 600 or less cost. Cannot use if already attacked.</t>
+  </si>
+  <si>
+    <t>Pillow Fight</t>
+  </si>
+  <si>
+    <t>Until foe’s turn ends, both players can only attack with unit with 300 or less cost. Cannot use if already attacked.</t>
+  </si>
+  <si>
+    <t>Army Reformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swap or relocate 1 unit to any cell. </t>
+  </si>
+  <si>
+    <t>Institutionalization</t>
+  </si>
+  <si>
+    <t>Target 1 foe’s unit. Its ability becomes None until foe’s next turn ends</t>
+  </si>
+  <si>
     <t>Potent Poison</t>
   </si>
   <si>
-    <t>Attacking unit permanently lose 5 ATK&amp;DEF. it loses more 5 ATK&amp;DEF for each trap cards in trapper’s void</t>
-  </si>
-  <si>
-    <t>Acid Trap Hole</t>
-  </si>
-  <si>
-    <t>Flip 2 coin, attacking player loses 50 Crystals per each head(s).</t>
-  </si>
-  <si>
-    <t>Lava Trap Hole</t>
-  </si>
-  <si>
-    <t>Flip 3 coin, attacking player loses 100 Crystals per each head(s).</t>
-  </si>
-  <si>
-    <t>Fissure</t>
-  </si>
-  <si>
-    <t>Attacking player loses 200 Crystals</t>
-  </si>
-  <si>
-    <t>Soul Blast</t>
-  </si>
-  <si>
-    <t>Attacking player lose 150 Crystals for each unit cards in trapper’s void</t>
-  </si>
-  <si>
-    <t>Grudge</t>
-  </si>
-  <si>
-    <t>-10 ATK to the attacking monster permanently for each unit cards in trapper’s void</t>
-  </si>
-  <si>
-    <t>Anti-virus</t>
-  </si>
-  <si>
-    <t>If attacker is Bio, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
-  </si>
-  <si>
-    <t>Witch Hunt</t>
-  </si>
-  <si>
-    <t>If attacker is Arcane, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
-  </si>
-  <si>
-    <t>Standoff</t>
-  </si>
-  <si>
-    <t>If attacker is Anima, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
-  </si>
-  <si>
-    <t>Apple of Adam</t>
-  </si>
-  <si>
-    <t>If attacker is Divine, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
-  </si>
-  <si>
-    <t>Purify</t>
-  </si>
-  <si>
-    <t>If attacker is Chaos, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
-  </si>
-  <si>
-    <t>Solar Flare</t>
-  </si>
-  <si>
-    <t>If attacker is Cosmic, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
-  </si>
-  <si>
-    <t>Hunting Season</t>
-  </si>
-  <si>
-    <t>If attacker is Nature, flip a coin. Head: destroy it. Always head, if trapper’s Crystal is 1000 or less.</t>
-  </si>
-  <si>
-    <t>Dart Trap</t>
-  </si>
-  <si>
-    <t>If the attacking monster is the first one in that turn, destroy it.</t>
-  </si>
-  <si>
-    <t>Science Cage</t>
-  </si>
-  <si>
-    <t>If attacking unit Is Bio affinity, end owner's turn immediately. Remove all flags from it.</t>
-  </si>
-  <si>
-    <t>Loop Hole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If attacker is Arcane, end the owner's turn immediately. </t>
-  </si>
-  <si>
-    <t>Talisman of Light</t>
-  </si>
-  <si>
-    <t>If attacker is Chaos, -50 ATK to that monster permanently</t>
-  </si>
-  <si>
-    <t>Forbidden Grail</t>
-  </si>
-  <si>
-    <t>If attacker is Divine, -50 DEF to that monster permanently</t>
-  </si>
-  <si>
-    <t>Electric Fence</t>
-  </si>
-  <si>
-    <t>If attacker is Nature, it cannot attack until attacker’s next turn ends</t>
-  </si>
-  <si>
-    <t>Discourage</t>
-  </si>
-  <si>
-    <t>If attacker Is Anima -15 ATK to all exposed cards on their side until attacker’s next turn ends</t>
-  </si>
-  <si>
-    <t>Galaxy Toll</t>
-  </si>
-  <si>
-    <t>If attacker is Cosmic, foe loses 1000 Crystals</t>
-  </si>
-  <si>
-    <t>Union Cage</t>
-  </si>
-  <si>
-    <t>If attacking unit Is Union card, that unit cannot attack until the attacker’s next turn ends.</t>
-  </si>
-  <si>
-    <t>Plunder</t>
-  </si>
-  <si>
-    <t>The attacker chooses to let trapper receive 2000 Crystals, or destroy the attacking monster.</t>
-  </si>
-  <si>
-    <t>Decoy Puppet</t>
-  </si>
-  <si>
-    <t>This turn, attacker cannot perform any more attack using unit with 400 or less cost.</t>
-  </si>
-  <si>
-    <t>Hard Scale</t>
-  </si>
-  <si>
-    <t>All of trapper’s unit gain +5 DEF in Reckoning until attacker’s next turn ends</t>
-  </si>
-  <si>
-    <t>Steel Scale</t>
-  </si>
-  <si>
-    <t>All of trapper’s units gain +15 DEF in Reckoning until attacker’s next turn ends</t>
-  </si>
-  <si>
-    <t>Trick Door</t>
-  </si>
-  <si>
-    <t>Trapper select 1 unit and swap or relocate to any cell. Repeat Reckoning if it’s this cell.</t>
-  </si>
-  <si>
-    <t>Boiling Oil</t>
-  </si>
-  <si>
-    <t>All of attacker’s unit get -10 ATK in Reckoning until this turn’s end</t>
-  </si>
-  <si>
-    <t>Lightning Rod</t>
-  </si>
-  <si>
-    <t>Foe loses 1000 Crystals if they target this card with any tech card</t>
-  </si>
-  <si>
-    <t>Dreamcatcher</t>
-  </si>
-  <si>
-    <t>When foe use a tech card, this card can be triggered. That tech card effect is cancelled.</t>
-  </si>
-  <si>
-    <t>Stumble</t>
-  </si>
-  <si>
-    <t>Attacker ends owner's turn immediately. If attacker has any remaining attack, they are transferred to their next turn.</t>
-  </si>
-  <si>
-    <t>Ruckus</t>
-  </si>
-  <si>
-    <t>Until the end of trapper’s turn, All exposed Bio monster gain +5 ATK</t>
-  </si>
-  <si>
-    <t>Red Card</t>
-  </si>
-  <si>
-    <t>Flip 2 coin, if both are head, that unit cannot until attacker’s next turn ends</t>
-  </si>
-  <si>
-    <t>Counter Punch</t>
-  </si>
-  <si>
-    <t>Attacking unit get -5 DEF until the end of trapper’s turn</t>
-  </si>
-  <si>
-    <t>Counter Tackle</t>
-  </si>
-  <si>
-    <t>Attacking unit get -15 DEF until the end of trapper’s turn</t>
-  </si>
-  <si>
-    <t>Street Joke</t>
-  </si>
-  <si>
-    <t>Reveal 1 of trapper’s cell, they receive 100 Crystal</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Until this turn ends, All trapper’s Anima monster gain +10 DEF in Reckoning</t>
-  </si>
-  <si>
-    <t>Protective Instinct</t>
-  </si>
-  <si>
-    <t>Trapper select 1 Nature unit. Until the end of trapper’s turn, that card gain +10 ATK</t>
-  </si>
-  <si>
-    <t>Self-destruct</t>
-  </si>
-  <si>
-    <t>Trapper select 1 of their unit. +10 ATK until trapper’s turn ends, but also destroy it. Trapper pay no cost.</t>
-  </si>
-  <si>
-    <t>Bounty</t>
-  </si>
-  <si>
-    <t>Until the end of trapper’s turn, if trapper destroy that unit, they receive Crystal equal to half of the unit’s cost</t>
-  </si>
-  <si>
-    <t>Pepper Spray</t>
-  </si>
-  <si>
-    <t>Flip 2 coin, if head, the attacker lose -5 ATK for each head(s) until attacker’s next turn ends.</t>
-  </si>
-  <si>
-    <t>Share the Pain</t>
-  </si>
-  <si>
-    <t>If trapper has 1000 or less Crystal, drain Crystal from attacker until both players have same amount of Crystals</t>
-  </si>
-  <si>
-    <t>Tripwire</t>
-  </si>
-  <si>
-    <t>Destroy the attacker with 20 or less ATK. Attacker side pay no cost.</t>
-  </si>
-  <si>
-    <t>Illustration</t>
-  </si>
-  <si>
-    <t>Booster Pack - Blightsilver / 11</t>
-  </si>
-  <si>
-    <t>Booster Pack - Wind of Dominance / 4</t>
-  </si>
-  <si>
-    <t>Welcoming Door</t>
-  </si>
-  <si>
-    <t>Tech</t>
-  </si>
-  <si>
-    <t>Choose any square on their side and reveal it</t>
-  </si>
-  <si>
-    <t>Spy</t>
-  </si>
-  <si>
-    <t>Reveal 1 of foe’s cell</t>
-  </si>
-  <si>
-    <t>Ceasefire</t>
-  </si>
-  <si>
-    <t>Both players skip 1 turn (tax is forced to apply)</t>
-  </si>
-  <si>
-    <t>Make Friend</t>
-  </si>
-  <si>
-    <t>Both players select 1 monster from their side. That monster cannot attack until this player’s next turn ends</t>
-  </si>
-  <si>
-    <t>Double Spy</t>
-  </si>
-  <si>
-    <t>Only trigger if this player have Spy card in the void. Reveal 2 square on foe's side of the field.</t>
-  </si>
-  <si>
-    <t>Invisible Spy</t>
-  </si>
-  <si>
-    <t>Only trigger if this player have Double Spy card in the void. Reveal 2 square on foe's side of the field.</t>
-  </si>
-  <si>
-    <t>Corrupted Spy</t>
-  </si>
-  <si>
-    <t>Reveal 3 square on foe's side of the field. If any trap or unit is found, this player pays 700 Crystal for each card found.</t>
-  </si>
-  <si>
-    <t>Tease</t>
-  </si>
-  <si>
-    <t>Foe chooses and reveal 1 of their cell</t>
-  </si>
-  <si>
-    <t>Bribe</t>
-  </si>
-  <si>
-    <t>Foe can choose to reveal a unit card and receive 700 Crystals or do nothing</t>
-  </si>
-  <si>
-    <t>Release Mutagen</t>
-  </si>
-  <si>
-    <t>Add Mutagen Flag to 1 of this player’s unit</t>
-  </si>
-  <si>
-    <t>Prayer</t>
-  </si>
-  <si>
-    <t>Once, until foe’s turn ends: prevent Divine card from being destroyed</t>
-  </si>
-  <si>
-    <t>Arcane Nova</t>
-  </si>
-  <si>
-    <t>Destroy up to 3 exposed foe units (no cost is paid). This player discard all of their tech cards afterward.</t>
-  </si>
-  <si>
-    <t>Rift Strike</t>
-  </si>
-  <si>
-    <t>Select 1 exposed foe’s card. Destroy other exposed units on that same rows. Foe don’t pay cost.</t>
-  </si>
-  <si>
-    <t>Great Diplomacy</t>
-  </si>
-  <si>
-    <t>This player selects up to 5 of their units and reveal them.</t>
-  </si>
-  <si>
-    <t>War Supply</t>
-  </si>
-  <si>
-    <t>This player’s units get +10 ATK&amp;DEF in Reckoning until turn’s end</t>
-  </si>
-  <si>
-    <t>Harsh Training</t>
-  </si>
-  <si>
-    <t>+10 ATK permanently to one of this player's unit.</t>
-  </si>
-  <si>
-    <t>Illegal Steroid</t>
-  </si>
-  <si>
-    <t>+30 ATK for 1 unit until the end of this turn.</t>
-  </si>
-  <si>
-    <t>Secret Dagger</t>
-  </si>
-  <si>
-    <t>Can only be used on face-down card. Turn that card exposed and +15 ATK until the end of this turn.</t>
-  </si>
-  <si>
-    <t>Garrison</t>
-  </si>
-  <si>
-    <t>Until foe's turn ends: +20 DEF to all this player's cards in Reckoning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulletproof Vest </t>
-  </si>
-  <si>
-    <t>+15 DEF permanently for 1 exposed unit. If use on face-down card, flip it up.</t>
-  </si>
-  <si>
-    <t>Siege Cannon</t>
-  </si>
-  <si>
-    <t>Until the end of this turn, once, foe’s defending unit is destroyed.</t>
-  </si>
-  <si>
-    <t>Silence Agent</t>
-  </si>
-  <si>
-    <t>Destroy 1 of foe’s exposed card</t>
-  </si>
-  <si>
-    <t>Accident</t>
-  </si>
-  <si>
-    <t>Destroy 1 of foe’s exposed card. If there is no exposed card, foe must choose the target. foe pays no cost.</t>
-  </si>
-  <si>
-    <t>Berserk</t>
-  </si>
-  <si>
-    <t>Select 1 of this player's exposed unit. They get 1 additional attack, but can only perform attack with that unit. Can’t use this card if already performed any attack.</t>
-  </si>
-  <si>
-    <t>Radar</t>
-  </si>
-  <si>
-    <t>Reveal 3 of foe’s cell</t>
-  </si>
-  <si>
-    <t>Palace Party</t>
-  </si>
-  <si>
-    <t>This player reveal 1 face-down unit. Foe must reveal 1 of their face-down unit (if any)</t>
-  </si>
-  <si>
-    <t>Essence Transfer</t>
-  </si>
-  <si>
-    <t>This player chooses 1 unit. Move all its ATK&amp;DEF bonuses or debuffs to another ally unit.</t>
-  </si>
-  <si>
-    <t>Blood Ritual</t>
-  </si>
-  <si>
-    <t>Destroy 1 card on this player’s side (No paid cost). Choose 1 of foe's exposed unit. Its ATK&amp;DEF becomes 0 permanently</t>
-  </si>
-  <si>
-    <t>Arcane Duplication</t>
-  </si>
-  <si>
-    <t>This player. Choose 1 unit. Create a token copy of it on an empty cell. Destroy it at the end of this player’s next turn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Travel </t>
-  </si>
-  <si>
-    <t>Once only, revive 1 unit to any unoccupied or empty cell in exposed position. Double its Crystal cost.</t>
-  </si>
-  <si>
-    <t>Resurrection</t>
-  </si>
-  <si>
-    <t>Once, revive 1 unit. It has no ATK,DEF, or ability.</t>
-  </si>
-  <si>
-    <t>Tech Copy</t>
-  </si>
-  <si>
-    <t>Foe show 1 tech card in their hand. Add a copy of that card into this player's Tech Stack.</t>
-  </si>
-  <si>
-    <t>Force Shield</t>
-  </si>
-  <si>
-    <t>This player selects 1 card. It is not destroyed until the end of foe's turn</t>
-  </si>
-  <si>
-    <t>Wisp Light</t>
-  </si>
-  <si>
-    <t>Destroy as many ally ‘wisp’ units. Reveal that much cells on foe's side.</t>
-  </si>
-  <si>
-    <t>Lucky Day</t>
-  </si>
-  <si>
-    <t>Flip a coin. If head, receive 600 Crystals. Always head, if trapper’s Crystal is 1000 or less.</t>
-  </si>
-  <si>
-    <t>Immortal Blood</t>
-  </si>
-  <si>
-    <t>Revive 1 immortal vampire or vampire servant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yin Yang Swap </t>
-  </si>
-  <si>
-    <t>Swap ATK&amp;DEF on 1 exposed unit until the end of this turn</t>
-  </si>
-  <si>
-    <t>Coin on the Street</t>
-  </si>
-  <si>
-    <t>Receive 20 Crystals</t>
-  </si>
-  <si>
-    <t>Bank Note on the Street</t>
-  </si>
-  <si>
-    <t>Receive 50 Crystals</t>
-  </si>
-  <si>
-    <t>Casual Gambling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flip a coin. If head, receive 100 Crystals. </t>
-  </si>
-  <si>
-    <t>Degen Gambling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flip a coin. If head, receive 200 Crystals. If tail, lose 400 Crystals </t>
-  </si>
-  <si>
-    <t>Gift</t>
-  </si>
-  <si>
-    <t>Foe receive 50 Crystals</t>
-  </si>
-  <si>
-    <t>Hired Spanker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Until the end of foe's turn, if foe attack the bluffed cell, foe receive 1000 Crystals. </t>
-  </si>
-  <si>
-    <t>Tax Avoidance</t>
-  </si>
-  <si>
-    <t>End this player’s turn without paying tax (the tax penalty still doubles)</t>
-  </si>
-  <si>
-    <t>Compensation</t>
-  </si>
-  <si>
-    <t>This turn, whenever this player attack a Dead End, they receive 20 Crystals</t>
-  </si>
-  <si>
-    <t>Phony Fight</t>
-  </si>
-  <si>
-    <t>-10 DEF to 1 exposed unit on the field until the end of this turn. Foe receive 500 Crystals</t>
-  </si>
-  <si>
-    <t>Facetious</t>
-  </si>
-  <si>
-    <t>Send an emoticon bubble to another player once</t>
-  </si>
-  <si>
-    <t>Telepathy</t>
-  </si>
-  <si>
-    <t>Send a very short message to foe once.</t>
-  </si>
-  <si>
-    <t>Borrow</t>
-  </si>
-  <si>
-    <t>Receive 200 Crystals. At the end of this player’s turn, they lose 300 Crystals</t>
-  </si>
-  <si>
-    <t>Flimsy Axe</t>
-  </si>
-  <si>
-    <t>Flip a coin. If head, +5 ATK to 1 ally unit until this turn ends.</t>
-  </si>
-  <si>
-    <t>Flimsy Shield</t>
-  </si>
-  <si>
-    <t>Flip a coin. If head, +5 DEF to 1 ally unit until this turn ends.</t>
-  </si>
-  <si>
-    <t>All-out Tactics</t>
-  </si>
-  <si>
-    <t>+10 ATK to one ally unit permanently. But its DEF becomes 0 permanently.</t>
-  </si>
-  <si>
-    <t>Fair Fight</t>
-  </si>
-  <si>
-    <t>Both players select 1 of their unit. They gain +10 ATK&amp;DEF permanently</t>
-  </si>
-  <si>
-    <t>Greater Telepathy</t>
-  </si>
-  <si>
-    <t>Send a medium length message to foe once.</t>
-  </si>
-  <si>
-    <t>Loan</t>
-  </si>
-  <si>
-    <t>Receive 600 Crystals. At this player’s next turn’s end: lose 800 Crystals</t>
-  </si>
-  <si>
-    <t>Old Spear</t>
-  </si>
-  <si>
-    <t>+5 ATK to 1 ally unit until this turn ends.</t>
-  </si>
-  <si>
-    <t>Old Shield</t>
-  </si>
-  <si>
-    <t>+5 DEF to 1 ally unit until this turn ends.</t>
-  </si>
-  <si>
-    <t>Provoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At the end of foe’s turn, foe must attack the selected cell first. </t>
-  </si>
-  <si>
-    <t>Supreme Telepathy</t>
-  </si>
-  <si>
-    <t>Send a long message to foe once.</t>
-  </si>
-  <si>
-    <t>Mortgage</t>
-  </si>
-  <si>
-    <t>Receive 1200 Crystals. At the end of this player’s turn, lose 1500 Crystals</t>
-  </si>
-  <si>
-    <t>Big Finger</t>
-  </si>
-  <si>
-    <t>Send a very big improper emoticon bubble to foe</t>
-  </si>
-  <si>
-    <t>Big Love</t>
-  </si>
-  <si>
-    <t>Send a very big lovely emoticon bubble to foe</t>
-  </si>
-  <si>
-    <t>Pretify</t>
-  </si>
-  <si>
-    <t>+20 DEF permanently to ally unit or foe’s exposed unit. But its ATK becomes 0 permanently.</t>
-  </si>
-  <si>
-    <t>Stone Skin</t>
-  </si>
-  <si>
-    <t>+20 DEF permanently to ally unit. But its ATK becomes 0 permanently.</t>
-  </si>
-  <si>
-    <t>Battle Royale</t>
-  </si>
-  <si>
-    <t>Both players select 1 of their unit. They gain +30 ATK&amp;DEF</t>
-  </si>
-  <si>
-    <t>Guerrilla Tactics</t>
-  </si>
-  <si>
-    <t>Until the end of foe's turn, If they attack a non-unit card, flip a coin. Head: destroy the attacking unit.</t>
-  </si>
-  <si>
-    <t>Toll</t>
-  </si>
-  <si>
-    <t>Until the end of foe's turn, they have to pay 500 Crystal tax to perform an attack.</t>
-  </si>
-  <si>
-    <t>Skull Amulet</t>
-  </si>
-  <si>
-    <t>+5 ATK permanently to 1 Chaos card.</t>
-  </si>
-  <si>
-    <t>Might</t>
-  </si>
-  <si>
-    <t>+10 ATK to 1 ally Anima card until this turn ends</t>
-  </si>
-  <si>
-    <t>Arcane Knowledge</t>
-  </si>
-  <si>
-    <t>+5 ATK&amp;DEF to 1 ally Arcane unit until the end of foe’s turn.</t>
-  </si>
-  <si>
-    <t>Forest Fire</t>
-  </si>
-  <si>
-    <t>Destroy all Nature cards on foe's side. Discard all of this player’s Tech cards.</t>
-  </si>
-  <si>
-    <t>Black Hole</t>
-  </si>
-  <si>
-    <t>Destroy all Cosmo cards on foe's side. Discard all of this player’s Tech cards.</t>
-  </si>
-  <si>
-    <t>Holy Arrival</t>
-  </si>
-  <si>
-    <t>Destroy all Chaos cards on foe's side. Discard all of this player’s Tech cards.</t>
-  </si>
-  <si>
-    <t>Corrupted Heaven</t>
-  </si>
-  <si>
-    <t>Destroy all Divine cards on foe's side. Discard all of this player’s Tech cards.</t>
-  </si>
-  <si>
-    <t>Earthquake</t>
-  </si>
-  <si>
-    <t>Destroy all Anima cards on foe's side. Discard all of this player’s Tech cards.</t>
-  </si>
-  <si>
-    <t>Lab Destruction</t>
-  </si>
-  <si>
-    <t>Destroy all Bio cards on foe's side. Discard all of this player’s Tech cards.</t>
-  </si>
-  <si>
-    <t>Anti-magic Field</t>
-  </si>
-  <si>
-    <t>Destroy all Arcane cards on foe's side. Discard all of this player’s Tech cards.</t>
-  </si>
-  <si>
-    <t>Air Shower</t>
-  </si>
-  <si>
-    <t>Clear all flags on the field</t>
-  </si>
-  <si>
-    <t>Mining Tax</t>
-  </si>
-  <si>
-    <t>Until the end of foe’s turn, if any player attacks a Dead End, that player loses 200 Crystals</t>
-  </si>
-  <si>
-    <t>Ouija</t>
-  </si>
-  <si>
-    <t>Reveal foe’s cells up to number of this player’s unit in the void.</t>
-  </si>
-  <si>
-    <t>Deep Mine</t>
-  </si>
-  <si>
-    <t>Flip a coin. If head, reveal 2 square on foe's side of the field</t>
-  </si>
-  <si>
-    <t>Gold Panning</t>
-  </si>
-  <si>
-    <t>Flip a coin. If head, reveal 1 square on foe's side of the field</t>
-  </si>
-  <si>
-    <t>Flashlight</t>
-  </si>
-  <si>
-    <t>Reveal 1 column on foe’s side. Cannot perform attack this turn. Cannot use this card if already attacked this turn.</t>
-  </si>
-  <si>
-    <t>Lantern</t>
-  </si>
-  <si>
-    <t>Reveal 2 adjacent cells on foe's side of the field.</t>
-  </si>
-  <si>
-    <t>GPS Tracker</t>
-  </si>
-  <si>
-    <t>Reveal 2 adjacent cells next to exposed unit on foe's side of the field.</t>
-  </si>
-  <si>
-    <t>Blessing</t>
-  </si>
-  <si>
-    <t>Clear all flags from 1 ally unit</t>
-  </si>
-  <si>
-    <t>Bright Sun</t>
-  </si>
-  <si>
-    <t>Clear all flags from all cards on the field</t>
-  </si>
-  <si>
-    <t>Rugpull</t>
-  </si>
-  <si>
-    <t>Both players lose 2000 Crystals. Discard all tech in this player’s hands.</t>
-  </si>
-  <si>
-    <t>Crack the Whip</t>
-  </si>
-  <si>
-    <t>Once, this player’s attacking unit can attack twice. But it cannot attack again until the end of this player’s next turn.</t>
-  </si>
-  <si>
-    <t>Need Revise</t>
-  </si>
-  <si>
-    <t>Full open fire</t>
-  </si>
-  <si>
-    <t>Both players gain 2 additional attack for one of owner's turn.</t>
-  </si>
-  <si>
-    <t>Service Charge</t>
-  </si>
-  <si>
-    <t>Until the end of foe's turn. Foe have to pay 50 Crystal tax to perform an attack.</t>
-  </si>
-  <si>
-    <t>Lazy Scout</t>
-  </si>
-  <si>
-    <t>Reveal 1 foe’s cell. This player cannot perform any attack. Cannot use this card if already attacked.</t>
-  </si>
-  <si>
-    <t>Last Gambit</t>
-  </si>
-  <si>
-    <t>If this player has 5 or less cards on the field, destroy 1 foe’s card.</t>
-  </si>
-  <si>
-    <t>Trash Penalty</t>
-  </si>
-  <si>
-    <t>Foe chooses either clearing all of their bluffs or take 500 damage</t>
-  </si>
-  <si>
-    <t>Silence Zone</t>
-  </si>
-  <si>
-    <t>Clear all bluffs from both players. No one can use bluff ever again during this duel.</t>
-  </si>
-  <si>
-    <t>Big Mouth</t>
-  </si>
-  <si>
-    <t>Select 1 cell. Bluff on that cell becomes large permanently</t>
-  </si>
-  <si>
-    <t>Bare Fist Fight</t>
-  </si>
-  <si>
-    <t>Both players select and discard 1 tech card from their hand.</t>
-  </si>
-  <si>
-    <t>Mine Detector</t>
-  </si>
-  <si>
-    <t>Reveal 1 card on foe's side. If it’s a trap, destroy it and gain 200 Crystals</t>
-  </si>
-  <si>
-    <t>Natural Healing</t>
-  </si>
-  <si>
-    <t>If all exposed ally units are Nature card, gain 40 Crystals for each of them</t>
-  </si>
-  <si>
-    <t>Third Eye</t>
-  </si>
-  <si>
-    <t>If this is the last tech card on this player’s hand, reveal 3 cards on foe's side</t>
-  </si>
-  <si>
-    <t>Punching Bag</t>
-  </si>
-  <si>
-    <t>1 ally unit’s ATK&amp;DEF becomes 0 permanently. It cannot be destroyed until the end of foe’s turn.</t>
-  </si>
-  <si>
-    <t>Scattered Shot</t>
-  </si>
-  <si>
-    <t>Flip 3 coins. Destroy foe’s exposed unit equal to number of heads. foe pays no cost.</t>
-  </si>
-  <si>
-    <t>Spotlight</t>
-  </si>
-  <si>
-    <t>Flip 5 coins. Reveal foe’s cell equal to number of heads</t>
-  </si>
-  <si>
-    <t>Tight Door</t>
-  </si>
-  <si>
-    <t>Next turn, foe can attack only once</t>
-  </si>
-  <si>
-    <t>Katana Strike</t>
-  </si>
-  <si>
-    <t>Select 1 exposed foe’s card. Destroy other exposed cards on that same columns as the selected cell. Foe don’t pay Crystal cost.</t>
-  </si>
-  <si>
-    <t>Mining Season</t>
-  </si>
-  <si>
-    <t>Until foe’s turn ends, both players can only target face-down card</t>
-  </si>
-  <si>
-    <t>Throne Duel</t>
-  </si>
-  <si>
-    <t>Until foe’s turn ends, both players can only attack with unit with 800 or more cost. Cannot use if already attacked.</t>
-  </si>
-  <si>
-    <t>Joint Maneuver</t>
-  </si>
-  <si>
-    <t>Until foe’s turn ends, both players can only attack with unit with 600 or less cost. Cannot use if already attacked.</t>
-  </si>
-  <si>
-    <t>Pillow Fight</t>
-  </si>
-  <si>
-    <t>Until foe’s turn ends, both players can only attack with unit with 300 or less cost. Cannot use if already attacked.</t>
-  </si>
-  <si>
-    <t>Army Reformation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swap or relocate 1 unit to any cell. </t>
-  </si>
-  <si>
-    <t>Institutionalization</t>
-  </si>
-  <si>
-    <t>Target 1 foe’s unit. Its ability becomes None until foe’s next turn ends</t>
+    <t>Select 1 card with Venom Flag. Double its cost, then destroy it.</t>
   </si>
   <si>
     <t>Expected</t>
@@ -6314,15 +6335,15 @@
         <v>28</v>
       </c>
       <c r="N2" t="s" s="5">
-        <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(L3:L568,"Yes")</f>
+        <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N568,"Yes")</f>
         <v>29</v>
       </c>
       <c r="O2" t="s" s="5">
-        <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(M3:M568,"Yes")</f>
+        <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O568,"Yes")</f>
         <v>30</v>
       </c>
       <c r="P2" t="s" s="5">
-        <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(N3:N568,"Yes")</f>
+        <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P568,"Yes")</f>
         <v>31</v>
       </c>
     </row>
@@ -7257,9 +7278,7 @@
       </c>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
-      <c r="O24" t="s" s="19">
-        <v>35</v>
-      </c>
+      <c r="O24" s="19"/>
       <c r="P24" t="s" s="19">
         <v>35</v>
       </c>
@@ -8885,7 +8904,9 @@
         <v>39</v>
       </c>
       <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
+      <c r="J64" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K64" s="18">
         <f>(D64*6)+(E64*4)</f>
         <v>250</v>
@@ -8965,7 +8986,9 @@
         <v>39</v>
       </c>
       <c r="I66" s="12"/>
-      <c r="J66" s="12"/>
+      <c r="J66" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K66" s="18">
         <f>(D66*6)+(E66*4)</f>
         <v>890</v>
@@ -9045,7 +9068,9 @@
         <v>39</v>
       </c>
       <c r="I68" s="12"/>
-      <c r="J68" s="12"/>
+      <c r="J68" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K68" s="18">
         <f>(D68*6)+(E68*4)</f>
         <v>150</v>
@@ -9254,7 +9279,9 @@
         <v>158</v>
       </c>
       <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
+      <c r="J73" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K73" s="18">
         <f>(D73*6)+(E73*4)</f>
         <v>140</v>
@@ -9291,7 +9318,9 @@
         <v>39</v>
       </c>
       <c r="I74" s="12"/>
-      <c r="J74" s="12"/>
+      <c r="J74" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K74" s="18">
         <f>(D74*6)+(E74*4)</f>
         <v>180</v>
@@ -9328,7 +9357,9 @@
         <v>161</v>
       </c>
       <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
+      <c r="J75" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K75" s="18">
         <f>(D75*6)+(E75*4)</f>
         <v>100</v>
@@ -9408,7 +9439,9 @@
         <v>164</v>
       </c>
       <c r="I77" s="12"/>
-      <c r="J77" s="12"/>
+      <c r="J77" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K77" s="18">
         <f>(D77*6)+(E77*4)</f>
         <v>210</v>
@@ -9746,7 +9779,9 @@
         <v>176</v>
       </c>
       <c r="I85" s="12"/>
-      <c r="J85" s="12"/>
+      <c r="J85" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K85" s="18">
         <f>(D85*6)+(E85*4)</f>
         <v>200</v>
@@ -9826,7 +9861,9 @@
         <v>180</v>
       </c>
       <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
+      <c r="J87" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K87" s="18">
         <f>(D87*6)+(E87*4)</f>
         <v>160</v>
@@ -9863,7 +9900,9 @@
         <v>182</v>
       </c>
       <c r="I88" s="12"/>
-      <c r="J88" s="12"/>
+      <c r="J88" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K88" s="18">
         <f>(D88*6)+(E88*4)</f>
         <v>200</v>
@@ -9900,7 +9939,9 @@
         <v>182</v>
       </c>
       <c r="I89" s="12"/>
-      <c r="J89" s="12"/>
+      <c r="J89" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K89" s="18">
         <f>(D89*6)+(E89*4)</f>
         <v>400</v>
@@ -9937,7 +9978,9 @@
         <v>185</v>
       </c>
       <c r="I90" s="12"/>
-      <c r="J90" s="12"/>
+      <c r="J90" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K90" s="18">
         <f>(D90*6)+(E90*4)</f>
         <v>810</v>
@@ -10017,7 +10060,9 @@
         <v>189</v>
       </c>
       <c r="I92" s="12"/>
-      <c r="J92" s="12"/>
+      <c r="J92" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K92" s="18">
         <f>(D92*6)+(E92*4)</f>
         <v>360</v>
@@ -10097,7 +10142,9 @@
         <v>192</v>
       </c>
       <c r="I94" s="12"/>
-      <c r="J94" s="12"/>
+      <c r="J94" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K94" s="18">
         <f>(D94*6)+(E94*4)</f>
         <v>350</v>
@@ -10134,7 +10181,9 @@
         <v>194</v>
       </c>
       <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
+      <c r="J95" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K95" s="18">
         <f>(D95*6)+(E95*4)</f>
         <v>270</v>
@@ -10300,7 +10349,9 @@
         <v>200</v>
       </c>
       <c r="I99" s="12"/>
-      <c r="J99" s="12"/>
+      <c r="J99" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K99" s="18">
         <f>(D99*6)+(E99*4)</f>
         <v>510</v>
@@ -10337,7 +10388,9 @@
         <v>202</v>
       </c>
       <c r="I100" s="12"/>
-      <c r="J100" s="12"/>
+      <c r="J100" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K100" s="18">
         <f>(D100*6)+(E100*4)</f>
         <v>430</v>
@@ -10374,7 +10427,9 @@
         <v>204</v>
       </c>
       <c r="I101" s="12"/>
-      <c r="J101" s="12"/>
+      <c r="J101" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K101" s="18">
         <f>(D101*6)+(E101*4)</f>
         <v>370</v>
@@ -10411,7 +10466,9 @@
         <v>206</v>
       </c>
       <c r="I102" s="12"/>
-      <c r="J102" s="12"/>
+      <c r="J102" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K102" s="18">
         <f>(D102*6)+(E102*4)</f>
         <v>400</v>
@@ -10448,7 +10505,9 @@
         <v>208</v>
       </c>
       <c r="I103" s="12"/>
-      <c r="J103" s="12"/>
+      <c r="J103" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K103" s="18">
         <f>(D103*6)+(E103*4)</f>
         <v>570</v>
@@ -12644,9 +12703,7 @@
         <v>35</v>
       </c>
       <c r="O158" s="12"/>
-      <c r="P158" t="s" s="19">
-        <v>35</v>
-      </c>
+      <c r="P158" s="19"/>
     </row>
     <row r="159" ht="32.05" customHeight="1">
       <c r="A159" t="s" s="10">
@@ -13593,7 +13650,7 @@
         <v>33</v>
       </c>
       <c r="C184" s="18">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="D184" s="18">
         <v>15</v>
@@ -13611,15 +13668,21 @@
         <v>346</v>
       </c>
       <c r="I184" s="12"/>
-      <c r="J184" s="12"/>
+      <c r="J184" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K184" s="18">
         <f>(D184*6)+(E184*4)</f>
         <v>170</v>
       </c>
-      <c r="L184" s="12"/>
+      <c r="L184" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M184" s="12"/>
       <c r="N184" s="12"/>
-      <c r="O184" s="12"/>
+      <c r="O184" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="P184" s="12"/>
     </row>
     <row r="185" ht="20.05" customHeight="1">
@@ -14025,9 +14088,7 @@
       <c r="N194" t="s" s="19">
         <v>35</v>
       </c>
-      <c r="O194" t="s" s="19">
-        <v>35</v>
-      </c>
+      <c r="O194" s="19"/>
       <c r="P194" s="12"/>
     </row>
     <row r="195" ht="44.05" customHeight="1">
@@ -18079,9 +18140,7 @@
       <c r="O303" t="s" s="19">
         <v>35</v>
       </c>
-      <c r="P303" t="s" s="19">
-        <v>35</v>
-      </c>
+      <c r="P303" s="19"/>
     </row>
     <row r="304" ht="32.05" customHeight="1">
       <c r="A304" t="s" s="10">
@@ -22235,55 +22294,95 @@
       <c r="O437" s="12"/>
       <c r="P437" s="12"/>
     </row>
-    <row r="438" ht="20.05" customHeight="1">
-      <c r="A438" s="13"/>
+    <row r="438" ht="38.7" customHeight="1">
+      <c r="A438" t="s" s="10">
+        <v>656</v>
+      </c>
       <c r="B438" t="s" s="11">
         <v>33</v>
       </c>
-      <c r="C438" s="12"/>
-      <c r="D438" s="12"/>
-      <c r="E438" s="12"/>
-      <c r="F438" s="12"/>
-      <c r="G438" s="12"/>
-      <c r="H438" s="12"/>
+      <c r="C438" s="18">
+        <v>550</v>
+      </c>
+      <c r="D438" s="18">
+        <v>45</v>
+      </c>
+      <c r="E438" s="18">
+        <v>75</v>
+      </c>
+      <c r="F438" t="s" s="19">
+        <v>9</v>
+      </c>
+      <c r="G438" s="18">
+        <v>4</v>
+      </c>
+      <c r="H438" t="s" s="19">
+        <v>657</v>
+      </c>
       <c r="I438" s="12"/>
-      <c r="J438" s="12"/>
+      <c r="J438" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K438" s="18">
         <f>(D438*6)+(E438*4)</f>
-        <v>0</v>
-      </c>
-      <c r="L438" s="12"/>
+        <v>570</v>
+      </c>
+      <c r="L438" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M438" s="12"/>
       <c r="N438" s="12"/>
       <c r="O438" s="12"/>
-      <c r="P438" s="12"/>
-    </row>
-    <row r="439" ht="20.05" customHeight="1">
-      <c r="A439" s="13"/>
+      <c r="P438" t="s" s="19">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="439" ht="38.7" customHeight="1">
+      <c r="A439" t="s" s="10">
+        <v>658</v>
+      </c>
       <c r="B439" t="s" s="11">
         <v>33</v>
       </c>
-      <c r="C439" s="12"/>
-      <c r="D439" s="12"/>
-      <c r="E439" s="12"/>
-      <c r="F439" s="12"/>
-      <c r="G439" s="12"/>
-      <c r="H439" s="12"/>
+      <c r="C439" s="18">
+        <v>900</v>
+      </c>
+      <c r="D439" s="18">
+        <v>40</v>
+      </c>
+      <c r="E439" s="18">
+        <v>25</v>
+      </c>
+      <c r="F439" t="s" s="19">
+        <v>9</v>
+      </c>
+      <c r="G439" s="18">
+        <v>3</v>
+      </c>
+      <c r="H439" t="s" s="19">
+        <v>659</v>
+      </c>
       <c r="I439" s="12"/>
-      <c r="J439" s="12"/>
+      <c r="J439" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K439" s="18">
         <f>(D439*6)+(E439*4)</f>
-        <v>0</v>
-      </c>
-      <c r="L439" s="12"/>
+        <v>340</v>
+      </c>
+      <c r="L439" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M439" s="12"/>
       <c r="N439" s="12"/>
-      <c r="O439" s="12"/>
+      <c r="O439" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="P439" s="12"/>
     </row>
     <row r="440" ht="44.05" customHeight="1">
       <c r="A440" t="s" s="10">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B440" t="s" s="11">
         <v>33</v>
@@ -22304,7 +22403,7 @@
         <v>5</v>
       </c>
       <c r="H440" t="s" s="19">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="I440" s="12"/>
       <c r="J440" s="12"/>
@@ -22317,7 +22416,7 @@
     </row>
     <row r="441" ht="20.05" customHeight="1">
       <c r="A441" t="s" s="10">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B441" t="s" s="11">
         <v>5</v>
@@ -24696,19 +24795,19 @@
         <v>22</v>
       </c>
       <c r="H2" t="s" s="5">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="I2" t="s" s="5">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="J2" t="s" s="5">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="K2" t="s" s="5">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="L2" t="s" s="5">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="M2" t="s" s="5">
         <v>25</v>
@@ -24722,10 +24821,10 @@
     </row>
     <row r="3" ht="68.25" customHeight="1">
       <c r="A3" t="s" s="7">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="16">
@@ -24745,13 +24844,13 @@
         <v>39</v>
       </c>
       <c r="J3" t="s" s="17">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K3" t="s" s="17">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="L3" t="s" s="17">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="M3" t="s" s="17">
         <v>35</v>
@@ -24763,10 +24862,10 @@
     </row>
     <row r="4" ht="68.05" customHeight="1">
       <c r="A4" t="s" s="10">
+        <v>673</v>
+      </c>
+      <c r="B4" t="s" s="11">
         <v>669</v>
-      </c>
-      <c r="B4" t="s" s="11">
-        <v>665</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="18">
@@ -24780,19 +24879,19 @@
       </c>
       <c r="G4" s="12"/>
       <c r="H4" t="s" s="19">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="I4" t="s" s="19">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="J4" t="s" s="19">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="K4" t="s" s="19">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="L4" t="s" s="19">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="M4" t="s" s="19">
         <v>35</v>
@@ -24804,10 +24903,10 @@
     </row>
     <row r="5" ht="68.05" customHeight="1">
       <c r="A5" t="s" s="10">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="18">
@@ -24827,13 +24926,13 @@
         <v>39</v>
       </c>
       <c r="J5" t="s" s="19">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="K5" t="s" s="19">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L5" t="s" s="19">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="M5" t="s" s="19">
         <v>35</v>
@@ -24845,10 +24944,10 @@
     </row>
     <row r="6" ht="68.05" customHeight="1">
       <c r="A6" t="s" s="10">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="18">
@@ -24868,13 +24967,13 @@
         <v>39</v>
       </c>
       <c r="J6" t="s" s="19">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K6" t="s" s="19">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L6" t="s" s="19">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="M6" t="s" s="19">
         <v>35</v>
@@ -24886,10 +24985,10 @@
     </row>
     <row r="7" ht="68.05" customHeight="1">
       <c r="A7" t="s" s="10">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="18">
@@ -24903,19 +25002,19 @@
       </c>
       <c r="G7" s="12"/>
       <c r="H7" t="s" s="19">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="I7" t="s" s="19">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="J7" t="s" s="19">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="K7" t="s" s="19">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="L7" t="s" s="19">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="M7" t="s" s="19">
         <v>35</v>
@@ -24927,10 +25026,10 @@
     </row>
     <row r="8" ht="68.05" customHeight="1">
       <c r="A8" t="s" s="10">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="18">
@@ -24950,13 +25049,13 @@
         <v>39</v>
       </c>
       <c r="J8" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K8" t="s" s="19">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="L8" t="s" s="19">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="M8" t="s" s="19">
         <v>35</v>
@@ -24968,10 +25067,10 @@
     </row>
     <row r="9" ht="68.05" customHeight="1">
       <c r="A9" t="s" s="10">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="18">
@@ -24985,19 +25084,19 @@
       </c>
       <c r="G9" s="12"/>
       <c r="H9" t="s" s="19">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="I9" t="s" s="19">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="J9" t="s" s="19">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="K9" t="s" s="19">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="L9" t="s" s="19">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M9" t="s" s="19">
         <v>35</v>
@@ -25009,10 +25108,10 @@
     </row>
     <row r="10" ht="68.05" customHeight="1">
       <c r="A10" t="s" s="10">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="18">
@@ -25026,19 +25125,19 @@
       </c>
       <c r="G10" s="12"/>
       <c r="H10" t="s" s="19">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="I10" t="s" s="19">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="J10" t="s" s="19">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="K10" t="s" s="19">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="L10" t="s" s="19">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="M10" t="s" s="19">
         <v>35</v>
@@ -25050,10 +25149,10 @@
     </row>
     <row r="11" ht="68.05" customHeight="1">
       <c r="A11" t="s" s="10">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="18">
@@ -25067,19 +25166,19 @@
       </c>
       <c r="G11" s="12"/>
       <c r="H11" t="s" s="19">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I11" t="s" s="19">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="J11" t="s" s="19">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="K11" t="s" s="19">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="L11" t="s" s="19">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="M11" t="s" s="19">
         <v>35</v>
@@ -25091,10 +25190,10 @@
     </row>
     <row r="12" ht="68.05" customHeight="1">
       <c r="A12" t="s" s="10">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="18">
@@ -25108,19 +25207,19 @@
       </c>
       <c r="G12" s="12"/>
       <c r="H12" t="s" s="19">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="I12" t="s" s="19">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="J12" t="s" s="19">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="K12" t="s" s="19">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="L12" t="s" s="19">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="M12" t="s" s="19">
         <v>35</v>
@@ -25132,10 +25231,10 @@
     </row>
     <row r="13" ht="68.05" customHeight="1">
       <c r="A13" t="s" s="10">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B13" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="18">
@@ -25149,19 +25248,19 @@
       </c>
       <c r="G13" s="12"/>
       <c r="H13" t="s" s="19">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="I13" t="s" s="19">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="J13" t="s" s="19">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="K13" t="s" s="19">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="L13" t="s" s="19">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="M13" t="s" s="19">
         <v>35</v>
@@ -25173,10 +25272,10 @@
     </row>
     <row r="14" ht="68.05" customHeight="1">
       <c r="A14" t="s" s="10">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B14" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="18">
@@ -25190,19 +25289,19 @@
       </c>
       <c r="G14" s="12"/>
       <c r="H14" t="s" s="19">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="I14" t="s" s="19">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="J14" t="s" s="19">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="K14" t="s" s="19">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="L14" t="s" s="19">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="M14" t="s" s="19">
         <v>35</v>
@@ -25214,10 +25313,10 @@
     </row>
     <row r="15" ht="68.05" customHeight="1">
       <c r="A15" t="s" s="10">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B15" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="18">
@@ -25237,13 +25336,13 @@
         <v>39</v>
       </c>
       <c r="J15" t="s" s="19">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="K15" t="s" s="19">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="L15" t="s" s="19">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="M15" t="s" s="19">
         <v>35</v>
@@ -25255,10 +25354,10 @@
     </row>
     <row r="16" ht="92.05" customHeight="1">
       <c r="A16" t="s" s="10">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B16" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="18">
@@ -25272,19 +25371,19 @@
       </c>
       <c r="G16" s="12"/>
       <c r="H16" t="s" s="19">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="I16" t="s" s="19">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="J16" t="s" s="19">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K16" t="s" s="19">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="L16" t="s" s="19">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="M16" t="s" s="19">
         <v>35</v>
@@ -25296,10 +25395,10 @@
     </row>
     <row r="17" ht="68.05" customHeight="1">
       <c r="A17" t="s" s="10">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B17" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="18">
@@ -25313,19 +25412,19 @@
       </c>
       <c r="G17" s="12"/>
       <c r="H17" t="s" s="19">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="I17" t="s" s="19">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="J17" t="s" s="19">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="K17" t="s" s="19">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="L17" t="s" s="19">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="M17" t="s" s="19">
         <v>35</v>
@@ -25337,10 +25436,10 @@
     </row>
     <row r="18" ht="68.05" customHeight="1">
       <c r="A18" t="s" s="10">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B18" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="18">
@@ -25360,13 +25459,13 @@
         <v>39</v>
       </c>
       <c r="J18" t="s" s="19">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="K18" t="s" s="19">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="L18" t="s" s="19">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="M18" t="s" s="19">
         <v>35</v>
@@ -25378,10 +25477,10 @@
     </row>
     <row r="19" ht="68.05" customHeight="1">
       <c r="A19" t="s" s="10">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B19" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="18">
@@ -25395,19 +25494,19 @@
       </c>
       <c r="G19" s="12"/>
       <c r="H19" t="s" s="19">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="I19" t="s" s="19">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="J19" t="s" s="19">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="K19" t="s" s="19">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="L19" t="s" s="19">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="M19" t="s" s="19">
         <v>35</v>
@@ -25419,10 +25518,10 @@
     </row>
     <row r="20" ht="68.05" customHeight="1">
       <c r="A20" t="s" s="10">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B20" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="18">
@@ -25442,13 +25541,13 @@
         <v>39</v>
       </c>
       <c r="J20" t="s" s="19">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="K20" t="s" s="19">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="L20" t="s" s="19">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="M20" t="s" s="19">
         <v>35</v>
@@ -25460,10 +25559,10 @@
     </row>
     <row r="21" ht="68.05" customHeight="1">
       <c r="A21" t="s" s="10">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B21" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="18">
@@ -25483,13 +25582,13 @@
         <v>39</v>
       </c>
       <c r="J21" t="s" s="19">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="K21" t="s" s="19">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="L21" t="s" s="19">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="M21" t="s" s="19">
         <v>35</v>
@@ -25501,10 +25600,10 @@
     </row>
     <row r="22" ht="68.05" customHeight="1">
       <c r="A22" t="s" s="10">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B22" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="18">
@@ -25518,19 +25617,19 @@
       </c>
       <c r="G22" s="12"/>
       <c r="H22" t="s" s="19">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="I22" t="s" s="19">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="J22" t="s" s="19">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="K22" t="s" s="19">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="L22" t="s" s="19">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="M22" t="s" s="19">
         <v>35</v>
@@ -25542,10 +25641,10 @@
     </row>
     <row r="23" ht="68.05" customHeight="1">
       <c r="A23" t="s" s="10">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="18">
@@ -25559,19 +25658,19 @@
       </c>
       <c r="G23" s="12"/>
       <c r="H23" t="s" s="19">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="I23" t="s" s="19">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="J23" t="s" s="19">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="K23" t="s" s="19">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="L23" t="s" s="19">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="M23" t="s" s="19">
         <v>35</v>
@@ -25583,10 +25682,10 @@
     </row>
     <row r="24" ht="68.05" customHeight="1">
       <c r="A24" t="s" s="10">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B24" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="18">
@@ -25606,13 +25705,13 @@
         <v>39</v>
       </c>
       <c r="J24" t="s" s="19">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="K24" t="s" s="19">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L24" t="s" s="19">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="M24" t="s" s="19">
         <v>35</v>
@@ -25624,10 +25723,10 @@
     </row>
     <row r="25" ht="68.05" customHeight="1">
       <c r="A25" t="s" s="10">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B25" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="18">
@@ -25641,19 +25740,19 @@
       </c>
       <c r="G25" s="12"/>
       <c r="H25" t="s" s="19">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="I25" t="s" s="19">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="J25" t="s" s="19">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K25" t="s" s="19">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="L25" t="s" s="19">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="M25" t="s" s="19">
         <v>35</v>
@@ -25665,10 +25764,10 @@
     </row>
     <row r="26" ht="68.05" customHeight="1">
       <c r="A26" t="s" s="10">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B26" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="18">
@@ -25688,13 +25787,13 @@
         <v>39</v>
       </c>
       <c r="J26" t="s" s="19">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="K26" t="s" s="19">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="L26" t="s" s="19">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="M26" t="s" s="19">
         <v>35</v>
@@ -25706,10 +25805,10 @@
     </row>
     <row r="27" ht="80.05" customHeight="1">
       <c r="A27" t="s" s="10">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B27" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="18">
@@ -25723,19 +25822,19 @@
       </c>
       <c r="G27" s="12"/>
       <c r="H27" t="s" s="19">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="I27" t="s" s="19">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="J27" t="s" s="19">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="K27" t="s" s="19">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="L27" t="s" s="19">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="M27" t="s" s="19">
         <v>35</v>
@@ -25747,10 +25846,10 @@
     </row>
     <row r="28" ht="68.05" customHeight="1">
       <c r="A28" t="s" s="10">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B28" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="18">
@@ -25764,19 +25863,19 @@
       </c>
       <c r="G28" s="12"/>
       <c r="H28" t="s" s="19">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="I28" t="s" s="19">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="J28" t="s" s="19">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="K28" t="s" s="19">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="L28" t="s" s="19">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="M28" t="s" s="19">
         <v>35</v>
@@ -25788,10 +25887,10 @@
     </row>
     <row r="29" ht="80.05" customHeight="1">
       <c r="A29" t="s" s="10">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B29" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="18">
@@ -25811,13 +25910,13 @@
         <v>39</v>
       </c>
       <c r="J29" t="s" s="19">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="K29" t="s" s="19">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="L29" t="s" s="19">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="M29" t="s" s="19">
         <v>35</v>
@@ -25829,10 +25928,10 @@
     </row>
     <row r="30" ht="80.05" customHeight="1">
       <c r="A30" t="s" s="10">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B30" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="18">
@@ -25846,19 +25945,19 @@
       </c>
       <c r="G30" s="12"/>
       <c r="H30" t="s" s="19">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="I30" t="s" s="19">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="J30" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K30" t="s" s="19">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="L30" t="s" s="19">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="M30" t="s" s="19">
         <v>35</v>
@@ -25870,10 +25969,10 @@
     </row>
     <row r="31" ht="80.05" customHeight="1">
       <c r="A31" t="s" s="10">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B31" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="18">
@@ -25887,19 +25986,19 @@
       </c>
       <c r="G31" s="12"/>
       <c r="H31" t="s" s="19">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="I31" t="s" s="19">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="J31" t="s" s="19">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="K31" t="s" s="19">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="L31" t="s" s="19">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="M31" t="s" s="19">
         <v>35</v>
@@ -25911,10 +26010,10 @@
     </row>
     <row r="32" ht="80.05" customHeight="1">
       <c r="A32" t="s" s="10">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B32" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="18">
@@ -25928,19 +26027,19 @@
       </c>
       <c r="G32" s="12"/>
       <c r="H32" t="s" s="19">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="I32" t="s" s="19">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="J32" t="s" s="19">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="K32" t="s" s="19">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="L32" t="s" s="19">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="M32" t="s" s="19">
         <v>35</v>
@@ -25952,10 +26051,10 @@
     </row>
     <row r="33" ht="80.05" customHeight="1">
       <c r="A33" t="s" s="10">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="B33" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="18">
@@ -25969,19 +26068,19 @@
       </c>
       <c r="G33" s="12"/>
       <c r="H33" t="s" s="19">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="I33" t="s" s="19">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="J33" t="s" s="19">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K33" t="s" s="19">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="L33" t="s" s="19">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="M33" t="s" s="19">
         <v>35</v>
@@ -25993,10 +26092,10 @@
     </row>
     <row r="34" ht="80.05" customHeight="1">
       <c r="A34" t="s" s="10">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="B34" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="18">
@@ -26010,19 +26109,19 @@
       </c>
       <c r="G34" s="12"/>
       <c r="H34" t="s" s="19">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="I34" t="s" s="19">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="J34" t="s" s="19">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="K34" t="s" s="19">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="L34" t="s" s="19">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="M34" t="s" s="19">
         <v>35</v>
@@ -26034,10 +26133,10 @@
     </row>
     <row r="35" ht="80.05" customHeight="1">
       <c r="A35" t="s" s="10">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B35" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="18">
@@ -26057,13 +26156,13 @@
         <v>39</v>
       </c>
       <c r="J35" t="s" s="19">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="K35" t="s" s="19">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="L35" t="s" s="19">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="M35" t="s" s="19">
         <v>35</v>
@@ -26075,10 +26174,10 @@
     </row>
     <row r="36" ht="80.05" customHeight="1">
       <c r="A36" t="s" s="10">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B36" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="18">
@@ -26092,19 +26191,19 @@
       </c>
       <c r="G36" s="12"/>
       <c r="H36" t="s" s="19">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="I36" t="s" s="19">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="J36" t="s" s="19">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K36" t="s" s="19">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="L36" t="s" s="19">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="M36" t="s" s="19">
         <v>35</v>
@@ -26116,10 +26215,10 @@
     </row>
     <row r="37" ht="68.05" customHeight="1">
       <c r="A37" t="s" s="10">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B37" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="18">
@@ -26133,19 +26232,19 @@
       </c>
       <c r="G37" s="12"/>
       <c r="H37" t="s" s="19">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I37" t="s" s="19">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="J37" t="s" s="19">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="K37" t="s" s="19">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="L37" t="s" s="19">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="M37" t="s" s="19">
         <v>35</v>
@@ -26157,10 +26256,10 @@
     </row>
     <row r="38" ht="80.05" customHeight="1">
       <c r="A38" t="s" s="10">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="B38" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C38" s="12"/>
       <c r="D38" s="18">
@@ -26174,19 +26273,19 @@
       </c>
       <c r="G38" s="12"/>
       <c r="H38" t="s" s="19">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="I38" t="s" s="19">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="J38" t="s" s="19">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K38" t="s" s="19">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="L38" t="s" s="19">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="M38" t="s" s="19">
         <v>35</v>
@@ -26198,10 +26297,10 @@
     </row>
     <row r="39" ht="68.05" customHeight="1">
       <c r="A39" t="s" s="10">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B39" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C39" s="12"/>
       <c r="D39" s="18">
@@ -26215,19 +26314,19 @@
       </c>
       <c r="G39" s="12"/>
       <c r="H39" t="s" s="19">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="I39" t="s" s="19">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="J39" t="s" s="19">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="K39" t="s" s="19">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="L39" t="s" s="19">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="M39" s="12"/>
       <c r="N39" s="12"/>
@@ -26235,10 +26334,10 @@
     </row>
     <row r="40" ht="68.05" customHeight="1">
       <c r="A40" t="s" s="10">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B40" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C40" s="12"/>
       <c r="D40" s="18">
@@ -26252,19 +26351,19 @@
       </c>
       <c r="G40" s="12"/>
       <c r="H40" t="s" s="19">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="I40" t="s" s="19">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="J40" t="s" s="19">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="K40" t="s" s="19">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="L40" t="s" s="19">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="M40" s="12"/>
       <c r="N40" s="12"/>
@@ -26272,10 +26371,10 @@
     </row>
     <row r="41" ht="68.05" customHeight="1">
       <c r="A41" t="s" s="10">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B41" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C41" s="12"/>
       <c r="D41" s="18">
@@ -26289,19 +26388,19 @@
       </c>
       <c r="G41" s="12"/>
       <c r="H41" t="s" s="19">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I41" t="s" s="19">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="J41" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K41" t="s" s="19">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="L41" t="s" s="19">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
@@ -26309,10 +26408,10 @@
     </row>
     <row r="42" ht="68.05" customHeight="1">
       <c r="A42" t="s" s="10">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B42" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C42" s="12"/>
       <c r="D42" s="18">
@@ -26326,19 +26425,19 @@
       </c>
       <c r="G42" s="12"/>
       <c r="H42" t="s" s="19">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="I42" t="s" s="19">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="J42" t="s" s="19">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="K42" t="s" s="19">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="L42" t="s" s="19">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="M42" s="12"/>
       <c r="N42" s="12"/>
@@ -26346,10 +26445,10 @@
     </row>
     <row r="43" ht="68.05" customHeight="1">
       <c r="A43" t="s" s="10">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B43" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C43" s="12"/>
       <c r="D43" s="18">
@@ -26363,19 +26462,19 @@
       </c>
       <c r="G43" s="12"/>
       <c r="H43" t="s" s="19">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="I43" t="s" s="19">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="J43" t="s" s="19">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="K43" t="s" s="19">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="L43" t="s" s="19">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="M43" s="12"/>
       <c r="N43" s="12"/>
@@ -26383,10 +26482,10 @@
     </row>
     <row r="44" ht="68.05" customHeight="1">
       <c r="A44" t="s" s="10">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B44" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C44" s="12"/>
       <c r="D44" s="18">
@@ -26400,19 +26499,19 @@
       </c>
       <c r="G44" s="12"/>
       <c r="H44" t="s" s="19">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="I44" t="s" s="19">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="J44" t="s" s="19">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="K44" t="s" s="19">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="L44" t="s" s="19">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
@@ -26420,10 +26519,10 @@
     </row>
     <row r="45" ht="68.05" customHeight="1">
       <c r="A45" t="s" s="10">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B45" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C45" s="12"/>
       <c r="D45" s="18">
@@ -26437,19 +26536,19 @@
       </c>
       <c r="G45" s="12"/>
       <c r="H45" t="s" s="19">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="I45" t="s" s="19">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="J45" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K45" t="s" s="19">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="L45" t="s" s="19">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="12"/>
@@ -26457,10 +26556,10 @@
     </row>
     <row r="46" ht="68.05" customHeight="1">
       <c r="A46" t="s" s="10">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B46" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C46" s="12"/>
       <c r="D46" s="18">
@@ -26474,19 +26573,19 @@
       </c>
       <c r="G46" s="12"/>
       <c r="H46" t="s" s="19">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="I46" t="s" s="19">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="J46" t="s" s="19">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="K46" t="s" s="19">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="L46" t="s" s="19">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="M46" s="12"/>
       <c r="N46" s="12"/>
@@ -26494,10 +26593,10 @@
     </row>
     <row r="47" ht="68.05" customHeight="1">
       <c r="A47" t="s" s="10">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B47" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C47" s="12"/>
       <c r="D47" s="18">
@@ -26511,19 +26610,19 @@
       </c>
       <c r="G47" s="12"/>
       <c r="H47" t="s" s="19">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="I47" t="s" s="19">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="J47" t="s" s="19">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="K47" t="s" s="19">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="L47" t="s" s="19">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="M47" s="12"/>
       <c r="N47" s="12"/>
@@ -26531,10 +26630,10 @@
     </row>
     <row r="48" ht="68.05" customHeight="1">
       <c r="A48" t="s" s="10">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B48" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C48" s="12"/>
       <c r="D48" s="18">
@@ -26548,19 +26647,19 @@
       </c>
       <c r="G48" s="12"/>
       <c r="H48" t="s" s="19">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="I48" t="s" s="19">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="J48" t="s" s="19">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="K48" t="s" s="19">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="L48" t="s" s="19">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="M48" s="12"/>
       <c r="N48" s="12"/>
@@ -26568,10 +26667,10 @@
     </row>
     <row r="49" ht="68.05" customHeight="1">
       <c r="A49" t="s" s="10">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B49" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C49" s="12"/>
       <c r="D49" s="18">
@@ -26585,19 +26684,19 @@
       </c>
       <c r="G49" s="12"/>
       <c r="H49" t="s" s="19">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="I49" t="s" s="19">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="J49" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K49" t="s" s="19">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="L49" t="s" s="19">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
@@ -26605,10 +26704,10 @@
     </row>
     <row r="50" ht="68.05" customHeight="1">
       <c r="A50" t="s" s="10">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="B50" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C50" s="12"/>
       <c r="D50" s="18">
@@ -26622,19 +26721,19 @@
       </c>
       <c r="G50" s="12"/>
       <c r="H50" t="s" s="19">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="I50" t="s" s="19">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="J50" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K50" t="s" s="19">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="L50" t="s" s="19">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="M50" s="12"/>
       <c r="N50" s="12"/>
@@ -26642,10 +26741,10 @@
     </row>
     <row r="51" ht="68.05" customHeight="1">
       <c r="A51" t="s" s="10">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B51" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C51" s="12"/>
       <c r="D51" s="18">
@@ -26659,19 +26758,19 @@
       </c>
       <c r="G51" s="12"/>
       <c r="H51" t="s" s="19">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="I51" t="s" s="19">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="J51" t="s" s="19">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="K51" t="s" s="19">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="L51" t="s" s="19">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="M51" s="12"/>
       <c r="N51" s="12"/>
@@ -26679,10 +26778,10 @@
     </row>
     <row r="52" ht="68.05" customHeight="1">
       <c r="A52" t="s" s="10">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B52" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C52" s="12"/>
       <c r="D52" s="18">
@@ -26702,13 +26801,13 @@
         <v>39</v>
       </c>
       <c r="J52" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K52" t="s" s="19">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="L52" t="s" s="19">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="M52" s="12"/>
       <c r="N52" s="12"/>
@@ -26716,10 +26815,10 @@
     </row>
     <row r="53" ht="80.05" customHeight="1">
       <c r="A53" t="s" s="10">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="B53" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C53" s="12"/>
       <c r="D53" s="18">
@@ -26733,19 +26832,19 @@
       </c>
       <c r="G53" s="12"/>
       <c r="H53" t="s" s="19">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="I53" t="s" s="19">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="J53" t="s" s="19">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="K53" t="s" s="19">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="L53" t="s" s="19">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="M53" s="12"/>
       <c r="N53" s="12"/>
@@ -26753,10 +26852,10 @@
     </row>
     <row r="54" ht="68.05" customHeight="1">
       <c r="A54" t="s" s="10">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B54" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C54" s="12"/>
       <c r="D54" s="18">
@@ -26770,19 +26869,19 @@
       </c>
       <c r="G54" s="12"/>
       <c r="H54" t="s" s="19">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="I54" t="s" s="19">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="J54" t="s" s="19">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="K54" t="s" s="19">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="L54" t="s" s="19">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="M54" s="12"/>
       <c r="N54" s="12"/>
@@ -26790,10 +26889,10 @@
     </row>
     <row r="55" ht="68.05" customHeight="1">
       <c r="A55" t="s" s="10">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B55" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C55" s="12"/>
       <c r="D55" s="18">
@@ -26807,19 +26906,19 @@
       </c>
       <c r="G55" s="12"/>
       <c r="H55" t="s" s="19">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="I55" t="s" s="19">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="J55" t="s" s="19">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="K55" t="s" s="19">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="L55" t="s" s="19">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="M55" s="12"/>
       <c r="N55" s="12"/>
@@ -26827,10 +26926,10 @@
     </row>
     <row r="56" ht="68.05" customHeight="1">
       <c r="A56" t="s" s="10">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B56" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C56" s="12"/>
       <c r="D56" s="18">
@@ -26844,19 +26943,19 @@
       </c>
       <c r="G56" s="12"/>
       <c r="H56" t="s" s="19">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="I56" t="s" s="19">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="J56" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K56" t="s" s="19">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="L56" t="s" s="19">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="M56" s="12"/>
       <c r="N56" s="12"/>
@@ -26864,10 +26963,10 @@
     </row>
     <row r="57" ht="80.05" customHeight="1">
       <c r="A57" t="s" s="10">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B57" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C57" s="12"/>
       <c r="D57" s="18">
@@ -26881,19 +26980,19 @@
       </c>
       <c r="G57" s="12"/>
       <c r="H57" t="s" s="19">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="I57" t="s" s="19">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="J57" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K57" t="s" s="19">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="L57" t="s" s="19">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="M57" s="12"/>
       <c r="N57" s="12"/>
@@ -26901,10 +27000,10 @@
     </row>
     <row r="58" ht="68.05" customHeight="1">
       <c r="A58" t="s" s="10">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B58" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C58" s="12"/>
       <c r="D58" s="18">
@@ -26918,19 +27017,19 @@
       </c>
       <c r="G58" s="12"/>
       <c r="H58" t="s" s="19">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="I58" t="s" s="19">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="J58" t="s" s="19">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K58" t="s" s="19">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="L58" t="s" s="19">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="M58" s="12"/>
       <c r="N58" s="12"/>
@@ -26938,10 +27037,10 @@
     </row>
     <row r="59" ht="68.05" customHeight="1">
       <c r="A59" t="s" s="10">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B59" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C59" s="12"/>
       <c r="D59" s="18">
@@ -26955,19 +27054,19 @@
       </c>
       <c r="G59" s="12"/>
       <c r="H59" t="s" s="19">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="I59" t="s" s="19">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="J59" t="s" s="19">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="K59" t="s" s="19">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="L59" t="s" s="19">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="M59" s="12"/>
       <c r="N59" s="12"/>
@@ -26975,10 +27074,10 @@
     </row>
     <row r="60" ht="68.05" customHeight="1">
       <c r="A60" t="s" s="10">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B60" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C60" s="12"/>
       <c r="D60" s="18">
@@ -26992,19 +27091,19 @@
       </c>
       <c r="G60" s="12"/>
       <c r="H60" t="s" s="19">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="I60" t="s" s="19">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="J60" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K60" t="s" s="19">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="L60" t="s" s="19">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="M60" s="12"/>
       <c r="N60" s="12"/>
@@ -27012,10 +27111,10 @@
     </row>
     <row r="61" ht="68.05" customHeight="1">
       <c r="A61" t="s" s="10">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="B61" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C61" s="12"/>
       <c r="D61" s="18">
@@ -27029,19 +27128,19 @@
       </c>
       <c r="G61" s="12"/>
       <c r="H61" t="s" s="19">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="I61" t="s" s="19">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="J61" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K61" t="s" s="19">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="L61" t="s" s="19">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="M61" s="12"/>
       <c r="N61" s="12"/>
@@ -27049,10 +27148,10 @@
     </row>
     <row r="62" ht="68.05" customHeight="1">
       <c r="A62" t="s" s="10">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B62" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C62" s="12"/>
       <c r="D62" s="18">
@@ -27066,19 +27165,19 @@
       </c>
       <c r="G62" s="12"/>
       <c r="H62" t="s" s="19">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="I62" t="s" s="19">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="J62" t="s" s="19">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="K62" t="s" s="19">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="L62" t="s" s="19">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="M62" s="12"/>
       <c r="N62" s="12"/>
@@ -27086,10 +27185,10 @@
     </row>
     <row r="63" ht="68.05" customHeight="1">
       <c r="A63" t="s" s="10">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B63" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C63" s="12"/>
       <c r="D63" s="18">
@@ -27103,19 +27202,19 @@
       </c>
       <c r="G63" s="12"/>
       <c r="H63" t="s" s="19">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="I63" t="s" s="19">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="J63" t="s" s="19">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="K63" t="s" s="19">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="L63" t="s" s="19">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="M63" s="12"/>
       <c r="N63" s="12"/>
@@ -27123,10 +27222,10 @@
     </row>
     <row r="64" ht="68.05" customHeight="1">
       <c r="A64" t="s" s="10">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B64" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C64" s="12"/>
       <c r="D64" s="18">
@@ -27140,19 +27239,19 @@
       </c>
       <c r="G64" s="12"/>
       <c r="H64" t="s" s="19">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="I64" t="s" s="19">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="J64" t="s" s="19">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K64" t="s" s="19">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="L64" t="s" s="19">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="M64" s="12"/>
       <c r="N64" s="12"/>
@@ -27160,10 +27259,10 @@
     </row>
     <row r="65" ht="80.05" customHeight="1">
       <c r="A65" t="s" s="10">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="B65" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C65" s="12"/>
       <c r="D65" s="18">
@@ -27178,14 +27277,14 @@
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" t="s" s="19">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="J65" s="12"/>
       <c r="K65" t="s" s="19">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="L65" t="s" s="19">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="M65" s="12"/>
       <c r="N65" s="12"/>
@@ -27193,10 +27292,10 @@
     </row>
     <row r="66" ht="80.05" customHeight="1">
       <c r="A66" t="s" s="10">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="B66" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C66" s="12"/>
       <c r="D66" s="18">
@@ -27210,17 +27309,17 @@
       </c>
       <c r="G66" s="12"/>
       <c r="H66" t="s" s="19">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="I66" t="s" s="19">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="J66" s="12"/>
       <c r="K66" t="s" s="19">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="L66" t="s" s="19">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="M66" s="12"/>
       <c r="N66" s="12"/>
@@ -27228,10 +27327,10 @@
     </row>
     <row r="67" ht="80.05" customHeight="1">
       <c r="A67" t="s" s="10">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B67" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C67" s="12"/>
       <c r="D67" s="18">
@@ -27246,14 +27345,14 @@
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
       <c r="I67" t="s" s="19">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="J67" s="12"/>
       <c r="K67" t="s" s="19">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="L67" t="s" s="19">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="M67" s="12"/>
       <c r="N67" s="12"/>
@@ -27261,10 +27360,10 @@
     </row>
     <row r="68" ht="80.05" customHeight="1">
       <c r="A68" t="s" s="10">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="B68" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C68" s="12"/>
       <c r="D68" s="18">
@@ -27279,14 +27378,14 @@
       <c r="G68" s="12"/>
       <c r="H68" s="12"/>
       <c r="I68" t="s" s="19">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="J68" s="12"/>
       <c r="K68" t="s" s="19">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="L68" t="s" s="19">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
@@ -27294,10 +27393,10 @@
     </row>
     <row r="69" ht="80.05" customHeight="1">
       <c r="A69" t="s" s="10">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="B69" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C69" s="12"/>
       <c r="D69" s="18">
@@ -27312,14 +27411,14 @@
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
       <c r="I69" t="s" s="19">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="J69" s="12"/>
       <c r="K69" t="s" s="19">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="L69" t="s" s="19">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="M69" s="12"/>
       <c r="N69" s="12"/>
@@ -27327,10 +27426,10 @@
     </row>
     <row r="70" ht="80.05" customHeight="1">
       <c r="A70" t="s" s="10">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="B70" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C70" s="12"/>
       <c r="D70" s="18">
@@ -27349,10 +27448,10 @@
       </c>
       <c r="J70" s="12"/>
       <c r="K70" t="s" s="19">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="L70" t="s" s="19">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="M70" s="12"/>
       <c r="N70" s="12"/>
@@ -27360,10 +27459,10 @@
     </row>
     <row r="71" ht="80.05" customHeight="1">
       <c r="A71" t="s" s="10">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B71" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C71" s="12"/>
       <c r="D71" s="18">
@@ -27378,14 +27477,14 @@
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
       <c r="I71" t="s" s="19">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="J71" s="12"/>
       <c r="K71" t="s" s="19">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="L71" t="s" s="19">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="M71" s="12"/>
       <c r="N71" s="12"/>
@@ -27393,10 +27492,10 @@
     </row>
     <row r="72" ht="80.05" customHeight="1">
       <c r="A72" t="s" s="10">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="B72" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C72" s="12"/>
       <c r="D72" s="18">
@@ -27415,10 +27514,10 @@
       </c>
       <c r="J72" s="12"/>
       <c r="K72" t="s" s="19">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="L72" t="s" s="19">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="M72" s="12"/>
       <c r="N72" s="12"/>
@@ -27426,10 +27525,10 @@
     </row>
     <row r="73" ht="80.05" customHeight="1">
       <c r="A73" t="s" s="10">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="B73" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="18">
@@ -27444,14 +27543,14 @@
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" t="s" s="19">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="J73" s="12"/>
       <c r="K73" t="s" s="19">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="L73" t="s" s="19">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="M73" s="12"/>
       <c r="N73" s="12"/>
@@ -27459,10 +27558,10 @@
     </row>
     <row r="74" ht="80.05" customHeight="1">
       <c r="A74" t="s" s="10">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="B74" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C74" s="12"/>
       <c r="D74" s="18">
@@ -27477,14 +27576,14 @@
       <c r="G74" s="12"/>
       <c r="H74" s="12"/>
       <c r="I74" t="s" s="19">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="J74" s="12"/>
       <c r="K74" t="s" s="19">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="L74" t="s" s="19">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="M74" s="12"/>
       <c r="N74" s="12"/>
@@ -27492,10 +27591,10 @@
     </row>
     <row r="75" ht="80.05" customHeight="1">
       <c r="A75" t="s" s="10">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="B75" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C75" s="12"/>
       <c r="D75" s="18">
@@ -27510,14 +27609,14 @@
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
       <c r="I75" t="s" s="19">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="J75" s="12"/>
       <c r="K75" t="s" s="19">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="L75" t="s" s="19">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M75" s="12"/>
       <c r="N75" s="12"/>
@@ -27525,10 +27624,10 @@
     </row>
     <row r="76" ht="80.05" customHeight="1">
       <c r="A76" t="s" s="10">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="B76" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="18">
@@ -27543,14 +27642,14 @@
       <c r="G76" s="12"/>
       <c r="H76" s="12"/>
       <c r="I76" t="s" s="19">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="J76" s="12"/>
       <c r="K76" t="s" s="19">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="L76" t="s" s="19">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M76" s="12"/>
       <c r="N76" s="12"/>
@@ -27558,10 +27657,10 @@
     </row>
     <row r="77" ht="80.05" customHeight="1">
       <c r="A77" t="s" s="10">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="B77" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C77" s="12"/>
       <c r="D77" s="18">
@@ -27576,14 +27675,14 @@
       <c r="G77" s="12"/>
       <c r="H77" s="12"/>
       <c r="I77" t="s" s="19">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="J77" s="12"/>
       <c r="K77" t="s" s="19">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="L77" t="s" s="19">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M77" s="12"/>
       <c r="N77" s="12"/>
@@ -27591,10 +27690,10 @@
     </row>
     <row r="78" ht="80.05" customHeight="1">
       <c r="A78" t="s" s="10">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="B78" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C78" s="12"/>
       <c r="D78" s="18">
@@ -27613,10 +27712,10 @@
       </c>
       <c r="J78" s="12"/>
       <c r="K78" t="s" s="19">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="L78" t="s" s="19">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M78" s="12"/>
       <c r="N78" s="12"/>
@@ -27624,10 +27723,10 @@
     </row>
     <row r="79" ht="80.05" customHeight="1">
       <c r="A79" t="s" s="10">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="B79" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C79" s="12"/>
       <c r="D79" s="18">
@@ -27642,14 +27741,14 @@
       <c r="G79" s="12"/>
       <c r="H79" s="12"/>
       <c r="I79" t="s" s="19">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="J79" s="12"/>
       <c r="K79" t="s" s="19">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="L79" t="s" s="19">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M79" s="12"/>
       <c r="N79" s="12"/>
@@ -27657,10 +27756,10 @@
     </row>
     <row r="80" ht="80.05" customHeight="1">
       <c r="A80" t="s" s="10">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="B80" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C80" s="12"/>
       <c r="D80" s="18">
@@ -27675,14 +27774,14 @@
       <c r="G80" s="12"/>
       <c r="H80" s="12"/>
       <c r="I80" t="s" s="19">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="J80" s="12"/>
       <c r="K80" t="s" s="19">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="L80" t="s" s="19">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="M80" s="12"/>
       <c r="N80" s="12"/>
@@ -27690,7 +27789,7 @@
     </row>
     <row r="81" ht="20.05" customHeight="1">
       <c r="A81" t="s" s="10">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B81" s="14"/>
       <c r="C81" s="12"/>
@@ -27709,7 +27808,7 @@
     </row>
     <row r="82" ht="32.05" customHeight="1">
       <c r="A82" t="s" s="10">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="B82" s="14"/>
       <c r="C82" s="12"/>
@@ -27729,7 +27828,7 @@
       </c>
       <c r="J82" s="12"/>
       <c r="K82" t="s" s="19">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="L82" s="12"/>
       <c r="M82" s="12"/>
@@ -27738,7 +27837,7 @@
     </row>
     <row r="83" ht="44.05" customHeight="1">
       <c r="A83" t="s" s="10">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B83" s="14"/>
       <c r="C83" s="12"/>
@@ -27752,7 +27851,7 @@
       <c r="I83" s="12"/>
       <c r="J83" s="12"/>
       <c r="K83" t="s" s="19">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="L83" s="12"/>
       <c r="M83" s="12"/>
@@ -27761,7 +27860,7 @@
     </row>
     <row r="84" ht="32.05" customHeight="1">
       <c r="A84" t="s" s="10">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="12"/>
@@ -27775,7 +27874,7 @@
       <c r="I84" s="12"/>
       <c r="J84" s="12"/>
       <c r="K84" t="s" s="19">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="L84" s="12"/>
       <c r="M84" s="12"/>
@@ -27784,7 +27883,7 @@
     </row>
     <row r="85" ht="20.05" customHeight="1">
       <c r="A85" t="s" s="10">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B85" s="14"/>
       <c r="C85" s="12"/>
@@ -27805,10 +27904,10 @@
     </row>
     <row r="86" ht="80.05" customHeight="1">
       <c r="A86" t="s" s="10">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B86" t="s" s="11">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C86" s="18">
         <v>0</v>
@@ -27824,19 +27923,19 @@
       </c>
       <c r="G86" s="12"/>
       <c r="H86" t="s" s="19">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="I86" t="s" s="19">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="J86" t="s" s="19">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="K86" t="s" s="19">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="L86" t="s" s="19">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M86" s="12"/>
       <c r="N86" s="12"/>
@@ -27844,7 +27943,7 @@
     </row>
     <row r="87" ht="20.05" customHeight="1">
       <c r="A87" t="s" s="10">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="B87" s="14"/>
       <c r="C87" s="12"/>
@@ -27865,7 +27964,7 @@
     </row>
     <row r="88" ht="80.05" customHeight="1">
       <c r="A88" t="s" s="10">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B88" s="14"/>
       <c r="C88" s="12"/>
@@ -27878,10 +27977,10 @@
       <c r="F88" s="12"/>
       <c r="G88" s="12"/>
       <c r="H88" t="s" s="19">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="I88" t="s" s="19">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="J88" s="12"/>
       <c r="K88" s="12"/>
@@ -35869,24 +35968,24 @@
         <v>28</v>
       </c>
       <c r="N2" t="s" s="5">
-        <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(L3:L545,"Yes")</f>
-        <v>1057</v>
+        <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N545,"Yes")</f>
+        <v>1061</v>
       </c>
       <c r="O2" t="s" s="5">
-        <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(M3:M545,"Yes")</f>
-        <v>30</v>
+        <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O545,"Yes")</f>
+        <v>1062</v>
       </c>
       <c r="P2" t="s" s="5">
-        <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(N3:N545,"Yes")</f>
-        <v>1058</v>
+        <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P545,"Yes")</f>
+        <v>1063</v>
       </c>
     </row>
     <row r="3" ht="44.25" customHeight="1">
       <c r="A3" t="s" s="7">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C3" s="16">
         <v>0</v>
@@ -35898,7 +35997,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s" s="17">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" t="s" s="17">
@@ -35917,10 +36016,10 @@
     </row>
     <row r="4" ht="44.05" customHeight="1">
       <c r="A4" t="s" s="10">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C4" s="18">
         <v>200</v>
@@ -35932,7 +36031,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="s" s="19">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" t="s" s="19">
@@ -35951,10 +36050,10 @@
     </row>
     <row r="5" ht="32.05" customHeight="1">
       <c r="A5" t="s" s="10">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C5" s="18">
         <v>0</v>
@@ -35966,7 +36065,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s" s="19">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="I5" s="12"/>
       <c r="J5" t="s" s="19">
@@ -35985,10 +36084,10 @@
     </row>
     <row r="6" ht="44.05" customHeight="1">
       <c r="A6" t="s" s="10">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C6" s="18">
         <v>0</v>
@@ -36000,7 +36099,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="s" s="19">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" t="s" s="19">
@@ -36019,10 +36118,10 @@
     </row>
     <row r="7" ht="32.05" customHeight="1">
       <c r="A7" t="s" s="10">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C7" s="18">
         <v>500</v>
@@ -36034,7 +36133,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="s" s="19">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" t="s" s="19">
@@ -36053,10 +36152,10 @@
     </row>
     <row r="8" ht="56.05" customHeight="1">
       <c r="A8" t="s" s="10">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -36068,7 +36167,7 @@
         <v>5</v>
       </c>
       <c r="H8" t="s" s="19">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" t="s" s="19">
@@ -36087,10 +36186,10 @@
     </row>
     <row r="9" ht="32.05" customHeight="1">
       <c r="A9" t="s" s="10">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C9" s="18">
         <v>800</v>
@@ -36102,7 +36201,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s" s="19">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" t="s" s="19">
@@ -36121,10 +36220,10 @@
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="A10" t="s" s="10">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C10" s="18">
         <v>250</v>
@@ -36136,7 +36235,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s" s="19">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" t="s" s="19">
@@ -36155,10 +36254,10 @@
     </row>
     <row r="11" ht="32.05" customHeight="1">
       <c r="A11" t="s" s="10">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C11" s="18">
         <v>1000</v>
@@ -36170,7 +36269,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s" s="19">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" t="s" s="19">
@@ -36189,10 +36288,10 @@
     </row>
     <row r="12" ht="44.05" customHeight="1">
       <c r="A12" t="s" s="10">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C12" s="18">
         <v>200</v>
@@ -36204,7 +36303,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="s" s="19">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" t="s" s="19">
@@ -36219,10 +36318,10 @@
     </row>
     <row r="13" ht="44.05" customHeight="1">
       <c r="A13" t="s" s="10">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="B13" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C13" s="18">
         <v>500</v>
@@ -36234,7 +36333,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="s" s="19">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="I13" s="12"/>
       <c r="J13" t="s" s="19">
@@ -36253,10 +36352,10 @@
     </row>
     <row r="14" ht="20.05" customHeight="1">
       <c r="A14" t="s" s="10">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="B14" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C14" s="18">
         <v>1500</v>
@@ -36268,7 +36367,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s" s="19">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="I14" s="12"/>
       <c r="J14" t="s" s="19">
@@ -36287,10 +36386,10 @@
     </row>
     <row r="15" ht="44.05" customHeight="1">
       <c r="A15" t="s" s="10">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="B15" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C15" s="18">
         <v>500</v>
@@ -36302,7 +36401,7 @@
         <v>4</v>
       </c>
       <c r="H15" t="s" s="19">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" t="s" s="19">
@@ -36321,10 +36420,10 @@
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="A16" t="s" s="10">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="B16" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C16" s="18">
         <v>1500</v>
@@ -36336,7 +36435,7 @@
         <v>5</v>
       </c>
       <c r="H16" t="s" s="19">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" t="s" s="19">
@@ -36355,10 +36454,10 @@
     </row>
     <row r="17" ht="44.05" customHeight="1">
       <c r="A17" t="s" s="10">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="B17" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C17" s="18">
         <v>600</v>
@@ -36370,7 +36469,7 @@
         <v>4</v>
       </c>
       <c r="H17" t="s" s="19">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" t="s" s="19">
@@ -36389,10 +36488,10 @@
     </row>
     <row r="18" ht="44.05" customHeight="1">
       <c r="A18" t="s" s="10">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="B18" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -36404,7 +36503,7 @@
         <v>3</v>
       </c>
       <c r="H18" t="s" s="19">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" t="s" s="19">
@@ -36423,10 +36522,10 @@
     </row>
     <row r="19" ht="44.05" customHeight="1">
       <c r="A19" t="s" s="10">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="B19" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C19" s="18">
         <v>800</v>
@@ -36438,7 +36537,7 @@
         <v>4</v>
       </c>
       <c r="H19" t="s" s="19">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" t="s" s="19">
@@ -36453,13 +36552,13 @@
     </row>
     <row r="20" ht="56.05" customHeight="1">
       <c r="A20" t="s" s="10">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="B20" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C20" s="18">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
@@ -36468,7 +36567,7 @@
         <v>4</v>
       </c>
       <c r="H20" t="s" s="19">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" t="s" s="19">
@@ -36483,10 +36582,10 @@
     </row>
     <row r="21" ht="44.05" customHeight="1">
       <c r="A21" t="s" s="10">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="B21" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C21" s="18">
         <v>0</v>
@@ -36498,7 +36597,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s" s="19">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" t="s" s="19">
@@ -36517,10 +36616,10 @@
     </row>
     <row r="22" ht="44.05" customHeight="1">
       <c r="A22" t="s" s="10">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="B22" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C22" s="18">
         <v>50</v>
@@ -36532,7 +36631,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="s" s="19">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" t="s" s="19">
@@ -36547,10 +36646,10 @@
     </row>
     <row r="23" ht="32.05" customHeight="1">
       <c r="A23" t="s" s="10">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C23" s="18">
         <v>100</v>
@@ -36562,7 +36661,7 @@
         <v>3</v>
       </c>
       <c r="H23" t="s" s="19">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" t="s" s="19">
@@ -36577,10 +36676,10 @@
     </row>
     <row r="24" ht="44.05" customHeight="1">
       <c r="A24" t="s" s="10">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="B24" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C24" s="18">
         <v>1000</v>
@@ -36592,7 +36691,7 @@
         <v>5</v>
       </c>
       <c r="H24" t="s" s="19">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" t="s" s="19">
@@ -36607,10 +36706,10 @@
     </row>
     <row r="25" ht="44.05" customHeight="1">
       <c r="A25" t="s" s="10">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="B25" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C25" s="18">
         <v>850</v>
@@ -36622,7 +36721,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s" s="19">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" t="s" s="19">
@@ -36637,10 +36736,10 @@
     </row>
     <row r="26" ht="56.05" customHeight="1">
       <c r="A26" t="s" s="10">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="B26" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C26" s="18">
         <v>600</v>
@@ -36652,7 +36751,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="s" s="19">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" t="s" s="19">
@@ -36667,10 +36766,10 @@
     </row>
     <row r="27" ht="56.05" customHeight="1">
       <c r="A27" t="s" s="10">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="B27" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C27" s="18">
         <v>600</v>
@@ -36682,7 +36781,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s" s="19">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" t="s" s="19">
@@ -36697,10 +36796,10 @@
     </row>
     <row r="28" ht="56.05" customHeight="1">
       <c r="A28" t="s" s="10">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="B28" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C28" s="18">
         <v>600</v>
@@ -36712,7 +36811,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s" s="19">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" t="s" s="19">
@@ -36727,10 +36826,10 @@
     </row>
     <row r="29" ht="56.05" customHeight="1">
       <c r="A29" t="s" s="10">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="B29" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C29" s="18">
         <v>600</v>
@@ -36742,7 +36841,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s" s="19">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" t="s" s="19">
@@ -36757,10 +36856,10 @@
     </row>
     <row r="30" ht="56.05" customHeight="1">
       <c r="A30" t="s" s="10">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="B30" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C30" s="18">
         <v>600</v>
@@ -36772,7 +36871,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s" s="19">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" t="s" s="19">
@@ -36787,10 +36886,10 @@
     </row>
     <row r="31" ht="56.05" customHeight="1">
       <c r="A31" t="s" s="10">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="B31" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C31" s="18">
         <v>600</v>
@@ -36802,7 +36901,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s" s="19">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="I31" s="12"/>
       <c r="J31" t="s" s="19">
@@ -36817,10 +36916,10 @@
     </row>
     <row r="32" ht="56.05" customHeight="1">
       <c r="A32" t="s" s="10">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="B32" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C32" s="18">
         <v>600</v>
@@ -36832,7 +36931,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s" s="19">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" t="s" s="19">
@@ -36847,10 +36946,10 @@
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="A33" t="s" s="10">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="B33" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C33" s="18">
         <v>300</v>
@@ -36862,7 +36961,7 @@
         <v>2</v>
       </c>
       <c r="H33" t="s" s="19">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" t="s" s="19">
@@ -36877,10 +36976,10 @@
     </row>
     <row r="34" ht="44.05" customHeight="1">
       <c r="A34" t="s" s="10">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="B34" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C34" s="18">
         <v>800</v>
@@ -36892,7 +36991,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s" s="19">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" t="s" s="19">
@@ -36907,10 +37006,10 @@
     </row>
     <row r="35" ht="32.05" customHeight="1">
       <c r="A35" t="s" s="10">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="B35" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C35" s="18">
         <v>800</v>
@@ -36922,7 +37021,7 @@
         <v>3</v>
       </c>
       <c r="H35" t="s" s="19">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" t="s" s="19">
@@ -36937,10 +37036,10 @@
     </row>
     <row r="36" ht="32.05" customHeight="1">
       <c r="A36" t="s" s="10">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="B36" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C36" s="18">
         <v>800</v>
@@ -36952,7 +37051,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s" s="19">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" t="s" s="19">
@@ -36967,10 +37066,10 @@
     </row>
     <row r="37" ht="32.05" customHeight="1">
       <c r="A37" t="s" s="10">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="B37" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C37" s="18">
         <v>800</v>
@@ -36982,7 +37081,7 @@
         <v>3</v>
       </c>
       <c r="H37" t="s" s="19">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" t="s" s="19">
@@ -36997,10 +37096,10 @@
     </row>
     <row r="38" ht="44.05" customHeight="1">
       <c r="A38" t="s" s="10">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="B38" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C38" s="18">
         <v>800</v>
@@ -37012,7 +37111,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s" s="19">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" t="s" s="19">
@@ -37027,10 +37126,10 @@
     </row>
     <row r="39" ht="44.05" customHeight="1">
       <c r="A39" t="s" s="10">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="B39" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C39" s="18">
         <v>800</v>
@@ -37042,7 +37141,7 @@
         <v>3</v>
       </c>
       <c r="H39" t="s" s="19">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" t="s" s="19">
@@ -37057,10 +37156,10 @@
     </row>
     <row r="40" ht="32.05" customHeight="1">
       <c r="A40" t="s" s="10">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="B40" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C40" s="18">
         <v>800</v>
@@ -37072,7 +37171,7 @@
         <v>3</v>
       </c>
       <c r="H40" t="s" s="19">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" t="s" s="19">
@@ -37087,10 +37186,10 @@
     </row>
     <row r="41" ht="44.05" customHeight="1">
       <c r="A41" t="s" s="10">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="B41" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C41" s="18">
         <v>1200</v>
@@ -37102,7 +37201,7 @@
         <v>3</v>
       </c>
       <c r="H41" t="s" s="19">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" t="s" s="19">
@@ -37117,10 +37216,10 @@
     </row>
     <row r="42" ht="56.05" customHeight="1">
       <c r="A42" t="s" s="10">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="B42" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C42" s="18">
         <v>1500</v>
@@ -37132,7 +37231,7 @@
         <v>4</v>
       </c>
       <c r="H42" t="s" s="19">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" t="s" s="19">
@@ -37147,10 +37246,10 @@
     </row>
     <row r="43" ht="44.05" customHeight="1">
       <c r="A43" t="s" s="10">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="B43" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C43" s="18">
         <v>100</v>
@@ -37162,7 +37261,7 @@
         <v>2</v>
       </c>
       <c r="H43" t="s" s="19">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" t="s" s="19">
@@ -37181,10 +37280,10 @@
     </row>
     <row r="44" ht="44.05" customHeight="1">
       <c r="A44" t="s" s="10">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="B44" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C44" s="18">
         <v>700</v>
@@ -37196,7 +37295,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s" s="19">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" t="s" s="19">
@@ -37215,10 +37314,10 @@
     </row>
     <row r="45" ht="44.05" customHeight="1">
       <c r="A45" t="s" s="10">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="B45" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C45" s="18">
         <v>1200</v>
@@ -37230,7 +37329,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s" s="19">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12"/>
@@ -37243,10 +37342,10 @@
     </row>
     <row r="46" ht="44.05" customHeight="1">
       <c r="A46" t="s" s="10">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="B46" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C46" s="18">
         <v>1500</v>
@@ -37258,7 +37357,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s" s="19">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
@@ -37271,10 +37370,10 @@
     </row>
     <row r="47" ht="44.05" customHeight="1">
       <c r="A47" t="s" s="10">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="B47" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C47" s="18">
         <v>950</v>
@@ -37286,7 +37385,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s" s="19">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12"/>
@@ -37299,10 +37398,10 @@
     </row>
     <row r="48" ht="44.05" customHeight="1">
       <c r="A48" t="s" s="10">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="B48" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C48" s="18">
         <v>0</v>
@@ -37314,7 +37413,7 @@
         <v>3</v>
       </c>
       <c r="H48" t="s" s="19">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
@@ -37327,10 +37426,10 @@
     </row>
     <row r="49" ht="44.05" customHeight="1">
       <c r="A49" t="s" s="10">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="B49" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C49" s="18">
         <v>2000</v>
@@ -37342,7 +37441,7 @@
         <v>5</v>
       </c>
       <c r="H49" t="s" s="19">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
@@ -37355,10 +37454,10 @@
     </row>
     <row r="50" ht="56.05" customHeight="1">
       <c r="A50" t="s" s="10">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="B50" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C50" s="18">
         <v>100</v>
@@ -37370,7 +37469,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s" s="19">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
@@ -37383,7 +37482,7 @@
     </row>
     <row r="51" ht="44.05" customHeight="1">
       <c r="A51" t="s" s="10">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B51" s="14"/>
       <c r="C51" s="18">
@@ -37396,7 +37495,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s" s="19">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="I51" s="12"/>
       <c r="J51" s="12"/>
@@ -37409,10 +37508,10 @@
     </row>
     <row r="52" ht="44.05" customHeight="1">
       <c r="A52" t="s" s="10">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="B52" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C52" s="18">
         <v>0</v>
@@ -37424,7 +37523,7 @@
         <v>2</v>
       </c>
       <c r="H52" t="s" s="19">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="I52" s="12"/>
       <c r="J52" t="s" s="19">
@@ -37443,7 +37542,7 @@
     </row>
     <row r="53" ht="32.05" customHeight="1">
       <c r="A53" t="s" s="10">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="18">
@@ -37456,7 +37555,7 @@
         <v>2</v>
       </c>
       <c r="H53" t="s" s="19">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="I53" s="12"/>
       <c r="J53" s="12"/>
@@ -37469,7 +37568,7 @@
     </row>
     <row r="54" ht="32.05" customHeight="1">
       <c r="A54" t="s" s="10">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="B54" s="14"/>
       <c r="C54" s="18">
@@ -37482,7 +37581,7 @@
         <v>3</v>
       </c>
       <c r="H54" t="s" s="19">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
@@ -37495,10 +37594,10 @@
     </row>
     <row r="55" ht="32.05" customHeight="1">
       <c r="A55" t="s" s="10">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="B55" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C55" s="18">
         <v>0</v>
@@ -37510,7 +37609,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="s" s="19">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="I55" s="12"/>
       <c r="J55" t="s" s="19">
@@ -37529,10 +37628,10 @@
     </row>
     <row r="56" ht="44.05" customHeight="1">
       <c r="A56" t="s" s="10">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="B56" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C56" s="18">
         <v>0</v>
@@ -37544,7 +37643,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="s" s="19">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="I56" s="12"/>
       <c r="J56" t="s" s="19">
@@ -37563,7 +37662,7 @@
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="A57" t="s" s="10">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="B57" s="14"/>
       <c r="C57" s="18">
@@ -37576,7 +37675,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="s" s="19">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="I57" s="12"/>
       <c r="J57" s="12"/>
@@ -37589,10 +37688,10 @@
     </row>
     <row r="58" ht="56.05" customHeight="1">
       <c r="A58" t="s" s="10">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="B58" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C58" s="18">
         <v>0</v>
@@ -37604,7 +37703,7 @@
         <v>2</v>
       </c>
       <c r="H58" t="s" s="19">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="I58" s="12"/>
       <c r="J58" t="s" s="19">
@@ -37623,7 +37722,7 @@
     </row>
     <row r="59" ht="56.05" customHeight="1">
       <c r="A59" t="s" s="10">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="18">
@@ -37636,7 +37735,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="s" s="19">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="I59" s="12"/>
       <c r="J59" s="12"/>
@@ -37649,10 +37748,10 @@
     </row>
     <row r="60" ht="44.05" customHeight="1">
       <c r="A60" t="s" s="10">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="B60" t="s" s="11">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C60" s="18">
         <v>0</v>
@@ -37664,7 +37763,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="s" s="19">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="I60" s="12"/>
       <c r="J60" t="s" s="19">
@@ -37683,7 +37782,7 @@
     </row>
     <row r="61" ht="56.05" customHeight="1">
       <c r="A61" t="s" s="10">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="B61" s="14"/>
       <c r="C61" s="18">
@@ -37696,7 +37795,7 @@
         <v>5</v>
       </c>
       <c r="H61" t="s" s="19">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="I61" s="12"/>
       <c r="J61" s="12"/>
@@ -37709,7 +37808,7 @@
     </row>
     <row r="62" ht="44.05" customHeight="1">
       <c r="A62" t="s" s="10">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="18">
@@ -37720,7 +37819,7 @@
       <c r="F62" s="12"/>
       <c r="G62" s="12"/>
       <c r="H62" t="s" s="19">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="I62" s="12"/>
       <c r="J62" s="12"/>
@@ -46504,7 +46603,7 @@
         <v>24</v>
       </c>
       <c r="J2" t="s" s="5">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="K2" t="s" s="5">
         <v>26</v>
@@ -46516,24 +46615,24 @@
         <v>28</v>
       </c>
       <c r="N2" t="s" s="5">
-        <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(L3:L556,"Yes")</f>
-        <v>1181</v>
+        <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N556,"Yes")</f>
+        <v>1186</v>
       </c>
       <c r="O2" t="s" s="5">
-        <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(M3:M556,"Yes")</f>
-        <v>30</v>
+        <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O556,"Yes")</f>
+        <v>1187</v>
       </c>
       <c r="P2" t="s" s="5">
-        <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(N3:N556,"Yes")</f>
-        <v>1182</v>
+        <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P556,"Yes")</f>
+        <v>1063</v>
       </c>
     </row>
     <row r="3" ht="32.25" customHeight="1">
       <c r="A3" t="s" s="7">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C3" s="16">
         <v>0</v>
@@ -46545,7 +46644,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s" s="17">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" t="s" s="17">
@@ -46560,10 +46659,10 @@
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" t="s" s="10">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C4" s="18">
         <v>0</v>
@@ -46575,7 +46674,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s" s="19">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" t="s" s="19">
@@ -46594,10 +46693,10 @@
     </row>
     <row r="5" ht="32.05" customHeight="1">
       <c r="A5" t="s" s="10">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C5" s="18">
         <v>0</v>
@@ -46609,7 +46708,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="s" s="19">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="I5" s="12"/>
       <c r="J5" t="s" s="19">
@@ -46624,10 +46723,10 @@
     </row>
     <row r="6" ht="56.05" customHeight="1">
       <c r="A6" t="s" s="10">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C6" s="18">
         <v>0</v>
@@ -46639,7 +46738,7 @@
         <v>5</v>
       </c>
       <c r="H6" t="s" s="19">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" t="s" s="19">
@@ -46654,10 +46753,10 @@
     </row>
     <row r="7" ht="44.05" customHeight="1">
       <c r="A7" t="s" s="10">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C7" s="18">
         <v>0</v>
@@ -46669,7 +46768,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="s" s="19">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" t="s" s="19">
@@ -46684,10 +46783,10 @@
     </row>
     <row r="8" ht="56.05" customHeight="1">
       <c r="A8" t="s" s="10">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -46699,7 +46798,7 @@
         <v>3</v>
       </c>
       <c r="H8" t="s" s="19">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" t="s" s="19">
@@ -46714,10 +46813,10 @@
     </row>
     <row r="9" ht="56.05" customHeight="1">
       <c r="A9" t="s" s="10">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C9" s="18">
         <v>0</v>
@@ -46729,7 +46828,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s" s="19">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" t="s" s="19">
@@ -46744,10 +46843,10 @@
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="A10" t="s" s="10">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C10" s="18">
         <v>0</v>
@@ -46759,7 +46858,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s" s="19">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" t="s" s="19">
@@ -46778,10 +46877,10 @@
     </row>
     <row r="11" ht="44.05" customHeight="1">
       <c r="A11" t="s" s="10">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C11" s="18">
         <v>0</v>
@@ -46793,7 +46892,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s" s="19">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" t="s" s="19">
@@ -46812,10 +46911,10 @@
     </row>
     <row r="12" ht="32.05" customHeight="1">
       <c r="A12" t="s" s="10">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C12" s="18">
         <v>0</v>
@@ -46827,7 +46926,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="s" s="19">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" t="s" s="19">
@@ -46846,10 +46945,10 @@
     </row>
     <row r="13" ht="44.05" customHeight="1">
       <c r="A13" t="s" s="10">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="B13" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C13" s="18">
         <v>0</v>
@@ -46861,7 +46960,7 @@
         <v>4</v>
       </c>
       <c r="H13" t="s" s="19">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="I13" s="12"/>
       <c r="J13" t="s" s="19">
@@ -46880,10 +46979,10 @@
     </row>
     <row r="14" ht="56.05" customHeight="1">
       <c r="A14" t="s" s="10">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="B14" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C14" s="18">
         <v>3000</v>
@@ -46895,7 +46994,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s" s="19">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="I14" s="12"/>
       <c r="J14" t="s" s="19">
@@ -46910,10 +47009,10 @@
     </row>
     <row r="15" ht="56.05" customHeight="1">
       <c r="A15" t="s" s="10">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="B15" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C15" s="18">
         <v>2000</v>
@@ -46925,7 +47024,7 @@
         <v>3</v>
       </c>
       <c r="H15" t="s" s="19">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" t="s" s="19">
@@ -46940,10 +47039,10 @@
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="A16" t="s" s="10">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="B16" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C16" s="18">
         <v>1000</v>
@@ -46955,7 +47054,7 @@
         <v>4</v>
       </c>
       <c r="H16" t="s" s="19">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" t="s" s="19">
@@ -46974,10 +47073,10 @@
     </row>
     <row r="17" ht="44.05" customHeight="1">
       <c r="A17" t="s" s="10">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B17" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C17" s="18">
         <v>1000</v>
@@ -46989,7 +47088,7 @@
         <v>3</v>
       </c>
       <c r="H17" t="s" s="19">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" t="s" s="19">
@@ -47008,10 +47107,10 @@
     </row>
     <row r="18" ht="32.05" customHeight="1">
       <c r="A18" t="s" s="10">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="B18" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C18" s="18">
         <v>500</v>
@@ -47023,7 +47122,7 @@
         <v>2</v>
       </c>
       <c r="H18" t="s" s="19">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" t="s" s="19">
@@ -47038,10 +47137,10 @@
     </row>
     <row r="19" ht="32.05" customHeight="1">
       <c r="A19" t="s" s="10">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B19" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C19" s="18">
         <v>1000</v>
@@ -47053,7 +47152,7 @@
         <v>4</v>
       </c>
       <c r="H19" t="s" s="19">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" t="s" s="19">
@@ -47068,10 +47167,10 @@
     </row>
     <row r="20" ht="56.05" customHeight="1">
       <c r="A20" t="s" s="10">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B20" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C20" s="18">
         <v>600</v>
@@ -47083,7 +47182,7 @@
         <v>3</v>
       </c>
       <c r="H20" t="s" s="19">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" t="s" s="19">
@@ -47098,10 +47197,10 @@
     </row>
     <row r="21" ht="44.05" customHeight="1">
       <c r="A21" t="s" s="10">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="B21" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C21" s="18">
         <v>1500</v>
@@ -47113,7 +47212,7 @@
         <v>4</v>
       </c>
       <c r="H21" t="s" s="19">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" t="s" s="19">
@@ -47128,10 +47227,10 @@
     </row>
     <row r="22" ht="44.05" customHeight="1">
       <c r="A22" t="s" s="10">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="B22" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C22" s="18">
         <v>850</v>
@@ -47143,7 +47242,7 @@
         <v>3</v>
       </c>
       <c r="H22" t="s" s="19">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" t="s" s="19">
@@ -47158,10 +47257,10 @@
     </row>
     <row r="23" ht="44.05" customHeight="1">
       <c r="A23" t="s" s="10">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C23" s="18">
         <v>1000</v>
@@ -47173,7 +47272,7 @@
         <v>5</v>
       </c>
       <c r="H23" t="s" s="19">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" t="s" s="19">
@@ -47192,10 +47291,10 @@
     </row>
     <row r="24" ht="20.05" customHeight="1">
       <c r="A24" t="s" s="10">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="B24" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C24" s="18">
         <v>2000</v>
@@ -47207,7 +47306,7 @@
         <v>4</v>
       </c>
       <c r="H24" t="s" s="19">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" t="s" s="19">
@@ -47222,10 +47321,10 @@
     </row>
     <row r="25" ht="56.05" customHeight="1">
       <c r="A25" t="s" s="10">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="B25" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C25" s="18">
         <v>1000</v>
@@ -47237,7 +47336,7 @@
         <v>3</v>
       </c>
       <c r="H25" t="s" s="19">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" t="s" s="19">
@@ -47256,10 +47355,10 @@
     </row>
     <row r="26" ht="80.05" customHeight="1">
       <c r="A26" t="s" s="10">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B26" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C26" s="18">
         <v>2000</v>
@@ -47271,7 +47370,7 @@
         <v>5</v>
       </c>
       <c r="H26" t="s" s="19">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" t="s" s="19">
@@ -47286,10 +47385,10 @@
     </row>
     <row r="27" ht="20.05" customHeight="1">
       <c r="A27" t="s" s="10">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="B27" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C27" s="18">
         <v>600</v>
@@ -47301,7 +47400,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s" s="19">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" t="s" s="19">
@@ -47320,10 +47419,10 @@
     </row>
     <row r="28" ht="44.05" customHeight="1">
       <c r="A28" t="s" s="10">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="B28" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C28" s="18">
         <v>500</v>
@@ -47335,7 +47434,7 @@
         <v>2</v>
       </c>
       <c r="H28" t="s" s="19">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" t="s" s="19">
@@ -47350,10 +47449,10 @@
     </row>
     <row r="29" ht="44.05" customHeight="1">
       <c r="A29" t="s" s="10">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="B29" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C29" s="18">
         <v>700</v>
@@ -47365,7 +47464,7 @@
         <v>5</v>
       </c>
       <c r="H29" t="s" s="19">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" t="s" s="19">
@@ -47380,10 +47479,10 @@
     </row>
     <row r="30" ht="68.05" customHeight="1">
       <c r="A30" t="s" s="10">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="B30" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C30" s="18">
         <v>1200</v>
@@ -47395,7 +47494,7 @@
         <v>4</v>
       </c>
       <c r="H30" t="s" s="19">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" t="s" s="19">
@@ -47410,10 +47509,10 @@
     </row>
     <row r="31" ht="56.05" customHeight="1">
       <c r="A31" t="s" s="10">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="B31" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C31" s="18">
         <v>1000</v>
@@ -47425,7 +47524,7 @@
         <v>5</v>
       </c>
       <c r="H31" t="s" s="19">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="I31" s="12"/>
       <c r="J31" t="s" s="19">
@@ -47440,10 +47539,10 @@
     </row>
     <row r="32" ht="56.05" customHeight="1">
       <c r="A32" t="s" s="10">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="B32" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C32" s="18">
         <v>1800</v>
@@ -47455,7 +47554,7 @@
         <v>5</v>
       </c>
       <c r="H32" t="s" s="19">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" t="s" s="19">
@@ -47470,10 +47569,10 @@
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="A33" t="s" s="10">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="B33" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C33" s="18">
         <v>1500</v>
@@ -47485,7 +47584,7 @@
         <v>4</v>
       </c>
       <c r="H33" t="s" s="19">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" t="s" s="19">
@@ -47504,10 +47603,10 @@
     </row>
     <row r="34" ht="44.05" customHeight="1">
       <c r="A34" t="s" s="10">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="B34" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C34" s="18">
         <v>1000</v>
@@ -47519,7 +47618,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s" s="19">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
@@ -47532,10 +47631,10 @@
     </row>
     <row r="35" ht="44.05" customHeight="1">
       <c r="A35" t="s" s="10">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="B35" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C35" s="18">
         <v>600</v>
@@ -47547,7 +47646,7 @@
         <v>2</v>
       </c>
       <c r="H35" t="s" s="19">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
@@ -47560,10 +47659,10 @@
     </row>
     <row r="36" ht="44.05" customHeight="1">
       <c r="A36" t="s" s="10">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="B36" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C36" s="18">
         <v>250</v>
@@ -47575,7 +47674,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s" s="19">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
@@ -47588,10 +47687,10 @@
     </row>
     <row r="37" ht="56.05" customHeight="1">
       <c r="A37" t="s" s="10">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="B37" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C37" s="18">
         <v>300</v>
@@ -47603,7 +47702,7 @@
         <v>2</v>
       </c>
       <c r="H37" t="s" s="19">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
@@ -47616,10 +47715,10 @@
     </row>
     <row r="38" ht="32.05" customHeight="1">
       <c r="A38" t="s" s="10">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="B38" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C38" s="18">
         <v>1000</v>
@@ -47631,7 +47730,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s" s="19">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
@@ -47644,10 +47743,10 @@
     </row>
     <row r="39" ht="32.05" customHeight="1">
       <c r="A39" t="s" s="10">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="B39" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C39" s="18">
         <v>1200</v>
@@ -47659,7 +47758,7 @@
         <v>4</v>
       </c>
       <c r="H39" t="s" s="19">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
@@ -47672,10 +47771,10 @@
     </row>
     <row r="40" ht="20.05" customHeight="1">
       <c r="A40" t="s" s="10">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="B40" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C40" s="18">
         <v>0</v>
@@ -47687,7 +47786,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="s" s="19">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
@@ -47700,10 +47799,10 @@
     </row>
     <row r="41" ht="32.05" customHeight="1">
       <c r="A41" t="s" s="10">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="B41" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C41" s="18">
         <v>0</v>
@@ -47715,7 +47814,7 @@
         <v>2</v>
       </c>
       <c r="H41" t="s" s="19">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
@@ -47728,10 +47827,10 @@
     </row>
     <row r="42" ht="32.05" customHeight="1">
       <c r="A42" t="s" s="10">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="B42" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C42" s="18">
         <v>0</v>
@@ -47743,7 +47842,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s" s="19">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12"/>
@@ -47756,10 +47855,10 @@
     </row>
     <row r="43" ht="44.05" customHeight="1">
       <c r="A43" t="s" s="10">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="B43" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C43" s="18">
         <v>0</v>
@@ -47771,7 +47870,7 @@
         <v>2</v>
       </c>
       <c r="H43" t="s" s="19">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12"/>
@@ -47784,10 +47883,10 @@
     </row>
     <row r="44" ht="20.05" customHeight="1">
       <c r="A44" t="s" s="10">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="B44" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C44" s="18">
         <v>0</v>
@@ -47799,7 +47898,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s" s="19">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
@@ -47812,10 +47911,10 @@
     </row>
     <row r="45" ht="44.05" customHeight="1">
       <c r="A45" t="s" s="10">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="B45" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C45" s="18">
         <v>0</v>
@@ -47827,7 +47926,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="s" s="19">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12"/>
@@ -47840,10 +47939,10 @@
     </row>
     <row r="46" ht="44.05" customHeight="1">
       <c r="A46" t="s" s="10">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="B46" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C46" s="18">
         <v>0</v>
@@ -47855,7 +47954,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s" s="19">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
@@ -47868,10 +47967,10 @@
     </row>
     <row r="47" ht="44.05" customHeight="1">
       <c r="A47" t="s" s="10">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="B47" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C47" s="18">
         <v>0</v>
@@ -47883,7 +47982,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s" s="19">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12"/>
@@ -47896,10 +47995,10 @@
     </row>
     <row r="48" ht="44.05" customHeight="1">
       <c r="A48" t="s" s="10">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="B48" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C48" s="18">
         <v>500</v>
@@ -47911,7 +48010,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="s" s="19">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
@@ -47924,10 +48023,10 @@
     </row>
     <row r="49" ht="32.05" customHeight="1">
       <c r="A49" t="s" s="10">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="B49" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C49" s="18">
         <v>0</v>
@@ -47939,7 +48038,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="s" s="19">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
@@ -47952,10 +48051,10 @@
     </row>
     <row r="50" ht="32.05" customHeight="1">
       <c r="A50" t="s" s="10">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="B50" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C50" s="18">
         <v>100</v>
@@ -47967,7 +48066,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s" s="19">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
@@ -47980,10 +48079,10 @@
     </row>
     <row r="51" ht="44.05" customHeight="1">
       <c r="A51" t="s" s="10">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="B51" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C51" s="18">
         <v>0</v>
@@ -47995,7 +48094,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s" s="19">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="I51" s="12"/>
       <c r="J51" s="12"/>
@@ -48008,10 +48107,10 @@
     </row>
     <row r="52" ht="32.05" customHeight="1">
       <c r="A52" t="s" s="10">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="B52" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C52" s="18">
         <v>200</v>
@@ -48023,7 +48122,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="s" s="19">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
@@ -48036,10 +48135,10 @@
     </row>
     <row r="53" ht="32.05" customHeight="1">
       <c r="A53" t="s" s="10">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="B53" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C53" s="18">
         <v>200</v>
@@ -48051,7 +48150,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="s" s="19">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="I53" s="12"/>
       <c r="J53" s="12"/>
@@ -48064,10 +48163,10 @@
     </row>
     <row r="54" ht="44.05" customHeight="1">
       <c r="A54" t="s" s="10">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="B54" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C54" s="18">
         <v>600</v>
@@ -48079,7 +48178,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="s" s="19">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
@@ -48092,10 +48191,10 @@
     </row>
     <row r="55" ht="44.05" customHeight="1">
       <c r="A55" t="s" s="10">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="B55" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C55" s="18">
         <v>500</v>
@@ -48107,7 +48206,7 @@
         <v>2</v>
       </c>
       <c r="H55" t="s" s="19">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="I55" s="12"/>
       <c r="J55" s="12"/>
@@ -48120,10 +48219,10 @@
     </row>
     <row r="56" ht="32.05" customHeight="1">
       <c r="A56" t="s" s="10">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="B56" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C56" s="18">
         <v>400</v>
@@ -48135,7 +48234,7 @@
         <v>2</v>
       </c>
       <c r="H56" t="s" s="19">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
@@ -48148,10 +48247,10 @@
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="A57" t="s" s="10">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="B57" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C57" s="18">
         <v>0</v>
@@ -48163,7 +48262,7 @@
         <v>2</v>
       </c>
       <c r="H57" t="s" s="19">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="I57" s="12"/>
       <c r="J57" s="12"/>
@@ -48176,10 +48275,10 @@
     </row>
     <row r="58" ht="32.05" customHeight="1">
       <c r="A58" t="s" s="10">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="B58" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C58" s="18">
         <v>450</v>
@@ -48191,7 +48290,7 @@
         <v>2</v>
       </c>
       <c r="H58" t="s" s="19">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="I58" s="12"/>
       <c r="J58" s="12"/>
@@ -48204,10 +48303,10 @@
     </row>
     <row r="59" ht="32.05" customHeight="1">
       <c r="A59" t="s" s="10">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="B59" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C59" s="18">
         <v>450</v>
@@ -48219,7 +48318,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="s" s="19">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="I59" s="12"/>
       <c r="J59" s="12"/>
@@ -48232,10 +48331,10 @@
     </row>
     <row r="60" ht="44.05" customHeight="1">
       <c r="A60" t="s" s="10">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="B60" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C60" s="18">
         <v>200</v>
@@ -48247,7 +48346,7 @@
         <v>4</v>
       </c>
       <c r="H60" t="s" s="19">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="I60" s="12"/>
       <c r="J60" s="12"/>
@@ -48260,10 +48359,10 @@
     </row>
     <row r="61" ht="32.05" customHeight="1">
       <c r="A61" t="s" s="10">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="B61" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C61" s="18">
         <v>700</v>
@@ -48275,7 +48374,7 @@
         <v>5</v>
       </c>
       <c r="H61" t="s" s="19">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="I61" s="12"/>
       <c r="J61" s="12"/>
@@ -48288,10 +48387,10 @@
     </row>
     <row r="62" ht="44.05" customHeight="1">
       <c r="A62" t="s" s="10">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="B62" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C62" s="18">
         <v>0</v>
@@ -48303,7 +48402,7 @@
         <v>2</v>
       </c>
       <c r="H62" t="s" s="19">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="I62" s="12"/>
       <c r="J62" s="12"/>
@@ -48316,10 +48415,10 @@
     </row>
     <row r="63" ht="32.05" customHeight="1">
       <c r="A63" t="s" s="10">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B63" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C63" s="18">
         <v>0</v>
@@ -48331,7 +48430,7 @@
         <v>4</v>
       </c>
       <c r="H63" t="s" s="19">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
@@ -48344,10 +48443,10 @@
     </row>
     <row r="64" ht="32.05" customHeight="1">
       <c r="A64" t="s" s="10">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="B64" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C64" s="18">
         <v>0</v>
@@ -48359,7 +48458,7 @@
         <v>4</v>
       </c>
       <c r="H64" t="s" s="19">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="I64" s="12"/>
       <c r="J64" s="12"/>
@@ -48372,10 +48471,10 @@
     </row>
     <row r="65" ht="56.05" customHeight="1">
       <c r="A65" t="s" s="10">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="B65" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C65" s="18">
         <v>1000</v>
@@ -48387,7 +48486,7 @@
         <v>3</v>
       </c>
       <c r="H65" t="s" s="19">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
@@ -48400,10 +48499,10 @@
     </row>
     <row r="66" ht="44.05" customHeight="1">
       <c r="A66" t="s" s="10">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="B66" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C66" s="18">
         <v>800</v>
@@ -48415,7 +48514,7 @@
         <v>2</v>
       </c>
       <c r="H66" t="s" s="19">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="I66" s="12"/>
       <c r="J66" s="12"/>
@@ -48428,10 +48527,10 @@
     </row>
     <row r="67" ht="32.05" customHeight="1">
       <c r="A67" t="s" s="10">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="B67" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C67" s="18">
         <v>1000</v>
@@ -48443,7 +48542,7 @@
         <v>5</v>
       </c>
       <c r="H67" t="s" s="19">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
@@ -48456,10 +48555,10 @@
     </row>
     <row r="68" ht="56.05" customHeight="1">
       <c r="A68" t="s" s="10">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="B68" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C68" s="18">
         <v>1500</v>
@@ -48471,7 +48570,7 @@
         <v>3</v>
       </c>
       <c r="H68" t="s" s="19">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="I68" s="12"/>
       <c r="J68" s="12"/>
@@ -48484,10 +48583,10 @@
     </row>
     <row r="69" ht="44.05" customHeight="1">
       <c r="A69" t="s" s="10">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="B69" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C69" s="18">
         <v>1000</v>
@@ -48499,7 +48598,7 @@
         <v>2</v>
       </c>
       <c r="H69" t="s" s="19">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
@@ -48512,10 +48611,10 @@
     </row>
     <row r="70" ht="32.05" customHeight="1">
       <c r="A70" t="s" s="10">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="B70" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C70" s="18">
         <v>300</v>
@@ -48527,7 +48626,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="s" s="19">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="I70" s="12"/>
       <c r="J70" s="12"/>
@@ -48540,10 +48639,10 @@
     </row>
     <row r="71" ht="32.05" customHeight="1">
       <c r="A71" t="s" s="10">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="B71" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C71" s="18">
         <v>300</v>
@@ -48555,7 +48654,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="s" s="19">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
@@ -48568,10 +48667,10 @@
     </row>
     <row r="72" ht="32.05" customHeight="1">
       <c r="A72" t="s" s="10">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="B72" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C72" s="18">
         <v>500</v>
@@ -48583,7 +48682,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s" s="19">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="I72" s="12"/>
       <c r="J72" s="12"/>
@@ -48596,10 +48695,10 @@
     </row>
     <row r="73" ht="44.05" customHeight="1">
       <c r="A73" t="s" s="10">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="B73" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C73" s="18">
         <v>2000</v>
@@ -48611,7 +48710,7 @@
         <v>4</v>
       </c>
       <c r="H73" t="s" s="19">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
@@ -48624,10 +48723,10 @@
     </row>
     <row r="74" ht="44.05" customHeight="1">
       <c r="A74" t="s" s="10">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="B74" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C74" s="18">
         <v>2000</v>
@@ -48639,7 +48738,7 @@
         <v>5</v>
       </c>
       <c r="H74" t="s" s="19">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="I74" s="12"/>
       <c r="J74" s="12"/>
@@ -48652,10 +48751,10 @@
     </row>
     <row r="75" ht="44.05" customHeight="1">
       <c r="A75" t="s" s="10">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="B75" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C75" s="18">
         <v>2000</v>
@@ -48667,7 +48766,7 @@
         <v>5</v>
       </c>
       <c r="H75" t="s" s="19">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
@@ -48680,10 +48779,10 @@
     </row>
     <row r="76" ht="44.05" customHeight="1">
       <c r="A76" t="s" s="10">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="B76" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C76" s="18">
         <v>2000</v>
@@ -48695,7 +48794,7 @@
         <v>5</v>
       </c>
       <c r="H76" t="s" s="19">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="I76" s="12"/>
       <c r="J76" s="12"/>
@@ -48708,10 +48807,10 @@
     </row>
     <row r="77" ht="44.05" customHeight="1">
       <c r="A77" t="s" s="10">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="B77" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C77" s="18">
         <v>2000</v>
@@ -48723,7 +48822,7 @@
         <v>5</v>
       </c>
       <c r="H77" t="s" s="19">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="I77" s="12"/>
       <c r="J77" s="12"/>
@@ -48736,10 +48835,10 @@
     </row>
     <row r="78" ht="44.05" customHeight="1">
       <c r="A78" t="s" s="10">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="B78" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C78" s="18">
         <v>2000</v>
@@ -48751,7 +48850,7 @@
         <v>5</v>
       </c>
       <c r="H78" t="s" s="19">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="I78" s="12"/>
       <c r="J78" s="12"/>
@@ -48764,10 +48863,10 @@
     </row>
     <row r="79" ht="44.05" customHeight="1">
       <c r="A79" t="s" s="10">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="B79" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C79" s="18">
         <v>2000</v>
@@ -48779,7 +48878,7 @@
         <v>5</v>
       </c>
       <c r="H79" t="s" s="19">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="I79" s="12"/>
       <c r="J79" s="12"/>
@@ -48792,10 +48891,10 @@
     </row>
     <row r="80" ht="20.05" customHeight="1">
       <c r="A80" t="s" s="10">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="B80" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C80" s="18">
         <v>1200</v>
@@ -48807,7 +48906,7 @@
         <v>4</v>
       </c>
       <c r="H80" t="s" s="19">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="I80" s="12"/>
       <c r="J80" s="12"/>
@@ -48820,10 +48919,10 @@
     </row>
     <row r="81" ht="44.05" customHeight="1">
       <c r="A81" t="s" s="10">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="B81" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C81" s="18">
         <v>2000</v>
@@ -48835,7 +48934,7 @@
         <v>3</v>
       </c>
       <c r="H81" t="s" s="19">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="I81" s="12"/>
       <c r="J81" s="12"/>
@@ -48848,10 +48947,10 @@
     </row>
     <row r="82" ht="32.05" customHeight="1">
       <c r="A82" t="s" s="10">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="B82" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C82" s="18">
         <v>1000</v>
@@ -48863,7 +48962,7 @@
         <v>3</v>
       </c>
       <c r="H82" t="s" s="19">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="I82" s="12"/>
       <c r="J82" s="12"/>
@@ -48876,10 +48975,10 @@
     </row>
     <row r="83" ht="32.05" customHeight="1">
       <c r="A83" t="s" s="10">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="B83" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C83" s="18">
         <v>500</v>
@@ -48891,7 +48990,7 @@
         <v>2</v>
       </c>
       <c r="H83" t="s" s="19">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="I83" s="12"/>
       <c r="J83" s="12"/>
@@ -48904,10 +49003,10 @@
     </row>
     <row r="84" ht="32.05" customHeight="1">
       <c r="A84" t="s" s="10">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="B84" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C84" s="18">
         <v>250</v>
@@ -48919,7 +49018,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="s" s="19">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="I84" s="12"/>
       <c r="J84" s="12"/>
@@ -48932,10 +49031,10 @@
     </row>
     <row r="85" ht="56.05" customHeight="1">
       <c r="A85" t="s" s="10">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="B85" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C85" s="18">
         <v>1500</v>
@@ -48947,7 +49046,7 @@
         <v>4</v>
       </c>
       <c r="H85" t="s" s="19">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="I85" s="12"/>
       <c r="J85" s="12"/>
@@ -48960,10 +49059,10 @@
     </row>
     <row r="86" ht="32.05" customHeight="1">
       <c r="A86" t="s" s="10">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="B86" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C86" s="18">
         <v>1000</v>
@@ -48975,7 +49074,7 @@
         <v>3</v>
       </c>
       <c r="H86" t="s" s="19">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="I86" s="12"/>
       <c r="J86" s="12"/>
@@ -48988,10 +49087,10 @@
     </row>
     <row r="87" ht="44.05" customHeight="1">
       <c r="A87" t="s" s="10">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="B87" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C87" s="18">
         <v>800</v>
@@ -49003,7 +49102,7 @@
         <v>2</v>
       </c>
       <c r="H87" t="s" s="19">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="I87" s="12"/>
       <c r="J87" s="12"/>
@@ -49016,10 +49115,10 @@
     </row>
     <row r="88" ht="20.05" customHeight="1">
       <c r="A88" t="s" s="10">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="B88" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C88" s="18">
         <v>200</v>
@@ -49031,7 +49130,7 @@
         <v>2</v>
       </c>
       <c r="H88" t="s" s="19">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="I88" s="12"/>
       <c r="J88" s="12"/>
@@ -49044,10 +49143,10 @@
     </row>
     <row r="89" ht="32.05" customHeight="1">
       <c r="A89" t="s" s="10">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="B89" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C89" s="18">
         <v>1500</v>
@@ -49059,7 +49158,7 @@
         <v>3</v>
       </c>
       <c r="H89" t="s" s="19">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="I89" s="12"/>
       <c r="J89" s="12"/>
@@ -49072,10 +49171,10 @@
     </row>
     <row r="90" ht="44.05" customHeight="1">
       <c r="A90" t="s" s="10">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="B90" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C90" s="18">
         <v>500</v>
@@ -49087,7 +49186,7 @@
         <v>5</v>
       </c>
       <c r="H90" t="s" s="19">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="I90" s="12"/>
       <c r="J90" s="12"/>
@@ -49100,10 +49199,10 @@
     </row>
     <row r="91" ht="56.05" customHeight="1">
       <c r="A91" t="s" s="10">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="B91" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C91" s="18">
         <v>1000</v>
@@ -49115,11 +49214,11 @@
         <v>2</v>
       </c>
       <c r="H91" t="s" s="19">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="I91" s="12"/>
       <c r="J91" t="s" s="19">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="K91" s="12"/>
       <c r="L91" s="12"/>
@@ -49130,10 +49229,10 @@
     </row>
     <row r="92" ht="32.05" customHeight="1">
       <c r="A92" t="s" s="10">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="B92" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C92" s="18">
         <v>1500</v>
@@ -49145,7 +49244,7 @@
         <v>4</v>
       </c>
       <c r="H92" t="s" s="19">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="I92" s="12"/>
       <c r="J92" s="12"/>
@@ -49158,10 +49257,10 @@
     </row>
     <row r="93" ht="44.05" customHeight="1">
       <c r="A93" t="s" s="10">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="B93" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C93" s="18">
         <v>300</v>
@@ -49173,7 +49272,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="s" s="19">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="I93" s="12"/>
       <c r="J93" s="12"/>
@@ -49186,10 +49285,10 @@
     </row>
     <row r="94" ht="56.05" customHeight="1">
       <c r="A94" t="s" s="10">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="B94" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C94" s="18">
         <v>200</v>
@@ -49201,7 +49300,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="s" s="19">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="I94" s="12"/>
       <c r="J94" s="12"/>
@@ -49214,10 +49313,10 @@
     </row>
     <row r="95" ht="44.05" customHeight="1">
       <c r="A95" t="s" s="10">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="B95" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C95" s="18">
         <v>0</v>
@@ -49229,7 +49328,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="s" s="19">
-        <v>1370</v>
+        <v>1375</v>
       </c>
       <c r="I95" s="12"/>
       <c r="J95" s="12"/>
@@ -49242,10 +49341,10 @@
     </row>
     <row r="96" ht="32.05" customHeight="1">
       <c r="A96" t="s" s="10">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="B96" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C96" s="18">
         <v>0</v>
@@ -49257,7 +49356,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="s" s="19">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="I96" s="12"/>
       <c r="J96" s="12"/>
@@ -49270,10 +49369,10 @@
     </row>
     <row r="97" ht="44.05" customHeight="1">
       <c r="A97" t="s" s="10">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="B97" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C97" s="18">
         <v>1000</v>
@@ -49285,7 +49384,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="s" s="19">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="I97" s="12"/>
       <c r="J97" s="12"/>
@@ -49298,10 +49397,10 @@
     </row>
     <row r="98" ht="32.05" customHeight="1">
       <c r="A98" t="s" s="10">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="B98" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C98" s="18">
         <v>0</v>
@@ -49313,7 +49412,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="s" s="19">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="I98" s="12"/>
       <c r="J98" s="12"/>
@@ -49326,10 +49425,10 @@
     </row>
     <row r="99" ht="32.05" customHeight="1">
       <c r="A99" t="s" s="10">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="B99" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C99" s="18">
         <v>0</v>
@@ -49341,7 +49440,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="s" s="19">
-        <v>1378</v>
+        <v>1383</v>
       </c>
       <c r="I99" s="12"/>
       <c r="J99" s="12"/>
@@ -49354,10 +49453,10 @@
     </row>
     <row r="100" ht="44.05" customHeight="1">
       <c r="A100" t="s" s="10">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="B100" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C100" s="18">
         <v>500</v>
@@ -49369,7 +49468,7 @@
         <v>2</v>
       </c>
       <c r="H100" t="s" s="19">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="I100" s="12"/>
       <c r="J100" s="12"/>
@@ -49382,10 +49481,10 @@
     </row>
     <row r="101" ht="44.05" customHeight="1">
       <c r="A101" t="s" s="10">
-        <v>1381</v>
+        <v>1386</v>
       </c>
       <c r="B101" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C101" s="18">
         <v>0</v>
@@ -49397,7 +49496,7 @@
         <v>2</v>
       </c>
       <c r="H101" t="s" s="19">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="I101" s="12"/>
       <c r="J101" s="12"/>
@@ -49410,10 +49509,10 @@
     </row>
     <row r="102" ht="44.05" customHeight="1">
       <c r="A102" t="s" s="10">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="B102" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C102" s="18">
         <v>600</v>
@@ -49425,7 +49524,7 @@
         <v>2</v>
       </c>
       <c r="H102" t="s" s="19">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="I102" s="12"/>
       <c r="J102" s="12"/>
@@ -49438,10 +49537,10 @@
     </row>
     <row r="103" ht="56.05" customHeight="1">
       <c r="A103" t="s" s="10">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="B103" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C103" s="18">
         <v>500</v>
@@ -49453,7 +49552,7 @@
         <v>2</v>
       </c>
       <c r="H103" t="s" s="19">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="I103" s="12"/>
       <c r="J103" s="12"/>
@@ -49466,10 +49565,10 @@
     </row>
     <row r="104" ht="44.05" customHeight="1">
       <c r="A104" t="s" s="10">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="B104" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C104" s="18">
         <v>2000</v>
@@ -49481,7 +49580,7 @@
         <v>4</v>
       </c>
       <c r="H104" t="s" s="19">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="I104" s="12"/>
       <c r="J104" t="s" s="19">
@@ -49496,10 +49595,10 @@
     </row>
     <row r="105" ht="32.05" customHeight="1">
       <c r="A105" t="s" s="10">
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="B105" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C105" s="18">
         <v>1500</v>
@@ -49511,7 +49610,7 @@
         <v>4</v>
       </c>
       <c r="H105" t="s" s="19">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="I105" s="12"/>
       <c r="J105" s="12"/>
@@ -49524,10 +49623,10 @@
     </row>
     <row r="106" ht="32.05" customHeight="1">
       <c r="A106" t="s" s="10">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="B106" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C106" s="18">
         <v>0</v>
@@ -49539,7 +49638,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="s" s="19">
-        <v>1392</v>
+        <v>1397</v>
       </c>
       <c r="I106" s="12"/>
       <c r="J106" s="12"/>
@@ -49552,10 +49651,10 @@
     </row>
     <row r="107" ht="68.05" customHeight="1">
       <c r="A107" t="s" s="10">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="B107" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C107" s="18">
         <v>2000</v>
@@ -49567,7 +49666,7 @@
         <v>3</v>
       </c>
       <c r="H107" t="s" s="19">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="I107" s="12"/>
       <c r="J107" s="12"/>
@@ -49580,10 +49679,10 @@
     </row>
     <row r="108" ht="44.05" customHeight="1">
       <c r="A108" t="s" s="10">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="B108" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C108" s="18">
         <v>300</v>
@@ -49593,7 +49692,7 @@
       <c r="F108" s="12"/>
       <c r="G108" s="12"/>
       <c r="H108" t="s" s="19">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="I108" s="12"/>
       <c r="J108" s="12"/>
@@ -49606,10 +49705,10 @@
     </row>
     <row r="109" ht="56.05" customHeight="1">
       <c r="A109" t="s" s="10">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="B109" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C109" s="18">
         <v>800</v>
@@ -49619,7 +49718,7 @@
       <c r="F109" s="12"/>
       <c r="G109" s="12"/>
       <c r="H109" t="s" s="19">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="I109" s="12"/>
       <c r="J109" s="12"/>
@@ -49632,10 +49731,10 @@
     </row>
     <row r="110" ht="56.05" customHeight="1">
       <c r="A110" t="s" s="10">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="B110" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C110" s="18">
         <v>600</v>
@@ -49645,7 +49744,7 @@
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
       <c r="H110" t="s" s="19">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="I110" s="12"/>
       <c r="J110" s="12"/>
@@ -49658,10 +49757,10 @@
     </row>
     <row r="111" ht="56.05" customHeight="1">
       <c r="A111" t="s" s="10">
-        <v>1401</v>
+        <v>1406</v>
       </c>
       <c r="B111" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C111" s="18">
         <v>300</v>
@@ -49671,7 +49770,7 @@
       <c r="F111" s="12"/>
       <c r="G111" s="12"/>
       <c r="H111" t="s" s="19">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="I111" s="12"/>
       <c r="J111" s="12"/>
@@ -49684,10 +49783,10 @@
     </row>
     <row r="112" ht="32.05" customHeight="1">
       <c r="A112" t="s" s="10">
-        <v>1403</v>
+        <v>1408</v>
       </c>
       <c r="B112" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C112" s="18">
         <v>500</v>
@@ -49697,7 +49796,7 @@
       <c r="F112" s="12"/>
       <c r="G112" s="12"/>
       <c r="H112" t="s" s="19">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="I112" s="12"/>
       <c r="J112" s="12"/>
@@ -49710,10 +49809,10 @@
     </row>
     <row r="113" ht="44.05" customHeight="1">
       <c r="A113" t="s" s="10">
-        <v>1405</v>
+        <v>1410</v>
       </c>
       <c r="B113" t="s" s="11">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C113" s="18">
         <v>1000</v>
@@ -49723,7 +49822,7 @@
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
       <c r="H113" t="s" s="19">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="I113" s="12"/>
       <c r="J113" s="12"/>
@@ -49734,23 +49833,35 @@
       <c r="O113" s="12"/>
       <c r="P113" s="12"/>
     </row>
-    <row r="114" ht="20.05" customHeight="1">
-      <c r="A114" s="13"/>
-      <c r="B114" s="14"/>
-      <c r="C114" s="12"/>
+    <row r="114" ht="26.7" customHeight="1">
+      <c r="A114" t="s" s="10">
+        <v>1412</v>
+      </c>
+      <c r="B114" t="s" s="11">
+        <v>1189</v>
+      </c>
+      <c r="C114" s="18">
+        <v>1000</v>
+      </c>
       <c r="D114" s="12"/>
       <c r="E114" s="12"/>
       <c r="F114" s="12"/>
       <c r="G114" s="12"/>
-      <c r="H114" s="12"/>
+      <c r="H114" t="s" s="19">
+        <v>1413</v>
+      </c>
       <c r="I114" s="12"/>
       <c r="J114" s="12"/>
       <c r="K114" s="12"/>
-      <c r="L114" s="12"/>
+      <c r="L114" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M114" s="12"/>
       <c r="N114" s="12"/>
       <c r="O114" s="12"/>
-      <c r="P114" s="12"/>
+      <c r="P114" t="s" s="19">
+        <v>35</v>
+      </c>
     </row>
     <row r="115" ht="20.05" customHeight="1">
       <c r="A115" s="13"/>
@@ -57747,21 +57858,21 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="24">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="C2" t="s" s="24">
-        <v>1408</v>
+        <v>1415</v>
       </c>
       <c r="D2" t="s" s="24">
-        <v>1409</v>
+        <v>1416</v>
       </c>
       <c r="E2" t="s" s="24">
-        <v>1410</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="3" ht="16.55" customHeight="1">
       <c r="A3" t="s" s="25">
-        <v>1411</v>
+        <v>1418</v>
       </c>
       <c r="B3" s="26">
         <v>52</v>
@@ -57770,16 +57881,16 @@
         <v>0.347</v>
       </c>
       <c r="D3" t="s" s="28">
-        <v>1412</v>
+        <v>1419</v>
       </c>
       <c r="E3" s="29">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$568,"Yes",'Unit'!$G$3:$G$568,1)+_xlfn.COUNTIFS('Trap'!$J$3:$J$545,"Yes",'Trap'!$G$3:$G$545,1)+_xlfn.COUNTIFS('Tech'!$J$3:$J$556,"Yes",'Tech'!$G$3:$G$556,1)</f>
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" ht="16.35" customHeight="1">
       <c r="A4" t="s" s="30">
-        <v>1413</v>
+        <v>1420</v>
       </c>
       <c r="B4" s="31">
         <v>48</v>
@@ -57788,16 +57899,16 @@
         <v>0.337</v>
       </c>
       <c r="D4" t="s" s="33">
-        <v>1414</v>
+        <v>1421</v>
       </c>
       <c r="E4" s="34">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$568,"Yes",'Unit'!$G$3:$G$568,2)+_xlfn.COUNTIFS('Trap'!$J$3:$J$545,"Yes",'Trap'!$G$3:$G$545,2)+_xlfn.COUNTIFS('Tech'!$J$3:$J$556,"Yes",'Tech'!$G$3:$G$556,2)</f>
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" ht="16.35" customHeight="1">
       <c r="A5" t="s" s="30">
-        <v>1415</v>
+        <v>1422</v>
       </c>
       <c r="B5" s="31">
         <v>27</v>
@@ -57806,16 +57917,16 @@
         <v>0.167</v>
       </c>
       <c r="D5" t="s" s="33">
-        <v>1414</v>
+        <v>1421</v>
       </c>
       <c r="E5" s="34">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$568,"Yes",'Unit'!$G$3:$G$568,3)+_xlfn.COUNTIFS('Trap'!$J$3:$J$545,"Yes",'Trap'!$G$3:$G$545,3)+_xlfn.COUNTIFS('Tech'!$J$3:$J$556,"Yes",'Tech'!$G$3:$G$556,3)</f>
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" ht="30.35" customHeight="1">
       <c r="A6" t="s" s="30">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="B6" s="31">
         <v>16</v>
@@ -57824,16 +57935,16 @@
         <v>0.1</v>
       </c>
       <c r="D6" t="s" s="33">
-        <v>1417</v>
+        <v>1424</v>
       </c>
       <c r="E6" s="34">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$568,"Yes",'Unit'!$G$3:$G$568,4)+_xlfn.COUNTIFS('Trap'!$J$3:$J$545,"Yes",'Trap'!$G$3:$G$545,4)+_xlfn.COUNTIFS('Tech'!$J$3:$J$556,"Yes",'Tech'!$G$3:$G$556,4)</f>
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="16.35" customHeight="1">
       <c r="A7" t="s" s="35">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="B7" s="36">
         <v>9</v>
@@ -57842,7 +57953,7 @@
         <v>0.053</v>
       </c>
       <c r="D7" t="s" s="33">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="E7" s="34">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$568,"Yes",'Unit'!$G$3:$G$568,5)+_xlfn.COUNTIFS('Trap'!$J$3:$J$545,"Yes",'Trap'!$G$3:$G$545,5)+_xlfn.COUNTIFS('Tech'!$J$3:$J$556,"Yes",'Tech'!$G$3:$G$556,5)</f>
@@ -57875,17 +57986,17 @@
         <v>22</v>
       </c>
       <c r="B11" t="s" s="43">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="C11" s="44"/>
       <c r="D11" s="44"/>
       <c r="E11" t="s" s="45">
-        <v>1410</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="12" ht="16.35" customHeight="1">
       <c r="A12" t="s" s="30">
-        <v>1420</v>
+        <v>1427</v>
       </c>
       <c r="B12" s="31">
         <v>60</v>
@@ -57893,13 +58004,13 @@
       <c r="C12" s="41"/>
       <c r="D12" s="41"/>
       <c r="E12" s="34">
-        <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes")+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes")+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes")</f>
-        <v>167</v>
+        <f>_xlfn.COUNTIFS('Unit'!$N$3:$N$568,"Yes")+_xlfn.COUNTIFS('Trap'!$N$3:$N$545,"Yes")+_xlfn.COUNTIFS('Tech'!$N$3:$N$556,"Yes")</f>
+        <v>60</v>
       </c>
     </row>
     <row r="13" ht="16.35" customHeight="1">
       <c r="A13" t="s" s="30">
-        <v>1421</v>
+        <v>1428</v>
       </c>
       <c r="B13" s="31">
         <v>60</v>
@@ -57907,13 +58018,13 @@
       <c r="C13" s="41"/>
       <c r="D13" s="41"/>
       <c r="E13" s="34">
-        <f>_xlfn.COUNTIFS('Unit'!$M$3:$M$568,"Yes")+_xlfn.COUNTIFS('Trap'!$M$3:$M$545,"Yes")+_xlfn.COUNTIFS('Tech'!$M$3:$M$556,"Yes")</f>
-        <v>0</v>
+        <f>_xlfn.COUNTIFS('Unit'!$O$3:$O$568,"Yes")+_xlfn.COUNTIFS('Trap'!$O$3:$O$545,"Yes")+_xlfn.COUNTIFS('Tech'!$O$3:$O$556,"Yes")</f>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="16.35" customHeight="1">
       <c r="A14" t="s" s="30">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="B14" s="31">
         <v>60</v>
@@ -57921,7 +58032,7 @@
       <c r="C14" s="41"/>
       <c r="D14" s="41"/>
       <c r="E14" s="34">
-        <f>_xlfn.COUNTIFS('Unit'!$N$3:$N$568,"Yes")+_xlfn.COUNTIFS('Trap'!$N$3:$N$545,"Yes")+_xlfn.COUNTIFS('Tech'!$N$3:$N$556,"Yes")</f>
+        <f>_xlfn.COUNTIFS('Unit'!$P$3:$P$568,"Yes")+_xlfn.COUNTIFS('Trap'!$P$3:$P$545,"Yes")+_xlfn.COUNTIFS('Tech'!$P$3:$P$556,"Yes")</f>
         <v>60</v>
       </c>
     </row>
@@ -57961,10 +58072,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" t="s" s="5">
-        <v>1423</v>
+        <v>1430</v>
       </c>
       <c r="C2" t="s" s="5">
-        <v>1424</v>
+        <v>1431</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -57974,10 +58085,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="C3" t="s" s="17">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -57987,10 +58098,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>1427</v>
+        <v>1434</v>
       </c>
       <c r="C4" t="s" s="19">
-        <v>1428</v>
+        <v>1435</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -58000,10 +58111,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>1429</v>
+        <v>1436</v>
       </c>
       <c r="C5" t="s" s="19">
-        <v>1430</v>
+        <v>1437</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
@@ -58013,10 +58124,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>1431</v>
+        <v>1438</v>
       </c>
       <c r="C6" t="s" s="19">
-        <v>1431</v>
+        <v>1438</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -58026,10 +58137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>1432</v>
+        <v>1439</v>
       </c>
       <c r="C7" t="s" s="19">
-        <v>1433</v>
+        <v>1440</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
@@ -58039,10 +58150,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>1434</v>
+        <v>1441</v>
       </c>
       <c r="C8" t="s" s="19">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
@@ -58052,10 +58163,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>1436</v>
+        <v>1443</v>
       </c>
       <c r="C9" t="s" s="19">
-        <v>1437</v>
+        <v>1444</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
@@ -58065,10 +58176,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>1438</v>
+        <v>1445</v>
       </c>
       <c r="C10" t="s" s="19">
-        <v>1439</v>
+        <v>1446</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>

--- a/context/card_data.xlsx
+++ b/context/card_data.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2102">
   <si>
     <t>Table 1</t>
   </si>
@@ -391,7 +391,7 @@
     <t>Ice Mage</t>
   </si>
   <si>
-    <t>Asteroid Trooper</t>
+    <t>Star Hunter</t>
   </si>
   <si>
     <t>Slim Gray Tank</t>
@@ -877,7 +877,7 @@
     <t>Skeleton Sickleman</t>
   </si>
   <si>
-    <t>Human Dog</t>
+    <t>Kappa</t>
   </si>
   <si>
     <t>+10 ATK if there is Anima or Nature card on your side</t>
@@ -1207,7 +1207,7 @@
     <t>Mad Raccoon</t>
   </si>
   <si>
-    <t>Armored Monkey</t>
+    <t>Armored Cat</t>
   </si>
   <si>
     <t>+10 ATK if there is another exposed Nature card</t>
@@ -1678,10 +1678,10 @@
     <t>Zetamas the Great Summoner</t>
   </si>
   <si>
-    <t>At the end of your turn: create a token copy of Leviathan on an empty cell on your side</t>
-  </si>
-  <si>
-    <t>Ethereal Shielder</t>
+    <t>When this card is exposed, you can choose to summon 1 Mad Wyvern token on any of your cell.</t>
+  </si>
+  <si>
+    <t>Ethereal Soldiers</t>
   </si>
   <si>
     <t>Once per turn, this card cannot be destroyed vs Non-Arcane</t>
@@ -1762,7 +1762,7 @@
     <t>Sweet Lure Pod</t>
   </si>
   <si>
-    <t>This turn, foe can only target this card for an attack.</t>
+    <t>Foe can only target this exposed card for an attack.</t>
   </si>
   <si>
     <t>Radiaghoul</t>
@@ -1825,16 +1825,16 @@
     <t>S-02 the Hatcher</t>
   </si>
   <si>
-    <t>Once at foe’s turn end, create a token on an empty cell with 0 ATK&amp;DEF and no ability.</t>
-  </si>
-  <si>
-    <t>Rotten Shrieker</t>
+    <t>Once at foe’s turn end, create a token on an empty cell with 0 ATK&amp;DEF, no cost, and no ability</t>
+  </si>
+  <si>
+    <t>Rotten Spider</t>
   </si>
   <si>
     <t>Without Mutagen Flag : -10 ATK permanently at the end of your turn.</t>
   </si>
   <si>
-    <t>Toxin Folk</t>
+    <t>Toxin Eater</t>
   </si>
   <si>
     <t>While this card is exposed, foe that perform attack get -5 ATK until the end of foe’s turn.</t>
@@ -1891,10 +1891,10 @@
     <t>After successfully attacking, flip a coin, if head, gain 50 Crystal</t>
   </si>
   <si>
-    <t>Epsilon The Wither</t>
-  </si>
-  <si>
-    <t>At Reckoning, +40 ATK&amp;DEF until this turn ends, but all ally units lose 10 ATK&amp;DEF until this turn ends</t>
+    <t>Epsilon The Withered</t>
+  </si>
+  <si>
+    <t>At Reckoning, +40 ATK&amp;DEF until this turn ends, but all ally units lose 40 ATK&amp;DEF until foe’s turn ends</t>
   </si>
   <si>
     <t>Plaguespreader</t>
@@ -1903,7 +1903,7 @@
     <t>With Mutagen Flag : At the end of your turn, put 1 Mutagen Flag on one of your exposed card.</t>
   </si>
   <si>
-    <t>Black Worms</t>
+    <t>Slug-11</t>
   </si>
   <si>
     <t>At your turn’s end, foe loses 300 Crystals for each Mutagen flag on the field</t>
@@ -2026,10 +2026,10 @@
     <t>Exposed: Reveal 1 of your own cells</t>
   </si>
   <si>
-    <t>Aembar the Intel Dealer</t>
-  </si>
-  <si>
-    <t>Any player use Tech card, they reveal 1 cell on their field. Usable face-down.</t>
+    <t>Aembar the Intel Broker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any player lose or pay crystals, they reveal 1 cell on their field. Usable face-down. </t>
   </si>
   <si>
     <t>Tholin Lobster</t>
@@ -6762,6 +6762,12 @@
   </si>
   <si>
     <t>Relocate two of foe’s face-up units</t>
+  </si>
+  <si>
+    <t>Lex Purgatoria</t>
+  </si>
+  <si>
+    <t>Until the end of foe’s turn, destroy any Arcane unit in Reckoning with Anima units.</t>
   </si>
   <si>
     <t>Expected</t>
@@ -20501,7 +20507,7 @@
         <v>33</v>
       </c>
       <c r="C296" s="18">
-        <v>1200</v>
+        <v>820</v>
       </c>
       <c r="D296" s="18">
         <v>55</v>
@@ -20519,7 +20525,9 @@
         <v>549</v>
       </c>
       <c r="I296" s="12"/>
-      <c r="J296" s="12"/>
+      <c r="J296" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K296" s="18">
         <f>(D296*6)+(E296*4)</f>
         <v>670</v>
@@ -20556,7 +20564,9 @@
         <v>551</v>
       </c>
       <c r="I297" s="12"/>
-      <c r="J297" s="12"/>
+      <c r="J297" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K297" s="18">
         <f>(D297*6)+(E297*4)</f>
         <v>540</v>
@@ -20567,7 +20577,7 @@
       <c r="O297" s="12"/>
       <c r="P297" s="12"/>
     </row>
-    <row r="298" ht="44.05" customHeight="1">
+    <row r="298" ht="56.4" customHeight="1">
       <c r="A298" t="s" s="10">
         <v>552</v>
       </c>
@@ -20575,13 +20585,13 @@
         <v>33</v>
       </c>
       <c r="C298" s="18">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="D298" s="18">
         <v>0</v>
       </c>
       <c r="E298" s="18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F298" t="s" s="19">
         <v>7</v>
@@ -20593,10 +20603,12 @@
         <v>553</v>
       </c>
       <c r="I298" s="12"/>
-      <c r="J298" s="12"/>
+      <c r="J298" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K298" s="18">
         <f>(D298*6)+(E298*4)</f>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="L298" s="12"/>
       <c r="M298" s="12"/>
@@ -20630,7 +20642,9 @@
         <v>555</v>
       </c>
       <c r="I299" s="12"/>
-      <c r="J299" s="12"/>
+      <c r="J299" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K299" s="18">
         <f>(D299*6)+(E299*4)</f>
         <v>470</v>
@@ -20667,7 +20681,9 @@
         <v>557</v>
       </c>
       <c r="I300" s="12"/>
-      <c r="J300" s="12"/>
+      <c r="J300" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K300" s="18">
         <f>(D300*6)+(E300*4)</f>
         <v>1190</v>
@@ -20704,7 +20720,9 @@
         <v>559</v>
       </c>
       <c r="I301" s="12"/>
-      <c r="J301" s="12"/>
+      <c r="J301" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K301" s="18">
         <f>(D301*6)+(E301*4)</f>
         <v>1580</v>
@@ -20741,7 +20759,9 @@
         <v>561</v>
       </c>
       <c r="I302" s="12"/>
-      <c r="J302" s="12"/>
+      <c r="J302" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K302" s="18">
         <f>(D302*6)+(E302*4)</f>
         <v>870</v>
@@ -20763,10 +20783,10 @@
         <v>2000</v>
       </c>
       <c r="D303" s="18">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E303" s="18">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F303" t="s" s="19">
         <v>7</v>
@@ -20778,10 +20798,12 @@
         <v>563</v>
       </c>
       <c r="I303" s="12"/>
-      <c r="J303" s="12"/>
+      <c r="J303" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K303" s="18">
         <f>(D303*6)+(E303*4)</f>
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="L303" s="12"/>
       <c r="M303" s="12"/>
@@ -20901,7 +20923,9 @@
         <v>39</v>
       </c>
       <c r="I306" s="12"/>
-      <c r="J306" s="12"/>
+      <c r="J306" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K306" s="18">
         <f>(D306*6)+(E306*4)</f>
         <v>150</v>
@@ -20981,7 +21005,9 @@
         <v>39</v>
       </c>
       <c r="I308" s="12"/>
-      <c r="J308" s="12"/>
+      <c r="J308" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K308" s="18">
         <f>(D308*6)+(E308*4)</f>
         <v>220</v>
@@ -21061,7 +21087,9 @@
         <v>575</v>
       </c>
       <c r="I310" s="12"/>
-      <c r="J310" s="12"/>
+      <c r="J310" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K310" s="18">
         <f>(D310*6)+(E310*4)</f>
         <v>100</v>
@@ -21139,7 +21167,9 @@
         <v>579</v>
       </c>
       <c r="I312" s="12"/>
-      <c r="J312" s="12"/>
+      <c r="J312" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K312" s="18">
         <f>(D312*6)+(E312*4)</f>
         <v>140</v>
@@ -21176,7 +21206,9 @@
         <v>581</v>
       </c>
       <c r="I313" s="12"/>
-      <c r="J313" s="12"/>
+      <c r="J313" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K313" s="18">
         <f>(D313*6)+(E313*4)</f>
         <v>120</v>
@@ -21342,7 +21374,9 @@
         <v>589</v>
       </c>
       <c r="I317" s="12"/>
-      <c r="J317" s="12"/>
+      <c r="J317" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K317" s="18">
         <f>(D317*6)+(E317*4)</f>
         <v>0</v>
@@ -21422,7 +21456,9 @@
         <v>39</v>
       </c>
       <c r="I319" s="12"/>
-      <c r="J319" s="12"/>
+      <c r="J319" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K319" s="18">
         <f>(D319*6)+(E319*4)</f>
         <v>170</v>
@@ -21459,7 +21495,9 @@
         <v>594</v>
       </c>
       <c r="I320" s="12"/>
-      <c r="J320" s="12"/>
+      <c r="J320" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K320" s="18">
         <f>(D320*6)+(E320*4)</f>
         <v>80</v>
@@ -21496,7 +21534,9 @@
         <v>596</v>
       </c>
       <c r="I321" s="12"/>
-      <c r="J321" s="12"/>
+      <c r="J321" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K321" s="18">
         <f>(D321*6)+(E321*4)</f>
         <v>230</v>
@@ -21533,7 +21573,9 @@
         <v>39</v>
       </c>
       <c r="I322" s="12"/>
-      <c r="J322" s="12"/>
+      <c r="J322" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K322" s="18">
         <f>(D322*6)+(E322*4)</f>
         <v>280</v>
@@ -21656,7 +21698,9 @@
         <v>602</v>
       </c>
       <c r="I325" s="12"/>
-      <c r="J325" s="12"/>
+      <c r="J325" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K325" s="18">
         <f>(D325*6)+(E325*4)</f>
         <v>170</v>
@@ -21736,7 +21780,9 @@
         <v>606</v>
       </c>
       <c r="I327" s="12"/>
-      <c r="J327" s="12"/>
+      <c r="J327" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K327" s="18">
         <f>(D327*6)+(E327*4)</f>
         <v>250</v>
@@ -21773,7 +21819,9 @@
         <v>39</v>
       </c>
       <c r="I328" s="12"/>
-      <c r="J328" s="12"/>
+      <c r="J328" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K328" s="18">
         <f>(D328*6)+(E328*4)</f>
         <v>120</v>
@@ -21896,7 +21944,9 @@
         <v>39</v>
       </c>
       <c r="I331" s="12"/>
-      <c r="J331" s="12"/>
+      <c r="J331" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K331" s="18">
         <f>(D331*6)+(E331*4)</f>
         <v>550</v>
@@ -21937,7 +21987,9 @@
         <v>614</v>
       </c>
       <c r="I332" s="12"/>
-      <c r="J332" s="12"/>
+      <c r="J332" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K332" s="18">
         <f>(D332*6)+(E332*4)</f>
         <v>520</v>
@@ -21974,7 +22026,9 @@
         <v>616</v>
       </c>
       <c r="I333" s="12"/>
-      <c r="J333" s="12"/>
+      <c r="J333" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K333" s="18">
         <f>(D333*6)+(E333*4)</f>
         <v>660</v>
@@ -22011,7 +22065,9 @@
         <v>39</v>
       </c>
       <c r="I334" s="12"/>
-      <c r="J334" s="12"/>
+      <c r="J334" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K334" s="18">
         <f>(D334*6)+(E334*4)</f>
         <v>600</v>
@@ -22048,7 +22104,9 @@
         <v>619</v>
       </c>
       <c r="I335" s="12"/>
-      <c r="J335" s="12"/>
+      <c r="J335" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K335" s="18">
         <f>(D335*6)+(E335*4)</f>
         <v>360</v>
@@ -22085,7 +22143,9 @@
         <v>621</v>
       </c>
       <c r="I336" s="12"/>
-      <c r="J336" s="12"/>
+      <c r="J336" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K336" s="18">
         <f>(D336*6)+(E336*4)</f>
         <v>400</v>
@@ -22122,7 +22182,9 @@
         <v>623</v>
       </c>
       <c r="I337" s="12"/>
-      <c r="J337" s="12"/>
+      <c r="J337" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K337" s="18">
         <f>(D337*6)+(E337*4)</f>
         <v>690</v>
@@ -22159,7 +22221,9 @@
         <v>625</v>
       </c>
       <c r="I338" s="12"/>
-      <c r="J338" s="12"/>
+      <c r="J338" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K338" s="18">
         <f>(D338*6)+(E338*4)</f>
         <v>680</v>
@@ -22196,7 +22260,9 @@
         <v>627</v>
       </c>
       <c r="I339" s="12"/>
-      <c r="J339" s="12"/>
+      <c r="J339" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K339" s="18">
         <f>(D339*6)+(E339*4)</f>
         <v>590</v>
@@ -22276,7 +22342,9 @@
         <v>631</v>
       </c>
       <c r="I341" s="12"/>
-      <c r="J341" s="12"/>
+      <c r="J341" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K341" s="18">
         <f>(D341*6)+(E341*4)</f>
         <v>520</v>
@@ -22313,7 +22381,9 @@
         <v>633</v>
       </c>
       <c r="I342" s="12"/>
-      <c r="J342" s="12"/>
+      <c r="J342" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K342" s="18">
         <f>(D342*6)+(E342*4)</f>
         <v>540</v>
@@ -22350,7 +22420,9 @@
         <v>635</v>
       </c>
       <c r="I343" s="12"/>
-      <c r="J343" s="12"/>
+      <c r="J343" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K343" s="18">
         <f>(D343*6)+(E343*4)</f>
         <v>990</v>
@@ -22387,7 +22459,9 @@
         <v>637</v>
       </c>
       <c r="I344" s="12"/>
-      <c r="J344" s="12"/>
+      <c r="J344" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K344" s="18">
         <f>(D344*6)+(E344*4)</f>
         <v>800</v>
@@ -22424,7 +22498,9 @@
         <v>639</v>
       </c>
       <c r="I345" s="12"/>
-      <c r="J345" s="12"/>
+      <c r="J345" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K345" s="18">
         <f>(D345*6)+(E345*4)</f>
         <v>750</v>
@@ -22461,7 +22537,9 @@
         <v>641</v>
       </c>
       <c r="I346" s="12"/>
-      <c r="J346" s="12"/>
+      <c r="J346" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K346" s="18">
         <f>(D346*6)+(E346*4)</f>
         <v>1200</v>
@@ -22486,7 +22564,7 @@
         <v>40</v>
       </c>
       <c r="E347" s="18">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F347" t="s" s="19">
         <v>11</v>
@@ -22498,10 +22576,12 @@
         <v>643</v>
       </c>
       <c r="I347" s="12"/>
-      <c r="J347" s="12"/>
+      <c r="J347" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K347" s="18">
         <f>(D347*6)+(E347*4)</f>
-        <v>540</v>
+        <v>440</v>
       </c>
       <c r="L347" s="12"/>
       <c r="M347" s="12"/>
@@ -22535,7 +22615,9 @@
         <v>39</v>
       </c>
       <c r="I348" s="12"/>
-      <c r="J348" s="12"/>
+      <c r="J348" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K348" s="18">
         <f>(D348*6)+(E348*4)</f>
         <v>1150</v>
@@ -22744,7 +22826,9 @@
         <v>654</v>
       </c>
       <c r="I353" s="12"/>
-      <c r="J353" s="12"/>
+      <c r="J353" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K353" s="18">
         <f>(D353*6)+(E353*4)</f>
         <v>120</v>
@@ -22781,7 +22865,9 @@
         <v>656</v>
       </c>
       <c r="I354" s="12"/>
-      <c r="J354" s="12"/>
+      <c r="J354" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K354" s="18">
         <f>(D354*6)+(E354*4)</f>
         <v>100</v>
@@ -22818,7 +22904,9 @@
         <v>39</v>
       </c>
       <c r="I355" s="12"/>
-      <c r="J355" s="12"/>
+      <c r="J355" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K355" s="18">
         <f>(D355*6)+(E355*4)</f>
         <v>190</v>
@@ -22855,7 +22943,9 @@
         <v>39</v>
       </c>
       <c r="I356" s="12"/>
-      <c r="J356" s="12"/>
+      <c r="J356" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K356" s="18">
         <f>(D356*6)+(E356*4)</f>
         <v>230</v>
@@ -22892,7 +22982,9 @@
         <v>660</v>
       </c>
       <c r="I357" s="12"/>
-      <c r="J357" s="12"/>
+      <c r="J357" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K357" s="18">
         <f>(D357*6)+(E357*4)</f>
         <v>190</v>
@@ -22929,7 +23021,9 @@
         <v>662</v>
       </c>
       <c r="I358" s="12"/>
-      <c r="J358" s="12"/>
+      <c r="J358" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K358" s="18">
         <f>(D358*6)+(E358*4)</f>
         <v>100</v>
@@ -22966,7 +23060,9 @@
         <v>664</v>
       </c>
       <c r="I359" s="12"/>
-      <c r="J359" s="12"/>
+      <c r="J359" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K359" s="18">
         <f>(D359*6)+(E359*4)</f>
         <v>140</v>
@@ -23003,7 +23099,9 @@
         <v>666</v>
       </c>
       <c r="I360" s="12"/>
-      <c r="J360" s="12"/>
+      <c r="J360" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K360" s="18">
         <f>(D360*6)+(E360*4)</f>
         <v>180</v>
@@ -23040,7 +23138,9 @@
         <v>668</v>
       </c>
       <c r="I361" s="12"/>
-      <c r="J361" s="12"/>
+      <c r="J361" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K361" s="18">
         <f>(D361*6)+(E361*4)</f>
         <v>220</v>
@@ -23051,7 +23151,7 @@
       <c r="O361" s="12"/>
       <c r="P361" s="12"/>
     </row>
-    <row r="362" ht="32.05" customHeight="1">
+    <row r="362" ht="38.7" customHeight="1">
       <c r="A362" t="s" s="10">
         <v>669</v>
       </c>
@@ -23059,7 +23159,7 @@
         <v>33</v>
       </c>
       <c r="C362" s="18">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D362" s="18">
         <v>10</v>
@@ -23077,7 +23177,9 @@
         <v>670</v>
       </c>
       <c r="I362" s="12"/>
-      <c r="J362" s="12"/>
+      <c r="J362" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K362" s="18">
         <f>(D362*6)+(E362*4)</f>
         <v>100</v>
@@ -23114,7 +23216,9 @@
         <v>672</v>
       </c>
       <c r="I363" s="12"/>
-      <c r="J363" s="12"/>
+      <c r="J363" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K363" s="18">
         <f>(D363*6)+(E363*4)</f>
         <v>150</v>
@@ -23151,7 +23255,9 @@
         <v>674</v>
       </c>
       <c r="I364" s="12"/>
-      <c r="J364" s="12"/>
+      <c r="J364" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K364" s="18">
         <f>(D364*6)+(E364*4)</f>
         <v>200</v>
@@ -23317,7 +23423,9 @@
         <v>682</v>
       </c>
       <c r="I368" s="12"/>
-      <c r="J368" s="12"/>
+      <c r="J368" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K368" s="18">
         <f>(D368*6)+(E368*4)</f>
         <v>120</v>
@@ -50328,14 +50436,22 @@
       <c r="P132" s="12"/>
     </row>
     <row r="133" ht="20.05" customHeight="1">
-      <c r="A133" s="13"/>
-      <c r="B133" s="14"/>
-      <c r="C133" s="12"/>
+      <c r="A133" t="s" s="10">
+        <v>2067</v>
+      </c>
+      <c r="B133" t="s" s="11">
+        <v>1806</v>
+      </c>
+      <c r="C133" s="18">
+        <v>800</v>
+      </c>
       <c r="D133" s="12"/>
       <c r="E133" s="12"/>
       <c r="F133" s="12"/>
       <c r="G133" s="12"/>
-      <c r="H133" s="12"/>
+      <c r="H133" t="s" s="19">
+        <v>2068</v>
+      </c>
       <c r="I133" s="12"/>
       <c r="J133" s="12"/>
       <c r="K133" s="12"/>
@@ -57800,21 +57916,21 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="37">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="C2" t="s" s="37">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="D2" t="s" s="37">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="E2" t="s" s="37">
-        <v>2070</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="3" ht="16.55" customHeight="1">
       <c r="A3" t="s" s="38">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="B3" s="39">
         <v>52</v>
@@ -57823,16 +57939,16 @@
         <v>0.347</v>
       </c>
       <c r="D3" t="s" s="41">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="E3" s="42">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,1)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,1)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,1)</f>
-        <v>112</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" ht="16.35" customHeight="1">
       <c r="A4" t="s" s="43">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="B4" s="44">
         <v>48</v>
@@ -57841,16 +57957,16 @@
         <v>0.337</v>
       </c>
       <c r="D4" t="s" s="46">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="E4" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,2)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,2)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,2)</f>
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" ht="16.35" customHeight="1">
       <c r="A5" t="s" s="43">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B5" s="44">
         <v>27</v>
@@ -57859,16 +57975,16 @@
         <v>0.167</v>
       </c>
       <c r="D5" t="s" s="46">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="E5" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,3)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,3)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,3)</f>
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" ht="30.35" customHeight="1">
       <c r="A6" t="s" s="43">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="B6" s="44">
         <v>16</v>
@@ -57877,16 +57993,16 @@
         <v>0.1</v>
       </c>
       <c r="D6" t="s" s="46">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="E6" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,4)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,4)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,4)</f>
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" ht="16.35" customHeight="1">
       <c r="A7" t="s" s="48">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="B7" s="49">
         <v>9</v>
@@ -57895,11 +58011,11 @@
         <v>0.053</v>
       </c>
       <c r="D7" t="s" s="46">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="E7" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,5)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,5)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,5)</f>
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" ht="16.35" customHeight="1">
@@ -57928,17 +58044,17 @@
         <v>22</v>
       </c>
       <c r="B11" t="s" s="56">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="C11" s="57"/>
       <c r="D11" s="57"/>
       <c r="E11" t="s" s="58">
-        <v>2070</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="12" ht="16.35" customHeight="1">
       <c r="A12" t="s" s="43">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B12" s="44">
         <v>60</v>
@@ -57952,7 +58068,7 @@
     </row>
     <row r="13" ht="16.35" customHeight="1">
       <c r="A13" t="s" s="43">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="B13" s="44">
         <v>60</v>
@@ -57966,7 +58082,7 @@
     </row>
     <row r="14" ht="16.35" customHeight="1">
       <c r="A14" t="s" s="43">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="B14" s="44">
         <v>60</v>
@@ -58014,10 +58130,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" t="s" s="5">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="C2" t="s" s="5">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -58027,10 +58143,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="C3" t="s" s="17">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -58040,10 +58156,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="C4" t="s" s="19">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -58053,10 +58169,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="C5" t="s" s="19">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
@@ -58066,10 +58182,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="C6" t="s" s="19">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -58079,10 +58195,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="C7" t="s" s="19">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
@@ -58092,10 +58208,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="C8" t="s" s="19">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
@@ -58105,10 +58221,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="C9" t="s" s="19">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
@@ -58118,10 +58234,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="C10" t="s" s="19">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>

--- a/context/card_data.xlsx
+++ b/context/card_data.xlsx
@@ -31560,10 +31560,10 @@
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="30">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E27" s="30">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s" s="31">
         <v>3</v>

--- a/context/card_data.xlsx
+++ b/context/card_data.xlsx
@@ -5299,7 +5299,7 @@
     <t>Hostage</t>
   </si>
   <si>
-    <t>You reveal 1 own cell. Until this turn ends, attacker cannot target that cell.</t>
+    <t>Usable when foe attacks. You can reveal one of your unit. Until this turn ends, foe cannot target that unit. If already targeted it, foe must choose other cell.</t>
   </si>
   <si>
     <t>Bait</t>
@@ -5378,7 +5378,7 @@
     <t>Bunker</t>
   </si>
   <si>
-    <t>Attacker cannot target surrounding cells until the end of this turn.</t>
+    <t>Usable when foe attack this card or surround cells. Foe cannot target surrounding cells until the end of this turn. If already targeted, they must choose other cell.</t>
   </si>
   <si>
     <t>Foul Gas</t>
@@ -5618,7 +5618,7 @@
     <t>Self-destruct</t>
   </si>
   <si>
-    <t>You select 1 of your unit. +10 ATK until your turn ends, but also destroy it. You pay no cost.</t>
+    <t>You select 1 of your unit. +50 ATK&amp;DEF until your turn ends, but also destroy it. You pay no cost.</t>
   </si>
   <si>
     <t>Rank C Bounty</t>
@@ -5972,7 +5972,7 @@
     <t>Illustration</t>
   </si>
   <si>
-    <t>Booster Pack - Blightsilver / 3</t>
+    <t>Booster Pack - Blightsilver / 4</t>
   </si>
   <si>
     <t>Booster Pack - Unseen Presence / 2</t>
@@ -10050,7 +10050,9 @@
         <f>(D36*6)+(E36*4)</f>
         <v>1280</v>
       </c>
-      <c r="L36" s="12"/>
+      <c r="L36" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
       <c r="O36" s="12"/>
@@ -10798,7 +10800,9 @@
         <f>(D54*6)+(E54*4)</f>
         <v>300</v>
       </c>
-      <c r="L54" s="12"/>
+      <c r="L54" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M54" s="12"/>
       <c r="N54" s="12"/>
       <c r="O54" s="12"/>
@@ -10880,7 +10884,9 @@
         <f>(D56*6)+(E56*4)</f>
         <v>1310</v>
       </c>
-      <c r="L56" s="12"/>
+      <c r="L56" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M56" s="12"/>
       <c r="N56" s="12"/>
       <c r="O56" s="12"/>
@@ -16553,7 +16559,9 @@
         <f>(D197*6)+(E197*4)</f>
         <v>810</v>
       </c>
-      <c r="L197" s="12"/>
+      <c r="L197" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M197" s="12"/>
       <c r="N197" s="12"/>
       <c r="O197" s="12"/>
@@ -17863,7 +17871,9 @@
         <f>(D229*6)+(E229*4)</f>
         <v>410</v>
       </c>
-      <c r="L229" s="12"/>
+      <c r="L229" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M229" s="12"/>
       <c r="N229" s="12"/>
       <c r="O229" s="12"/>
@@ -23462,7 +23472,9 @@
         <v>684</v>
       </c>
       <c r="I369" s="12"/>
-      <c r="J369" s="12"/>
+      <c r="J369" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K369" s="18">
         <f>(D369*6)+(E369*4)</f>
         <v>150</v>
@@ -23499,7 +23511,9 @@
         <v>686</v>
       </c>
       <c r="I370" s="12"/>
-      <c r="J370" s="12"/>
+      <c r="J370" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K370" s="18">
         <f>(D370*6)+(E370*4)</f>
         <v>280</v>
@@ -23536,7 +23550,9 @@
         <v>688</v>
       </c>
       <c r="I371" s="12"/>
-      <c r="J371" s="12"/>
+      <c r="J371" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K371" s="18">
         <f>(D371*6)+(E371*4)</f>
         <v>330</v>
@@ -23616,7 +23632,9 @@
         <v>691</v>
       </c>
       <c r="I373" s="12"/>
-      <c r="J373" s="12"/>
+      <c r="J373" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K373" s="18">
         <f>(D373*6)+(E373*4)</f>
         <v>240</v>
@@ -23653,7 +23671,9 @@
         <v>693</v>
       </c>
       <c r="I374" s="12"/>
-      <c r="J374" s="12"/>
+      <c r="J374" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K374" s="18">
         <f>(D374*6)+(E374*4)</f>
         <v>130</v>
@@ -23776,7 +23796,9 @@
         <v>699</v>
       </c>
       <c r="I377" s="12"/>
-      <c r="J377" s="12"/>
+      <c r="J377" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K377" s="18">
         <f>(D377*6)+(E377*4)</f>
         <v>390</v>
@@ -23813,7 +23835,9 @@
         <v>701</v>
       </c>
       <c r="I378" s="12"/>
-      <c r="J378" s="12"/>
+      <c r="J378" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K378" s="18">
         <f>(D378*6)+(E378*4)</f>
         <v>590</v>
@@ -23850,7 +23874,9 @@
         <v>703</v>
       </c>
       <c r="I379" s="12"/>
-      <c r="J379" s="12"/>
+      <c r="J379" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K379" s="18">
         <f>(D379*6)+(E379*4)</f>
         <v>240</v>
@@ -23887,7 +23913,9 @@
         <v>705</v>
       </c>
       <c r="I380" s="12"/>
-      <c r="J380" s="12"/>
+      <c r="J380" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K380" s="18">
         <f>(D380*6)+(E380*4)</f>
         <v>490</v>
@@ -23924,7 +23952,9 @@
         <v>707</v>
       </c>
       <c r="I381" s="12"/>
-      <c r="J381" s="12"/>
+      <c r="J381" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K381" s="18">
         <f>(D381*6)+(E381*4)</f>
         <v>500</v>
@@ -23961,7 +23991,9 @@
         <v>709</v>
       </c>
       <c r="I382" s="12"/>
-      <c r="J382" s="12"/>
+      <c r="J382" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K382" s="18">
         <f>(D382*6)+(E382*4)</f>
         <v>470</v>
@@ -23998,7 +24030,9 @@
         <v>711</v>
       </c>
       <c r="I383" s="12"/>
-      <c r="J383" s="12"/>
+      <c r="J383" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K383" s="18">
         <f>(D383*6)+(E383*4)</f>
         <v>200</v>
@@ -24082,7 +24116,9 @@
         <v>715</v>
       </c>
       <c r="I385" s="12"/>
-      <c r="J385" s="12"/>
+      <c r="J385" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K385" s="18">
         <f>(D385*6)+(E385*4)</f>
         <v>630</v>
@@ -24119,7 +24155,9 @@
         <v>646</v>
       </c>
       <c r="I386" s="12"/>
-      <c r="J386" s="12"/>
+      <c r="J386" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K386" s="18">
         <f>(D386*6)+(E386*4)</f>
         <v>1300</v>
@@ -24199,7 +24237,9 @@
         <v>720</v>
       </c>
       <c r="I388" s="12"/>
-      <c r="J388" s="12"/>
+      <c r="J388" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K388" s="18">
         <f>(D388*6)+(E388*4)</f>
         <v>790</v>
@@ -24236,7 +24276,9 @@
         <v>722</v>
       </c>
       <c r="I389" s="12"/>
-      <c r="J389" s="12"/>
+      <c r="J389" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K389" s="18">
         <f>(D389*6)+(E389*4)</f>
         <v>0</v>
@@ -24273,7 +24315,9 @@
         <v>724</v>
       </c>
       <c r="I390" s="12"/>
-      <c r="J390" s="12"/>
+      <c r="J390" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K390" s="18">
         <f>(D390*6)+(E390*4)</f>
         <v>600</v>
@@ -24353,7 +24397,9 @@
         <v>39</v>
       </c>
       <c r="I392" s="12"/>
-      <c r="J392" s="12"/>
+      <c r="J392" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K392" s="18">
         <f>(D392*6)+(E392*4)</f>
         <v>1040</v>
@@ -24390,7 +24436,9 @@
         <v>39</v>
       </c>
       <c r="I393" s="12"/>
-      <c r="J393" s="12"/>
+      <c r="J393" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K393" s="18">
         <f>(D393*6)+(E393*4)</f>
         <v>420</v>
@@ -24427,7 +24475,9 @@
         <v>730</v>
       </c>
       <c r="I394" s="12"/>
-      <c r="J394" s="12"/>
+      <c r="J394" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K394" s="18">
         <f>(D394*6)+(E394*4)</f>
         <v>790</v>
@@ -24464,7 +24514,9 @@
         <v>732</v>
       </c>
       <c r="I395" s="12"/>
-      <c r="J395" s="12"/>
+      <c r="J395" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K395" s="18">
         <f>(D395*6)+(E395*4)</f>
         <v>1800</v>
@@ -24501,7 +24553,9 @@
         <v>734</v>
       </c>
       <c r="I396" s="12"/>
-      <c r="J396" s="12"/>
+      <c r="J396" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="K396" s="18">
         <f>(D396*6)+(E396*4)</f>
         <v>980</v>
@@ -35692,7 +35746,7 @@
         <v>1576</v>
       </c>
       <c r="C4" s="18">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -36130,7 +36184,7 @@
         <v>1576</v>
       </c>
       <c r="C17" s="18">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -36214,7 +36268,9 @@
         <v>35</v>
       </c>
       <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
+      <c r="L19" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
@@ -36244,7 +36300,9 @@
         <v>35</v>
       </c>
       <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
+      <c r="L20" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
       <c r="O20" s="12"/>
@@ -36308,7 +36366,9 @@
         <v>35</v>
       </c>
       <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
+      <c r="L22" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
       <c r="O22" s="12"/>
@@ -36368,7 +36428,9 @@
         <v>35</v>
       </c>
       <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
+      <c r="L24" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
       <c r="O24" s="12"/>
@@ -36398,7 +36460,9 @@
         <v>35</v>
       </c>
       <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
+      <c r="L25" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
@@ -36908,7 +36972,9 @@
         <v>35</v>
       </c>
       <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
+      <c r="L42" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M42" s="12"/>
       <c r="N42" s="12"/>
       <c r="O42" s="12"/>
@@ -46661,7 +46727,7 @@
   <dimension ref="A1:P545"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.3516" style="35" customWidth="1"/>
+    <col min="1" max="1" width="27.7422" style="35" customWidth="1"/>
     <col min="2" max="2" width="9.67188" style="35" customWidth="1"/>
     <col min="3" max="3" width="5.17188" style="35" customWidth="1"/>
     <col min="4" max="4" width="6.17188" style="35" customWidth="1"/>
@@ -47147,7 +47213,9 @@
         <v>35</v>
       </c>
       <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
+      <c r="L15" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
@@ -47247,7 +47315,9 @@
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
+      <c r="N18" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
     </row>
@@ -47275,7 +47345,9 @@
         <v>35</v>
       </c>
       <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
+      <c r="L19" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
@@ -47335,7 +47407,9 @@
         <v>35</v>
       </c>
       <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
+      <c r="L21" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
@@ -47493,7 +47567,9 @@
         <v>35</v>
       </c>
       <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
+      <c r="L26" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
@@ -57961,7 +58037,7 @@
       </c>
       <c r="E4" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,2)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,2)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,2)</f>
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="16.35" customHeight="1">
@@ -57979,7 +58055,7 @@
       </c>
       <c r="E5" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,3)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,3)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,3)</f>
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" ht="30.35" customHeight="1">
@@ -57997,7 +58073,7 @@
       </c>
       <c r="E6" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,4)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,4)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,4)</f>
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="16.35" customHeight="1">
@@ -58015,7 +58091,7 @@
       </c>
       <c r="E7" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$J$3:$J$599,"Yes",'Unit'!$G$3:$G$599,5)+_xlfn.COUNTIFS('Trap'!$J$3:$J$544,"Yes",'Trap'!$G$3:$G$544,5)+_xlfn.COUNTIFS('Tech'!$J$3:$J$545,"Yes",'Tech'!$G$3:$G$545,5)</f>
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" ht="16.35" customHeight="1">
@@ -58063,7 +58139,7 @@
       <c r="D12" s="54"/>
       <c r="E12" s="47">
         <f>_xlfn.COUNTIFS('Unit'!$N$3:$N$599,"Yes")+_xlfn.COUNTIFS('Trap'!$N$3:$N$544,"Yes")+_xlfn.COUNTIFS('Tech'!$N$3:$N$545,"Yes")</f>
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" ht="16.35" customHeight="1">

--- a/context/card_data.xlsx
+++ b/context/card_data.xlsx
@@ -5522,7 +5522,7 @@
     <t>Union Cage</t>
   </si>
   <si>
-    <t>If attacker Is Union card, that unit cannot attack until the attacker’s next turn ends.</t>
+    <t>Usable if a Union card attack this card or the surround cell. That Union card cannot attack until the attacker’s next turn ends.</t>
   </si>
   <si>
     <t>Plunder</t>
@@ -8845,7 +8845,9 @@
         <f>(D7*6)+(E7*4)</f>
         <v>780</v>
       </c>
-      <c r="L7" s="12"/>
+      <c r="L7" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
@@ -11081,7 +11083,9 @@
         <f>(D61*6)+(E61*4)</f>
         <v>830</v>
       </c>
-      <c r="L61" s="12"/>
+      <c r="L61" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M61" s="12"/>
       <c r="N61" s="12"/>
       <c r="O61" s="12"/>
@@ -36034,7 +36038,9 @@
         <v>35</v>
       </c>
       <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
+      <c r="L12" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
@@ -36942,7 +36948,9 @@
         <v>35</v>
       </c>
       <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
+      <c r="L41" t="s" s="19">
+        <v>35</v>
+      </c>
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
       <c r="O41" s="12"/>
@@ -47345,9 +47353,7 @@
         <v>35</v>
       </c>
       <c r="K19" s="12"/>
-      <c r="L19" t="s" s="19">
-        <v>35</v>
-      </c>
+      <c r="L19" s="12"/>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
@@ -47487,7 +47493,7 @@
         <v>1806</v>
       </c>
       <c r="C24" s="18">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
@@ -47551,7 +47557,7 @@
         <v>1806</v>
       </c>
       <c r="C26" s="18">
-        <v>2000</v>
+        <v>900</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
@@ -48585,7 +48591,7 @@
         <v>1806</v>
       </c>
       <c r="C62" s="18">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="12"/>
